--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF97705-A2CC-464B-A4F9-EF428D868DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE760351-495E-4FE4-BB8B-C285D05C4CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,24 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>GRADE</t>
-  </si>
-  <si>
-    <t>CLASS</t>
-  </si>
-  <si>
-    <t>PHONE</t>
-  </si>
-  <si>
-    <t>NOTES</t>
-  </si>
-  <si>
     <t>أحمد محمد</t>
   </si>
   <si>
@@ -52,13 +34,31 @@
   </si>
   <si>
     <t>محمد علي</t>
+  </si>
+  <si>
+    <t>student_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>notes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,13 +74,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -95,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -111,6 +123,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -392,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -405,22 +420,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -428,10 +443,10 @@
         <v>1234567890</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -446,10 +461,10 @@
         <v>1234567891</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
@@ -458,6 +473,12 @@
         <v>966500000001</v>
       </c>
       <c r="F3" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE760351-495E-4FE4-BB8B-C285D05C4CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA77534-E2F3-4388-8334-2ECE907ABA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>أحمد محمد</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="298">
   <si>
     <t>الأول الثانوي</t>
   </si>
   <si>
-    <t>محمد علي</t>
-  </si>
-  <si>
     <t>student_id</t>
   </si>
   <si>
@@ -52,13 +46,886 @@
   </si>
   <si>
     <t>notes</t>
+  </si>
+  <si>
+    <t>ﺍﺣﻣﺩ ﻋﺑﺩﺍﻟﺭﺣﻳﻡ ﻣﺻﻠﺢ ﺍﻻﺣﻣﺩﻱ</t>
+  </si>
+  <si>
+    <t>أصيل بخيت سعد الجهني</t>
+  </si>
+  <si>
+    <t>البراء معتز بن عمر هب الريح</t>
+  </si>
+  <si>
+    <t>باسم بن عبد الباسط بن مدني نمنكاني</t>
+  </si>
+  <si>
+    <t>حسن خالد حسن بوارشي</t>
+  </si>
+  <si>
+    <t>حسين معتوق بن محسن ابوعمير</t>
+  </si>
+  <si>
+    <t>خالد أحمد خالد تركستاني</t>
+  </si>
+  <si>
+    <t>زياد سامي حامد الحربي</t>
+  </si>
+  <si>
+    <t>سلطان عبد الله سليمان الأحمدي</t>
+  </si>
+  <si>
+    <t>عبدالاله فيصل بن غازي شندي</t>
+  </si>
+  <si>
+    <t>عبد الرحمن عامر اجرزو</t>
+  </si>
+  <si>
+    <t>عبد الرحمن نادر عبد الرحمن الياس</t>
+  </si>
+  <si>
+    <t>عبد العزيز سالم عواض المطيري</t>
+  </si>
+  <si>
+    <t>عبد الله خالد عبد الرحمن الردادي</t>
+  </si>
+  <si>
+    <t>عبد المجيد محمد عيد احمد</t>
+  </si>
+  <si>
+    <t>عمار ايمن انور نقشبندي</t>
+  </si>
+  <si>
+    <t>عمار عبد الله عبد العزيز العماري</t>
+  </si>
+  <si>
+    <t>عمر خالد عبد العزيز العماري</t>
+  </si>
+  <si>
+    <t>فارس بندر محمد القليطي</t>
+  </si>
+  <si>
+    <t>محمد احمد حمد الاحمدي</t>
+  </si>
+  <si>
+    <t>محمد تركي عيد السهلي</t>
+  </si>
+  <si>
+    <t>محمد حسين حامد الهاجوج</t>
+  </si>
+  <si>
+    <t>محمد خادم حسين أحمد</t>
+  </si>
+  <si>
+    <t>محمد غازي بن منصور الشريف</t>
+  </si>
+  <si>
+    <t>محمد كاتب مريشد الرويثي</t>
+  </si>
+  <si>
+    <t>نواف اكرم صالح العمري</t>
+  </si>
+  <si>
+    <t>هادي صالح محمد صالح النخلي</t>
+  </si>
+  <si>
+    <t>وليد احمد رجاء العوفي</t>
+  </si>
+  <si>
+    <t>يوسف حاتم عبد الله العمري</t>
+  </si>
+  <si>
+    <t>إبراهيم سلطان على الأحمدي</t>
+  </si>
+  <si>
+    <t>انس سعد مطلق الشمري</t>
+  </si>
+  <si>
+    <t>احمد محمد عبد الله محمود</t>
+  </si>
+  <si>
+    <t>اصيل ريان أنور أبو طالب</t>
+  </si>
+  <si>
+    <t>ساري اياد احمد سالم</t>
+  </si>
+  <si>
+    <t>صالح عبد الله صلاح الأحمدي</t>
+  </si>
+  <si>
+    <t>عبد الإله محمد عوده البلادي</t>
+  </si>
+  <si>
+    <t>عبد البر محمد عبد الرحمن الجهني</t>
+  </si>
+  <si>
+    <t>عبد الرحمن خالد حمدان ال مسعود</t>
+  </si>
+  <si>
+    <t>عبد الملك مروان عبد الرؤوف حفظي</t>
+  </si>
+  <si>
+    <t>عزام نشمي ناير الحربي</t>
+  </si>
+  <si>
+    <t>عمار محمد غالي الصبحي</t>
+  </si>
+  <si>
+    <t>فارس عبد الرحمن محمد المطيري</t>
+  </si>
+  <si>
+    <t>فارس محمد عمر فاروق</t>
+  </si>
+  <si>
+    <t>فراس بندر فواز السناني</t>
+  </si>
+  <si>
+    <t>فيصل ماجد محمد العلوي</t>
+  </si>
+  <si>
+    <t>فيصل وائل محمد المطيري</t>
+  </si>
+  <si>
+    <t>محمد أحمد محمد الصبحي</t>
+  </si>
+  <si>
+    <t>محمد حامد عبد الرحيم جان</t>
+  </si>
+  <si>
+    <t>محمد سامر مقبول الشريف</t>
+  </si>
+  <si>
+    <t>محمد عبد العزيز مشخص المخلفي</t>
+  </si>
+  <si>
+    <t>محمد نزار محمد صالح</t>
+  </si>
+  <si>
+    <t>محمد يحي محمد الشهري</t>
+  </si>
+  <si>
+    <t>معن صالح طالب الأحمدي</t>
+  </si>
+  <si>
+    <t>مهند سامي علي القليطي العمري</t>
+  </si>
+  <si>
+    <t>ناصر فهد صنيتان الحربي</t>
+  </si>
+  <si>
+    <t>يزن جعفر نزير عبد الغني</t>
+  </si>
+  <si>
+    <t>احمد عدنان ناجي جعفر</t>
+  </si>
+  <si>
+    <t>احمد وليد احمد آل عباس</t>
+  </si>
+  <si>
+    <t>بدر عبد الكريم على فلاته</t>
+  </si>
+  <si>
+    <t>تميم نايف مشعان الحربي</t>
+  </si>
+  <si>
+    <t>حازم ناصر محيل السهلي</t>
+  </si>
+  <si>
+    <t>حسن عبد الله حسن علام</t>
+  </si>
+  <si>
+    <t>حماد صالح حماد الحماد</t>
+  </si>
+  <si>
+    <t>حمزة احمد عبد المنعم صائب</t>
+  </si>
+  <si>
+    <t>خالد عبد الكريم محمد الشنقيطي</t>
+  </si>
+  <si>
+    <t>ريان عيسى معيض العوفي</t>
+  </si>
+  <si>
+    <t>ساري احمد بخيت الصاعدي</t>
+  </si>
+  <si>
+    <t>سامر طلال سلمان الصاعدي</t>
+  </si>
+  <si>
+    <t>سلطان سعيد أحمد باخشوين</t>
+  </si>
+  <si>
+    <t>عبد الرحمن طه سليمان شقرون</t>
+  </si>
+  <si>
+    <t>عبد الرحمن وائل حسين رفيع</t>
+  </si>
+  <si>
+    <t>عبد العزيز على دخيل الله العوفي</t>
+  </si>
+  <si>
+    <t>عبد الملك درويش صالح محروس</t>
+  </si>
+  <si>
+    <t>علي ماجد هاشم النخلي</t>
+  </si>
+  <si>
+    <t>غازي ياسر غويزي المطيري</t>
+  </si>
+  <si>
+    <t>فيصل تركي عبد الحميد العمري</t>
+  </si>
+  <si>
+    <t>فيصل محمد عواد العنزي</t>
+  </si>
+  <si>
+    <t>محمد حسين أحمد فلاته</t>
+  </si>
+  <si>
+    <t>محمد هيثم عبد الله امين</t>
+  </si>
+  <si>
+    <t>محمد نعمي محمد الشهري</t>
+  </si>
+  <si>
+    <t>نواف نايف هلال المطيري</t>
+  </si>
+  <si>
+    <t>هاشم فاضل شطي الشمري</t>
+  </si>
+  <si>
+    <t>يوسف عصام يوسف مطبقاني</t>
+  </si>
+  <si>
+    <t>ابراهيم سفيان ابراهيم القداح</t>
+  </si>
+  <si>
+    <t>احمد عبد الله عوض مبارك سعيد</t>
+  </si>
+  <si>
+    <t>البراء توفيق شاكر ناصر الأحمدي</t>
+  </si>
+  <si>
+    <t>الياس نزار امين شيخ</t>
+  </si>
+  <si>
+    <t>اياد عبد الله اياد ابوالفرج</t>
+  </si>
+  <si>
+    <t>أحمد إبراهيم عطية إسماعيل</t>
+  </si>
+  <si>
+    <t>أمجد سهل محمد بنجي</t>
+  </si>
+  <si>
+    <t>أويس اسامة محمد جبلاوي</t>
+  </si>
+  <si>
+    <t>براء ابراهيم عبد العزيز داغستاني</t>
+  </si>
+  <si>
+    <t>تميم عساف الحميدي التميمي</t>
+  </si>
+  <si>
+    <t>جهاد انس محمد رياض زهدي</t>
+  </si>
+  <si>
+    <t>جواد انس محمد رياض زهدي</t>
+  </si>
+  <si>
+    <t>حسن عباس حسن نور</t>
+  </si>
+  <si>
+    <t>سلمان عبد الله رابح الرحيلي</t>
+  </si>
+  <si>
+    <t>شاهين صالح دخيل الله موسى النخلي</t>
+  </si>
+  <si>
+    <t>عبد الرحيم إبراهيم الشنقيطي</t>
+  </si>
+  <si>
+    <t>عبد الله بندر غالب الرفيعي</t>
+  </si>
+  <si>
+    <t>عبد الله طلال عبد الله ابوحسين</t>
+  </si>
+  <si>
+    <t>عبدالاله علاء عبد المجيد بري</t>
+  </si>
+  <si>
+    <t>عدي ريان سعود العمري</t>
+  </si>
+  <si>
+    <t>عصام أشرف عواد حمد الاحمدي</t>
+  </si>
+  <si>
+    <t>عمار محمد عبد الله الميمني</t>
+  </si>
+  <si>
+    <t>فيصل عبد الحميد حامد السيد</t>
+  </si>
+  <si>
+    <t>محمد هاني حمزة جعفر</t>
+  </si>
+  <si>
+    <t>محمود ماجد محمود ابوخضير</t>
+  </si>
+  <si>
+    <t>معاذ حسن احمد البار</t>
+  </si>
+  <si>
+    <t>ياسر رائد سالم المحمدي</t>
+  </si>
+  <si>
+    <t>البراء عبد الرحمن غازي الصاعدي</t>
+  </si>
+  <si>
+    <t>أسامة إبراهيم شلوه الشاماني</t>
+  </si>
+  <si>
+    <t>حسام عبد العزيز دخيل المطيري</t>
+  </si>
+  <si>
+    <t>حمزة صياح فهد الجهني</t>
+  </si>
+  <si>
+    <t>خالد عادل خالد الجربوع</t>
+  </si>
+  <si>
+    <t>راكان هاني حامد السهلي</t>
+  </si>
+  <si>
+    <t>رامي عبد الله عويض الحربي</t>
+  </si>
+  <si>
+    <t>زياد عبد الله محمد القرني</t>
+  </si>
+  <si>
+    <t>سلطان محمد بخيت النزاوي</t>
+  </si>
+  <si>
+    <t>عبد الحميد حسن محمد حسن</t>
+  </si>
+  <si>
+    <t>عبد العزيز ياسر سليمان الحربي</t>
+  </si>
+  <si>
+    <t>عبد الله سالم صالح الصعيري</t>
+  </si>
+  <si>
+    <t>عبد الله علي عبد الله أبوالنصر</t>
+  </si>
+  <si>
+    <t>عبد الله غسان خالد نور</t>
+  </si>
+  <si>
+    <t>عبد الله محمد عبد الله باجيل</t>
+  </si>
+  <si>
+    <t>عبد الله مصلح سالم الصاعدي</t>
+  </si>
+  <si>
+    <t>عثمان عزيز مفلح المرواني</t>
+  </si>
+  <si>
+    <t>عمار مروان أسعد كابلي</t>
+  </si>
+  <si>
+    <t>عمر اسامه عمر عسيلان</t>
+  </si>
+  <si>
+    <t>عمر عبد الرحمن العوفي</t>
+  </si>
+  <si>
+    <t>قصي أحمد الزغيبي</t>
+  </si>
+  <si>
+    <t>محمد عبد الرحمن عيد الجهني</t>
+  </si>
+  <si>
+    <t>محمد محمود محمد كاتب</t>
+  </si>
+  <si>
+    <t>محمد نادر حامد سوتل</t>
+  </si>
+  <si>
+    <t>ناصر خالد ناصر الصبيحي</t>
+  </si>
+  <si>
+    <t>ناصر فارس الحربي</t>
+  </si>
+  <si>
+    <t>نبيل نشأت نبيل درندري</t>
+  </si>
+  <si>
+    <t>هشام يوسف محسن العمري</t>
+  </si>
+  <si>
+    <t>احمد فيصل بن احمد النعمان</t>
+  </si>
+  <si>
+    <t>الثاني الثانوي</t>
+  </si>
+  <si>
+    <t>اسامه محمدبسام ابراهيم قاره</t>
+  </si>
+  <si>
+    <t>بدر صالح بن حماد الحماد</t>
+  </si>
+  <si>
+    <t>تركي عبدالله تركي الشهراني</t>
+  </si>
+  <si>
+    <t>تميم وليد عبدالرحمن الرحيلي</t>
+  </si>
+  <si>
+    <t>حمزه محمد فضل الله قاضي</t>
+  </si>
+  <si>
+    <t>خالد وليد جابر الجزار</t>
+  </si>
+  <si>
+    <t>سعود سلطان بن سعود غوني</t>
+  </si>
+  <si>
+    <t>سيف ناصر بن سيف السبيعي</t>
+  </si>
+  <si>
+    <t>عابد أحمد عبد القادر مقرش</t>
+  </si>
+  <si>
+    <t>عبدالرحمن عبدالله عبدالرحمن السحيم</t>
+  </si>
+  <si>
+    <t>عدي علاء عبدالرؤف نجار</t>
+  </si>
+  <si>
+    <t>علي طلال علي الغري</t>
+  </si>
+  <si>
+    <t>فيصل سلطان بن غويزي الحربي</t>
+  </si>
+  <si>
+    <t>فيصل وليد خالد العقالي</t>
+  </si>
+  <si>
+    <t>ماهر حمد مرزوق الرشيدي</t>
+  </si>
+  <si>
+    <t>محمد ايهاب بن مدني سندي</t>
+  </si>
+  <si>
+    <t>محمد تركي دخيل الله العنزي</t>
+  </si>
+  <si>
+    <t>محمد خالد حسن عسيلان</t>
+  </si>
+  <si>
+    <t>محمد عماد سعد الدين براده</t>
+  </si>
+  <si>
+    <t>محمد يزن موسى محافظة</t>
+  </si>
+  <si>
+    <t>مساعد عبدالعزيز عبدالله الفالح</t>
+  </si>
+  <si>
+    <t>مصطفى هيثم طاهر قاره</t>
+  </si>
+  <si>
+    <t>معتز عبدالله بن عزالدين التونسى</t>
+  </si>
+  <si>
+    <t>يزن اياد انور نقشبندي</t>
+  </si>
+  <si>
+    <t>يوسف عبدالله بن ناشي السراني</t>
+  </si>
+  <si>
+    <t>احمد علي احمد البار</t>
+  </si>
+  <si>
+    <t>احمد بن منصور بن محمد الحناكي</t>
+  </si>
+  <si>
+    <t>اسامه فواز عواد الاحمدي</t>
+  </si>
+  <si>
+    <t>بدر خالد العنزي</t>
+  </si>
+  <si>
+    <t>الحسين وائل بن حسين رفيع</t>
+  </si>
+  <si>
+    <t>انس محمد عبيد الله العنزي</t>
+  </si>
+  <si>
+    <t>تركي هاني بن صالح محروس</t>
+  </si>
+  <si>
+    <t>حسام بن بدر بن سعد القليطي</t>
+  </si>
+  <si>
+    <t>حمود محمد بن حمود العنزي</t>
+  </si>
+  <si>
+    <t>راكان عبدالرحمن جابر الردادي</t>
+  </si>
+  <si>
+    <t>راكان عبد الله الجراح</t>
+  </si>
+  <si>
+    <t>راكان ماجد سعد الحربي</t>
+  </si>
+  <si>
+    <t>رائد فايز طالب الاحمدي</t>
+  </si>
+  <si>
+    <t>زين بن وائل بن زين فاخرجي</t>
+  </si>
+  <si>
+    <t>عاصم ماجد بن عبد الله الردادي</t>
+  </si>
+  <si>
+    <t>عبد المجيد سعيد فلاح الشهراني</t>
+  </si>
+  <si>
+    <t>عبد المجيد بن سلطان بن محسن الجهني</t>
+  </si>
+  <si>
+    <t>علي عبد الله علي النخلي</t>
+  </si>
+  <si>
+    <t>عمر بن عبد الله بن عبد الوهاب العباسي</t>
+  </si>
+  <si>
+    <t>عمرو خالد بن سليمان القطان</t>
+  </si>
+  <si>
+    <t>فهد محمد بن رافع الحربي</t>
+  </si>
+  <si>
+    <t>فيصل فهد بن عطية العوفي</t>
+  </si>
+  <si>
+    <t>فيصل محمد بن مرزق الجابري</t>
+  </si>
+  <si>
+    <t>ماجد محمد احمد محمد عبد الرحمن</t>
+  </si>
+  <si>
+    <t>احمد عباس مطيع النخلى</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد السوسي</t>
+  </si>
+  <si>
+    <t>اياد حامد احمدسالم الرحيلي</t>
+  </si>
+  <si>
+    <t>اياد عبدالرحمن بن سليم الحربي</t>
+  </si>
+  <si>
+    <t>تميم نايف بن محمد العوفي</t>
+  </si>
+  <si>
+    <t>حسين وهيب محسن المشهدي</t>
+  </si>
+  <si>
+    <t>حمزه وهيب محسن المشهدي</t>
+  </si>
+  <si>
+    <t>رائف ابراهيم جميل السقا</t>
+  </si>
+  <si>
+    <t>سلمان محمد مردان علي</t>
+  </si>
+  <si>
+    <t>عامر خالد بن عامر المطيري</t>
+  </si>
+  <si>
+    <t>عبد المحسن نايف بن خلف الحربي</t>
+  </si>
+  <si>
+    <t>عبدالرحمن خالد عبدالله الشمراني</t>
+  </si>
+  <si>
+    <t>عبدالرحمن عبدالمحسن محمدكريم جان</t>
+  </si>
+  <si>
+    <t>عبدالعزيز محمد بن عبدالرحمن التركى</t>
+  </si>
+  <si>
+    <t>عبدالله احمد بن محمد صادق</t>
+  </si>
+  <si>
+    <t>عبدالله حسين شفيق قاسم</t>
+  </si>
+  <si>
+    <t>علي عدنان عباس المعيرفي</t>
+  </si>
+  <si>
+    <t>عمر بن يوسف بن مصلح الردادي</t>
+  </si>
+  <si>
+    <t>فارس وليد بن مبارك السالمي</t>
+  </si>
+  <si>
+    <t>محمد صالح حمد المسند</t>
+  </si>
+  <si>
+    <t>محمد صالح صلاح الحربي</t>
+  </si>
+  <si>
+    <t>محمد عصام هلال باسيم</t>
+  </si>
+  <si>
+    <t>معتصم احمد مبارك السالمي</t>
+  </si>
+  <si>
+    <t>مهند عدنان بن محمد باعبدالله</t>
+  </si>
+  <si>
+    <t>مهند حماد عابد الحربي</t>
+  </si>
+  <si>
+    <t>يزن صقر عبدالعزيز الأحمدي</t>
+  </si>
+  <si>
+    <t>يزيد وليد بن مفلح اللقماني</t>
+  </si>
+  <si>
+    <t>اياد طلال بن منصور رحيم</t>
+  </si>
+  <si>
+    <t>اياد عادل عبدالعزيز محروس</t>
+  </si>
+  <si>
+    <t>اياد عايض عبدالعزيز السلمي</t>
+  </si>
+  <si>
+    <t>ثامر عبدالله حمود المطيري</t>
+  </si>
+  <si>
+    <t>حسام هاني حامد الاحمدي</t>
+  </si>
+  <si>
+    <t>حسان صالح بن عويد البلادي</t>
+  </si>
+  <si>
+    <t>حمزة احمد محمد سكر</t>
+  </si>
+  <si>
+    <t>خالد احمد بن خالد العلمي</t>
+  </si>
+  <si>
+    <t>راشد سعود بن راشد الرشيدي</t>
+  </si>
+  <si>
+    <t>رضا قاسم دبيان الشريف</t>
+  </si>
+  <si>
+    <t>زكي محمد بن زكي عامودي</t>
+  </si>
+  <si>
+    <t>ساري حمدي حمدان العمري</t>
+  </si>
+  <si>
+    <t>عبد العزيز احمد بن عبد العزيز صبري</t>
+  </si>
+  <si>
+    <t>عبدالعزيز عادل بن حامد الحربي</t>
+  </si>
+  <si>
+    <t>عبدالملك محمد فالح العمري</t>
+  </si>
+  <si>
+    <t>علي ابراهيم بن علي بدوي</t>
+  </si>
+  <si>
+    <t>غسان بن ابراهيم بن عبد الله الحيدري</t>
+  </si>
+  <si>
+    <t>فارس محمد علي بن جمعه</t>
+  </si>
+  <si>
+    <t>فيصل عبد مامون الخواجا</t>
+  </si>
+  <si>
+    <t>متعب عبدالله سلطان العمري</t>
+  </si>
+  <si>
+    <t>محمد ايمن عربى العربى</t>
+  </si>
+  <si>
+    <t>معتز هاشم بن غازي غازي</t>
+  </si>
+  <si>
+    <t>ناصر سلطان بن ناصر القزلان</t>
+  </si>
+  <si>
+    <t>نايف عبدالعزيز بن نايف ابوشرقيه</t>
+  </si>
+  <si>
+    <t>يزن عبد الله حمزة الكردي</t>
+  </si>
+  <si>
+    <t>يزن احمد بن فايز الانصارى</t>
+  </si>
+  <si>
+    <t>احمد شفيق رأفت شفيق سالم</t>
+  </si>
+  <si>
+    <t>اسامه هاني مرعي السيد</t>
+  </si>
+  <si>
+    <t>باسل فرحان حمدان البلوي</t>
+  </si>
+  <si>
+    <t>سهل سلطان بن سهل مرغلاني</t>
+  </si>
+  <si>
+    <t>طارق عمر بن الهاشمي العلمي</t>
+  </si>
+  <si>
+    <t>عبد العزيز بن عبد الرحمن بن الجابري</t>
+  </si>
+  <si>
+    <t>عبد العزيز مهند فهد ابو الفرع</t>
+  </si>
+  <si>
+    <t>عبد الله يوسف عبد الله الزهراني</t>
+  </si>
+  <si>
+    <t>عبد الهادي محمد صالح بخاري</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود يحيي مصلي</t>
+  </si>
+  <si>
+    <t>عبدالعزيز علي بن سليمان المهنا</t>
+  </si>
+  <si>
+    <t>عمار عبدالكريم شديد الحربي</t>
+  </si>
+  <si>
+    <t>عمر عبدالوهاب عبدالقادر السمان</t>
+  </si>
+  <si>
+    <t>عمر محمد وليد طباخ</t>
+  </si>
+  <si>
+    <t>فارس مرتضى عبده النخلي</t>
+  </si>
+  <si>
+    <t>فيصل عيسى بن معيض العوفي</t>
+  </si>
+  <si>
+    <t>قيس عبدالهادي اسماعيل الشوبكي</t>
+  </si>
+  <si>
+    <t>محمد أحمد يحيي الأعجم</t>
+  </si>
+  <si>
+    <t>مؤيد علي بن محمد النخلي</t>
+  </si>
+  <si>
+    <t>وسام حسين أحمد الحازمي</t>
+  </si>
+  <si>
+    <t>يحيى سعود عوض الاحمدي</t>
+  </si>
+  <si>
+    <t>يزيد عبدالله عبيد السليمي</t>
+  </si>
+  <si>
+    <t>يزيد مازن بن مصطفى الجاوي</t>
+  </si>
+  <si>
+    <t>يوسف وحيد احمد تركستاني</t>
+  </si>
+  <si>
+    <t>إياد أحمد مزعل الحربي</t>
+  </si>
+  <si>
+    <t>اياس هاني بن احمد محمد</t>
+  </si>
+  <si>
+    <t>أنس محمد بن منير الشجعاني</t>
+  </si>
+  <si>
+    <t>تركي محمود محمدسعيد الردادي</t>
+  </si>
+  <si>
+    <t>حسين عبدالفتاح سندي</t>
+  </si>
+  <si>
+    <t>صهيب حسن بن نويشي الرحيلي</t>
+  </si>
+  <si>
+    <t>عاصم مشعل يوسف كشك</t>
+  </si>
+  <si>
+    <t>عبد الصمد حسين بن عمر حبش</t>
+  </si>
+  <si>
+    <t>عبد العزيز محمد نمنكاني</t>
+  </si>
+  <si>
+    <t>عبدالاله جمال بن سعود الأحمدي</t>
+  </si>
+  <si>
+    <t>عبدالرحمن احمد محمد عسيري</t>
+  </si>
+  <si>
+    <t>عبدالرحمن بن عليان بن عيفان الحربي</t>
+  </si>
+  <si>
+    <t>عبدالرحمن سالم علي التمام</t>
+  </si>
+  <si>
+    <t>عبدالعزيز لؤي بن عبدالعزيز كابلي</t>
+  </si>
+  <si>
+    <t>عمر محمد بن حمزه السيسي</t>
+  </si>
+  <si>
+    <t>محمد حمزة بن احمد شكري</t>
+  </si>
+  <si>
+    <t>محمد فؤاد محمد السوسي</t>
+  </si>
+  <si>
+    <t>محمود الحسين بن احمد الشنقيطي</t>
+  </si>
+  <si>
+    <t>معتز فالح بن حسن الجهني</t>
+  </si>
+  <si>
+    <t>نايف هلال فالح العمري</t>
+  </si>
+  <si>
+    <t>نواف بن باسم بن عبدالله المغامسي</t>
+  </si>
+  <si>
+    <t>هاشم سامي هاشم النخلي</t>
+  </si>
+  <si>
+    <t>يوسف خالد سليمان الذبياني</t>
+  </si>
+  <si>
+    <t>يوسف عبدالجليل عرفه العزب</t>
+  </si>
+  <si>
+    <t>يوسف محمود عبدالمجيد بخش</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,10 +942,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Sakkal Majalla"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,11 +981,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -103,11 +993,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,8 +1062,87 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -142,6 +1159,891 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12860</xdr:col>
+      <xdr:colOff>270503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>137153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="صورة 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ED50A79-2346-9C80-885E-BBED246EE18F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147483647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>416553</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>283203</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="صورة 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A29B531B-6BBE-7F1F-9EEB-3D274651BBC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2146727997" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>16503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>492753</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="صورة 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0FF8822-34EB-7A12-C04E-6070CE9A35C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144689647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>41903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>518153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="صورة 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F53CD4C3-EEEB-CF15-0D00-33B71A0F5B53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144054647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>441953</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>308603</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="صورة 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44DA049C-8EA1-CAC3-4BC1-7D2CA2565836}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143654597" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12860</xdr:col>
+      <xdr:colOff>270503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>137153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="صورة 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE00AFF1-9789-172F-34C3-436A23CFBFE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147483647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>416553</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>283203</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="صورة 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C48F74F-AAB3-427F-405F-F4766419E1AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2146727997" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>16503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>492753</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="صورة 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F58F4385-00C6-C77A-3734-D1BFF7E6A703}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144689647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>41903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>518153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="صورة 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D053007-3848-2CA4-FA98-66DBEA010E24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144054647" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>441953</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>308603</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="صورة 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B7FD5D-7BC7-2766-8A1C-164887BEE7C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143654597" y="241300"/>
+          <a:ext cx="476250" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>41903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>137153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="صورة 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA55FEE-23C6-3CA7-D0BF-419A729947B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147483647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>187953</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>283203</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="صورة 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A829262-41B9-9181-EE4C-63C1B33B8A9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2146727997" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>397503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>492753</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="صورة 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{867CD62E-73E1-5EE6-C189-21326DD56ABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144689647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>422903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>518153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="صورة 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCC09412-1ABC-BED5-14CC-BFE10AEF744E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144054647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>213353</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>308603</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="صورة 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D02E25B-39AF-77A8-DE65-BA1AB87A28FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143654597" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>41903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12861</xdr:col>
+      <xdr:colOff>137153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="صورة 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D22D5318-2D4C-4D36-24A6-AA56BC0F1E72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147483647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>187953</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12862</xdr:col>
+      <xdr:colOff>283203</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="صورة 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B513BB05-FDBD-B24E-BDC1-9537FFCAD95F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2146727997" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>397503</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12865</xdr:col>
+      <xdr:colOff>492753</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="صورة 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718EE585-B7CE-79D9-E6D5-2A8EF270F06F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144689647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>422903</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12866</xdr:col>
+      <xdr:colOff>518153</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="صورة 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27A1C41-E714-6FEA-4236-B3C9209405C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2144054647" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>213353</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12867</xdr:col>
+      <xdr:colOff>308603</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="صورة 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2E86DDE-A7D4-9300-9AD0-909802B99FE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143654597" y="241300"/>
+          <a:ext cx="95250" cy="95250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,82 +2307,4159 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="1" width="525" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3FA88C89-1EB9-474E-BAEB-DA58F295EB31}">
+  <we:reference id="WA200004687" version="1.0.0.3" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200004687" version="1.0.0.3" store="WA200004687" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D6E9006F-CD2F-455C-8F37-8CCFEDC02759}">
+  <we:reference id="WA200003220" version="1.0.0.0" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003220" version="1.0.0.0" store="WA200003220" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension3.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B86BB41F-9A62-4F16-8FA2-809FA280336B}">
+  <we:reference id="wa104051163" version="1.2.0.3" store="ar-SA" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104051163" version="1.2.0.3" store="WA104051163" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F291"/>
+  <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.7265625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" style="5" customWidth="1"/>
     <col min="6" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="6">
+        <v>1150436838</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>966554289816</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="10">
+        <v>1152217368</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>966556732717</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="10">
+        <v>1152502371</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A5" s="10">
+        <v>1152327969</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="10">
+        <v>2302448127</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A7" s="10">
+        <v>1153472889</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A8" s="10">
+        <v>1152518682</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A9" s="10">
+        <v>1158331023</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A10" s="10">
+        <v>1157900240</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A11" s="10">
+        <v>1150731048</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A12" s="10">
+        <v>2293198442</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A13" s="10">
+        <v>1174946861</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="10">
+        <v>1152820641</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A15" s="10">
+        <v>1149366963</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A16" s="10">
+        <v>1152734123</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A17" s="10">
+        <v>1152480891</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A18" s="10">
+        <v>1153507684</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="10">
+        <v>1150008413</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A20" s="10">
+        <v>1152989354</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A21" s="10">
+        <v>1152061618</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A22" s="10">
+        <v>1149206417</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A23" s="10">
+        <v>1151880513</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A24" s="10">
+        <v>2290421144</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A25" s="10">
+        <v>1160061816</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A26" s="16">
+        <v>1152890750</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A27" s="10">
+        <v>1151773627</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A28" s="10">
+        <v>1152536601</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A29" s="10">
+        <v>1150018610</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A30" s="10">
+        <v>1146587298</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A31" s="10">
+        <v>1150743167</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A32" s="10">
+        <v>1151146907</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A33" s="10">
+        <v>2443189093</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A34" s="10">
+        <v>1151434659</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A35" s="10">
+        <v>1152565972</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A36" s="10">
+        <v>1154025124</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A37" s="10">
+        <v>1154153991</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A38" s="10">
+        <v>1149486605</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A39" s="10">
+        <v>1152472815</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A40" s="10">
+        <v>1150396164</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A41" s="10">
+        <v>1150491064</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A42" s="10">
+        <v>1152786958</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A43" s="10">
+        <v>1149922534</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A44" s="10">
+        <v>2269053001</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A45" s="10">
+        <v>1157238989</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A46" s="10">
+        <v>1153155559</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A47" s="10">
+        <v>1149465245</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A48" s="10">
+        <v>1155938150</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A49" s="10">
+        <v>1149696633</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A50" s="10">
+        <v>1155454240</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A51" s="10">
+        <v>1150039038</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A52" s="10">
+        <v>1152218085</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A53" s="10">
+        <v>1147013252</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A54" s="10">
+        <v>1154169450</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A55" s="10">
+        <v>1151233614</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A56" s="10">
+        <v>1151650809</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A57" s="10">
+        <v>1151119201</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A58" s="10">
+        <v>1152878417</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A59" s="10">
+        <v>1152574958</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A60" s="10">
+        <v>1152986681</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A61" s="10">
+        <v>1151154455</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A62" s="10">
+        <v>1159289287</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A63" s="10">
+        <v>1153334618</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A64" s="10">
+        <v>1152212658</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A65" s="10">
+        <v>1152410336</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A66" s="10">
+        <v>1154207904</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A67" s="10">
+        <v>1168345245</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A68" s="10">
+        <v>1149893040</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A69" s="10">
+        <v>1151849807</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A70" s="10">
+        <v>1152284103</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A71" s="10">
+        <v>1167082591</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A72" s="10">
+        <v>1153479645</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A73" s="10">
+        <v>1155524893</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A74" s="10">
+        <v>1150599171</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A75" s="10">
+        <v>1154873481</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A76" s="10">
+        <v>1152884167</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A77" s="10">
+        <v>1152128029</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A78" s="10">
+        <v>1151910013</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A79" s="10">
+        <v>1154287575</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A80" s="10">
+        <v>1152571822</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A81" s="10">
+        <v>1150680112</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A82" s="10">
+        <v>1150690798</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A83" s="10">
+        <v>1151961511</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A84" s="10">
+        <v>1149761460</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A85" s="10">
+        <v>2297211076</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="13">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="86" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A86" s="10">
+        <v>1153216211</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A87" s="10">
+        <v>1152536460</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A88" s="10">
+        <v>1152152763</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A89" s="10">
+        <v>1156092080</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A90" s="10">
+        <v>2510170026</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A91" s="10">
+        <v>1151404256</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A92" s="10">
+        <v>1152224984</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D92" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A93" s="10">
+        <v>1150781068</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A94" s="10">
+        <v>1150218970</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A95" s="10">
+        <v>1153072044</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A96" s="10">
+        <v>1153072069</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D96" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A97" s="10">
+        <v>1149401059</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A98" s="10">
+        <v>1153495591</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A99" s="10">
+        <v>1150973210</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A100" s="10">
+        <v>1151704598</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A101" s="10">
+        <v>1151845870</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A102" s="10">
+        <v>1149888925</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A103" s="10">
+        <v>1153380116</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A104" s="10">
+        <v>1152305007</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A105" s="10">
+        <v>1153607922</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A106" s="10">
+        <v>1152853493</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A107" s="10">
+        <v>1153534167</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D107" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A108" s="10">
+        <v>1149855445</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A109" s="10">
+        <v>1153291388</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D109" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A110" s="10">
+        <v>1151814371</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A111" s="10">
+        <v>1158612646</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D111" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A112" s="10">
+        <v>1151003728</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D112" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A113" s="10">
+        <v>1174052116</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A114" s="10">
+        <v>1153013931</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D114" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A115" s="10">
+        <v>1150396081</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A116" s="10">
+        <v>1150690699</v>
+      </c>
+      <c r="B116" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A117" s="10">
+        <v>1152698252</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A118" s="10">
+        <v>1153384795</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A119" s="10">
+        <v>1150304325</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A120" s="10">
+        <v>1152915870</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A121" s="10">
+        <v>1152367700</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A122" s="10">
+        <v>1152775639</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D122" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A123" s="10">
+        <v>1149182303</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D123" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A124" s="10">
+        <v>1149628024</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A125" s="10">
+        <v>1152522833</v>
+      </c>
+      <c r="B125" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A126" s="10">
+        <v>2382166136</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D126" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A127" s="10">
+        <v>1151669510</v>
+      </c>
+      <c r="B127" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D127" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A128" s="10">
+        <v>1155012543</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D128" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A129" s="10">
+        <v>1150763322</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A130" s="10">
+        <v>1150527107</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A131" s="10">
+        <v>1171859398</v>
+      </c>
+      <c r="B131" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D131" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A132" s="10">
+        <v>1151485529</v>
+      </c>
+      <c r="B132" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A133" s="10">
+        <v>1153562317</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D133" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A134" s="10">
+        <v>1153018385</v>
+      </c>
+      <c r="B134" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A135" s="10">
+        <v>2288260736</v>
+      </c>
+      <c r="B135" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A136" s="10">
+        <v>1152156905</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D136" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A137" s="10">
+        <v>1152746895</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D137" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A138" s="10">
+        <v>1153259260</v>
+      </c>
+      <c r="B138" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A139" s="10">
+        <v>1153491590</v>
+      </c>
+      <c r="B139" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A140" s="10">
+        <v>1148755273</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D140" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A141" s="10">
+        <v>1146774821</v>
+      </c>
+      <c r="B141" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A142" s="10">
+        <v>1146165780</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A143" s="10">
+        <v>1147913071</v>
+      </c>
+      <c r="B143" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A144" s="10">
+        <v>1149665844</v>
+      </c>
+      <c r="B144" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A145" s="10">
+        <v>2282375720</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A146" s="10">
+        <v>2415139746</v>
+      </c>
+      <c r="B146" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A147" s="10">
+        <v>1146628035</v>
+      </c>
+      <c r="B147" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A148" s="10">
+        <v>1148873159</v>
+      </c>
+      <c r="B148" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A149" s="10">
+        <v>2275349674</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A150" s="10">
+        <v>1145487730</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A151" s="10">
+        <v>1146809536</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A152" s="10">
+        <v>1164976993</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D152" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A153" s="10">
+        <v>1146821820</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D153" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A154" s="10">
+        <v>1146526668</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A155" s="10">
+        <v>1149762419</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D155" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A156" s="10">
+        <v>1146972862</v>
+      </c>
+      <c r="B156" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D156" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A157" s="10">
+        <v>1148273418</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D157" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A158" s="10">
+        <v>1148688326</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D158" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A159" s="10">
+        <v>1146775844</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D159" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A160" s="10">
+        <v>2344822255</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A161" s="10">
+        <v>1150838223</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D161" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A162" s="10">
+        <v>1146376064</v>
+      </c>
+      <c r="B162" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D162" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A163" s="10">
+        <v>1144789813</v>
+      </c>
+      <c r="B163" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D163" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A164" s="10">
+        <v>1146471519</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D164" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A165" s="10">
+        <v>1145431654</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D165" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A166" s="10">
+        <v>1148252990</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D166" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A167" s="10">
+        <v>1149306225</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D167" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A168" s="10">
+        <v>1151264437</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D168" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A169" s="10">
+        <v>1150158754</v>
+      </c>
+      <c r="B169" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D169" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A170" s="10">
+        <v>1148596271</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D170" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A171" s="10">
+        <v>1147407355</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D171" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A172" s="10">
+        <v>1146987373</v>
+      </c>
+      <c r="B172" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D172" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A173" s="10">
+        <v>1142858388</v>
+      </c>
+      <c r="B173" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D173" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A174" s="10">
+        <v>1148535568</v>
+      </c>
+      <c r="B174" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D174" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A175" s="10">
+        <v>1147255028</v>
+      </c>
+      <c r="B175" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D175" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A176" s="10">
+        <v>1147682353</v>
+      </c>
+      <c r="B176" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D176" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A177" s="10">
+        <v>1146380868</v>
+      </c>
+      <c r="B177" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D177" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A178" s="10">
+        <v>1149234906</v>
+      </c>
+      <c r="B178" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D178" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A179" s="10">
+        <v>1145460539</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D179" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A180" s="10">
+        <v>1146879539</v>
+      </c>
+      <c r="B180" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D180" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A181" s="10">
+        <v>1146061013</v>
+      </c>
+      <c r="B181" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D181" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A182" s="10">
+        <v>1161327497</v>
+      </c>
+      <c r="B182" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D182" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A183" s="10">
+        <v>1146546294</v>
+      </c>
+      <c r="B183" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D183" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A184" s="10">
+        <v>1147314809</v>
+      </c>
+      <c r="B184" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D184" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A185" s="10">
+        <v>1148907890</v>
+      </c>
+      <c r="B185" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D185" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A186" s="10">
+        <v>1148220138</v>
+      </c>
+      <c r="B186" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D186" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A187" s="10">
+        <v>1149587360</v>
+      </c>
+      <c r="B187" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D187" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A188" s="10">
+        <v>1149826164</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D188" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A189" s="10">
+        <v>2337878892</v>
+      </c>
+      <c r="B189" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D189" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A190" s="10">
+        <v>1149812065</v>
+      </c>
+      <c r="B190" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C190" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D190" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A191" s="10">
+        <v>1147392706</v>
+      </c>
+      <c r="B191" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C191" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D191" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A192" s="10">
+        <v>1145344212</v>
+      </c>
+      <c r="B192" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C192" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D192" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A193" s="10">
+        <v>1151073234</v>
+      </c>
+      <c r="B193" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C193" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D193" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A194" s="10">
+        <v>1149661421</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C194" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D194" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A195" s="10">
+        <v>1147116089</v>
+      </c>
+      <c r="B195" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D195" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A196" s="10">
+        <v>1147116014</v>
+      </c>
+      <c r="B196" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D196" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A197" s="10">
+        <v>1147138059</v>
+      </c>
+      <c r="B197" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D197" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A198" s="10">
+        <v>1146518921</v>
+      </c>
+      <c r="B198" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D198" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A199" s="10">
+        <v>1154144388</v>
+      </c>
+      <c r="B199" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D199" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A200" s="10">
+        <v>1147117111</v>
+      </c>
+      <c r="B200" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D200" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A201" s="10">
+        <v>1147073637</v>
+      </c>
+      <c r="B201" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D201" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A202" s="10">
+        <v>1149366534</v>
+      </c>
+      <c r="B202" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D202" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A203" s="10">
+        <v>1151122668</v>
+      </c>
+      <c r="B203" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D203" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A204" s="10">
+        <v>1147318826</v>
+      </c>
+      <c r="B204" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D204" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A205" s="10">
+        <v>2282275516</v>
+      </c>
+      <c r="B205" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D205" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A206" s="10">
+        <v>1148331737</v>
+      </c>
+      <c r="B206" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D206" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A207" s="10">
+        <v>1148003252</v>
+      </c>
+      <c r="B207" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D207" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A208" s="10">
+        <v>1146792161</v>
+      </c>
+      <c r="B208" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D208" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A209" s="10">
+        <v>1148196452</v>
+      </c>
+      <c r="B209" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D209" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A210" s="10">
+        <v>1146902935</v>
+      </c>
+      <c r="B210" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D210" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A211" s="10">
+        <v>1145718209</v>
+      </c>
+      <c r="B211" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A212" s="10">
+        <v>1148921412</v>
+      </c>
+      <c r="B212" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D212" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A213" s="10">
+        <v>1150070421</v>
+      </c>
+      <c r="B213" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D213" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A214" s="10">
+        <v>1169254040</v>
+      </c>
+      <c r="B214" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D214" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A215" s="10">
+        <v>1145733752</v>
+      </c>
+      <c r="B215" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D215" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A216" s="10">
+        <v>1146851652</v>
+      </c>
+      <c r="B216" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D216" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A217" s="10">
+        <v>1146339948</v>
+      </c>
+      <c r="B217" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D217" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A218" s="10">
+        <v>1156163931</v>
+      </c>
+      <c r="B218" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D218" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A219" s="10">
+        <v>1148066275</v>
+      </c>
+      <c r="B219" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D219" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A220" s="10">
+        <v>1148850710</v>
+      </c>
+      <c r="B220" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D220" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A221" s="10">
+        <v>1146399652</v>
+      </c>
+      <c r="B221" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D221" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A222" s="10">
+        <v>1148398181</v>
+      </c>
+      <c r="B222" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D222" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A223" s="10">
+        <v>1145648166</v>
+      </c>
+      <c r="B223" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D223" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A224" s="10">
+        <v>1147594236</v>
+      </c>
+      <c r="B224" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D224" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A225" s="10">
+        <v>1146766389</v>
+      </c>
+      <c r="B225" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D225" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A226" s="10">
+        <v>1148766015</v>
+      </c>
+      <c r="B226" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D226" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A227" s="10">
+        <v>1161794449</v>
+      </c>
+      <c r="B227" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D227" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A228" s="10">
+        <v>1149400937</v>
+      </c>
+      <c r="B228" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D228" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A229" s="10">
+        <v>1148097148</v>
+      </c>
+      <c r="B229" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D229" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A230" s="10">
+        <v>1149512558</v>
+      </c>
+      <c r="B230" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D230" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A231" s="10">
+        <v>1148636135</v>
+      </c>
+      <c r="B231" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D231" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A232" s="10">
+        <v>1148833708</v>
+      </c>
+      <c r="B232" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A233" s="10">
+        <v>1145244214</v>
+      </c>
+      <c r="B233" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D233" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A234" s="10">
+        <v>1149415935</v>
+      </c>
+      <c r="B234" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D234" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A235" s="10">
+        <v>2282843446</v>
+      </c>
+      <c r="B235" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A236" s="10">
+        <v>1147952509</v>
+      </c>
+      <c r="B236" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D236" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A237" s="10">
+        <v>1149342303</v>
+      </c>
+      <c r="B237" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D237" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A238" s="10">
+        <v>1147346579</v>
+      </c>
+      <c r="B238" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D238" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A239" s="10">
+        <v>1146982663</v>
+      </c>
+      <c r="B239" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D239" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A240" s="10">
+        <v>1148895673</v>
+      </c>
+      <c r="B240" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D240" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A241" s="6">
+        <v>1147803256</v>
+      </c>
+      <c r="B241" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D241" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A242" s="10">
+        <v>1147817827</v>
+      </c>
+      <c r="B242" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D242" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A243" s="10">
+        <v>2317822274</v>
+      </c>
+      <c r="B243" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D243" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A244" s="10">
+        <v>2368543738</v>
+      </c>
+      <c r="B244" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C244" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D244" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A245" s="10">
+        <v>1147244998</v>
+      </c>
+      <c r="B245" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D245" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A246" s="10">
+        <v>1147138414</v>
+      </c>
+      <c r="B246" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D246" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A247" s="10">
+        <v>1147800385</v>
+      </c>
+      <c r="B247" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D247" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A248" s="10">
+        <v>1145124374</v>
+      </c>
+      <c r="B248" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D248" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A249" s="10">
+        <v>1146362445</v>
+      </c>
+      <c r="B249" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D249" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A250" s="10">
+        <v>1149064972</v>
+      </c>
+      <c r="B250" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C250" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D250" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A251" s="10">
+        <v>1146726300</v>
+      </c>
+      <c r="B251" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D251" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A252" s="10">
+        <v>1149452821</v>
+      </c>
+      <c r="B252" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D252" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A253" s="10">
+        <v>1146907470</v>
+      </c>
+      <c r="B253" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D253" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A254" s="10">
+        <v>1145545081</v>
+      </c>
+      <c r="B254" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C254" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D254" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A255" s="10">
+        <v>1149931006</v>
+      </c>
+      <c r="B255" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D255" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A256" s="10">
+        <v>2277240962</v>
+      </c>
+      <c r="B256" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D256" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A257" s="10">
+        <v>1145922330</v>
+      </c>
+      <c r="B257" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D257" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A258" s="10">
+        <v>1168345146</v>
+      </c>
+      <c r="B258" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D258" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A259" s="10">
+        <v>2395502558</v>
+      </c>
+      <c r="B259" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C259" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D259" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A260" s="10">
+        <v>1146162415</v>
+      </c>
+      <c r="B260" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D260" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A261" s="10">
+        <v>1152946875</v>
+      </c>
+      <c r="B261" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D261" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A262" s="10">
+        <v>1150772208</v>
+      </c>
+      <c r="B262" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D262" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A263" s="10">
+        <v>1148980897</v>
+      </c>
+      <c r="B263" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C263" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D263" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A264" s="10">
+        <v>1146607773</v>
+      </c>
+      <c r="B264" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D264" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A265" s="10">
+        <v>1146979255</v>
+      </c>
+      <c r="B265" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D265" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A266" s="10">
+        <v>1149811893</v>
+      </c>
+      <c r="B266" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D266" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A267" s="22">
+        <v>1149339077</v>
+      </c>
+      <c r="B267" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="C267" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D267" s="25">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>1234567890</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>966500000000</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1234567891</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
-        <v>966500000001</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+    </row>
+    <row r="268" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A268" s="22">
+        <v>1149508598</v>
+      </c>
+      <c r="B268" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C268" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D268" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A269" s="22">
+        <v>1147789356</v>
+      </c>
+      <c r="B269" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C269" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D269" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A270" s="22">
+        <v>1146611726</v>
+      </c>
+      <c r="B270" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C270" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D270" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A271" s="22">
+        <v>1147262016</v>
+      </c>
+      <c r="B271" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="C271" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D271" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A272" s="22">
+        <v>1147494130</v>
+      </c>
+      <c r="B272" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="C272" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D272" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A273" s="22">
+        <v>1148272907</v>
+      </c>
+      <c r="B273" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="C273" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D273" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A274" s="22">
+        <v>1149254607</v>
+      </c>
+      <c r="B274" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="C274" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D274" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A275" s="22">
+        <v>1149049734</v>
+      </c>
+      <c r="B275" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C275" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D275" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A276" s="22">
+        <v>1147396244</v>
+      </c>
+      <c r="B276" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C276" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D276" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A277" s="22">
+        <v>1146310931</v>
+      </c>
+      <c r="B277" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="C277" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D277" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A278" s="22">
+        <v>1145927230</v>
+      </c>
+      <c r="B278" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="C278" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D278" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A279" s="22">
+        <v>1148274754</v>
+      </c>
+      <c r="B279" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C279" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D279" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A280" s="22">
+        <v>1147544322</v>
+      </c>
+      <c r="B280" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C280" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D280" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A281" s="22">
+        <v>1146374598</v>
+      </c>
+      <c r="B281" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="C281" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D281" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A282" s="22">
+        <v>1150177127</v>
+      </c>
+      <c r="B282" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="C282" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D282" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A283" s="22">
+        <v>1147539728</v>
+      </c>
+      <c r="B283" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="C283" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D283" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A284" s="22">
+        <v>1147293839</v>
+      </c>
+      <c r="B284" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="C284" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D284" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A285" s="22">
+        <v>1148251356</v>
+      </c>
+      <c r="B285" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="C285" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D285" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A286" s="22">
+        <v>1147637472</v>
+      </c>
+      <c r="B286" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C286" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D286" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A287" s="22">
+        <v>1149530295</v>
+      </c>
+      <c r="B287" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="C287" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D287" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A288" s="22">
+        <v>1148778382</v>
+      </c>
+      <c r="B288" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="C288" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D288" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A289" s="22">
+        <v>1147236846</v>
+      </c>
+      <c r="B289" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="C289" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D289" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A290" s="22">
+        <v>2389352689</v>
+      </c>
+      <c r="B290" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C290" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D290" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A291" s="22">
+        <v>2319640955</v>
+      </c>
+      <c r="B291" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="C291" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D291" s="25">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA77534-E2F3-4388-8334-2ECE907ABA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6B45F7-936D-4B26-B4BA-177B01E72F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1045,7 +1045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1063,10 +1063,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
@@ -1076,10 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1102,10 +1094,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
@@ -1126,9 +1114,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
@@ -1144,6 +1129,25 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -2362,7 +2366,7 @@
   <dimension ref="A1:F291"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="28" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.7265625" style="5" bestFit="1" customWidth="1"/>
@@ -2371,7 +2375,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2391,16 +2395,16 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="6">
+      <c r="A2" s="24">
         <v>1150436838</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9">
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8">
         <v>1</v>
       </c>
       <c r="E2" s="4">
@@ -2409,16 +2413,16 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="10">
+      <c r="A3" s="25">
         <v>1152217368</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13">
+      <c r="C3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11">
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -2427,4034 +2431,4034 @@
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="10">
+      <c r="A4" s="25">
         <v>1152502371</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A5" s="10">
+      <c r="A5" s="25">
         <v>1152327969</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
+      <c r="C5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="10">
+      <c r="A6" s="25">
         <v>2302448127</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
+      <c r="C6" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A7" s="10">
+      <c r="A7" s="25">
         <v>1153472889</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
+      <c r="C7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A8" s="10">
+      <c r="A8" s="25">
         <v>1152518682</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
+      <c r="C8" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A9" s="10">
+      <c r="A9" s="25">
         <v>1158331023</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="C9" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="10">
+      <c r="A10" s="25">
         <v>1157900240</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
+      <c r="C10" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="10">
+      <c r="A11" s="25">
         <v>1150731048</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A12" s="10">
+      <c r="A12" s="25">
         <v>2293198442</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A13" s="10">
+      <c r="A13" s="25">
         <v>1174946861</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A14" s="10">
+      <c r="A14" s="25">
         <v>1152820641</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="C14" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A15" s="10">
+      <c r="A15" s="25">
         <v>1149366963</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="10">
+      <c r="A16" s="25">
         <v>1152734123</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="10">
+      <c r="A17" s="25">
         <v>1152480891</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="C17" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A18" s="10">
+      <c r="A18" s="25">
         <v>1153507684</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="10">
+      <c r="A19" s="25">
         <v>1150008413</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A20" s="10">
+      <c r="A20" s="25">
         <v>1152989354</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
+      <c r="C20" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A21" s="10">
+      <c r="A21" s="25">
         <v>1152061618</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="10">
+      <c r="A22" s="25">
         <v>1149206417</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
+      <c r="C22" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A23" s="10">
+      <c r="A23" s="25">
         <v>1151880513</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="C23" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A24" s="10">
+      <c r="A24" s="25">
         <v>2290421144</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
+      <c r="C24" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A25" s="10">
+      <c r="A25" s="25">
         <v>1160061816</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="C25" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A26" s="16">
+      <c r="A26" s="26">
         <v>1152890750</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="C26" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A27" s="10">
+      <c r="A27" s="25">
         <v>1151773627</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="C27" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A28" s="10">
+      <c r="A28" s="25">
         <v>1152536601</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A29" s="10">
+      <c r="A29" s="25">
         <v>1150018610</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
+      <c r="C29" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A30" s="10">
+      <c r="A30" s="25">
         <v>1146587298</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
+      <c r="C30" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A31" s="10">
+      <c r="A31" s="25">
         <v>1150743167</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
+      <c r="C31" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A32" s="10">
+      <c r="A32" s="25">
         <v>1151146907</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="C32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A33" s="10">
+      <c r="A33" s="25">
         <v>2443189093</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33" s="13">
+      <c r="C33" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A34" s="10">
+      <c r="A34" s="25">
         <v>1151434659</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="13">
+      <c r="C34" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A35" s="10">
+      <c r="A35" s="25">
         <v>1152565972</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="C35" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A36" s="10">
+      <c r="A36" s="25">
         <v>1154025124</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="C36" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A37" s="10">
+      <c r="A37" s="25">
         <v>1154153991</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="C37" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A38" s="10">
+      <c r="A38" s="25">
         <v>1149486605</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="C38" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A39" s="10">
+      <c r="A39" s="25">
         <v>1152472815</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="13">
+      <c r="C39" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A40" s="10">
+      <c r="A40" s="25">
         <v>1150396164</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="13">
+      <c r="C40" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A41" s="10">
+      <c r="A41" s="25">
         <v>1150491064</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="13">
+      <c r="C41" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A42" s="10">
+      <c r="A42" s="25">
         <v>1152786958</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="13">
+      <c r="C42" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A43" s="10">
+      <c r="A43" s="25">
         <v>1149922534</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43" s="13">
+      <c r="C43" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A44" s="10">
+      <c r="A44" s="25">
         <v>2269053001</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="13">
+      <c r="C44" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A45" s="10">
+      <c r="A45" s="25">
         <v>1157238989</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="13">
+      <c r="C45" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A46" s="10">
+      <c r="A46" s="25">
         <v>1153155559</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="13">
+      <c r="C46" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A47" s="10">
+      <c r="A47" s="25">
         <v>1149465245</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="C47" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A48" s="10">
+      <c r="A48" s="25">
         <v>1155938150</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="13">
+      <c r="C48" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="10">
+      <c r="A49" s="25">
         <v>1149696633</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="13">
+      <c r="C49" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="10">
+      <c r="A50" s="25">
         <v>1155454240</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13">
+      <c r="C50" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A51" s="10">
+      <c r="A51" s="25">
         <v>1150039038</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="13">
+      <c r="C51" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A52" s="10">
+      <c r="A52" s="25">
         <v>1152218085</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="13">
+      <c r="C52" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="10">
+      <c r="A53" s="25">
         <v>1147013252</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="13">
+      <c r="C53" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A54" s="10">
+      <c r="A54" s="25">
         <v>1154169450</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="13">
+      <c r="C54" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="10">
+      <c r="A55" s="25">
         <v>1151233614</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="13">
+      <c r="C55" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="10">
+      <c r="A56" s="25">
         <v>1151650809</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="13">
+      <c r="C56" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="10">
+      <c r="A57" s="25">
         <v>1151119201</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="13">
+      <c r="C57" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="10">
+      <c r="A58" s="25">
         <v>1152878417</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="13">
+      <c r="C58" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="10">
+      <c r="A59" s="25">
         <v>1152574958</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="13">
+      <c r="C59" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A60" s="10">
+      <c r="A60" s="25">
         <v>1152986681</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C60" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A61" s="10">
+      <c r="A61" s="25">
         <v>1151154455</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="13">
+      <c r="C61" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A62" s="10">
+      <c r="A62" s="25">
         <v>1159289287</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="13">
+      <c r="C62" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A63" s="10">
+      <c r="A63" s="25">
         <v>1153334618</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="13">
+      <c r="C63" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A64" s="10">
+      <c r="A64" s="25">
         <v>1152212658</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="13">
+      <c r="C64" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A65" s="10">
+      <c r="A65" s="25">
         <v>1152410336</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="13">
+      <c r="C65" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A66" s="10">
+      <c r="A66" s="25">
         <v>1154207904</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="13">
+      <c r="C66" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A67" s="10">
+      <c r="A67" s="25">
         <v>1168345245</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" s="13">
+      <c r="C67" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A68" s="10">
+      <c r="A68" s="25">
         <v>1149893040</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="13">
+      <c r="C68" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A69" s="10">
+      <c r="A69" s="25">
         <v>1151849807</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" s="13">
+      <c r="C69" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A70" s="10">
+      <c r="A70" s="25">
         <v>1152284103</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="13">
+      <c r="C70" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A71" s="10">
+      <c r="A71" s="25">
         <v>1167082591</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="13">
+      <c r="C71" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A72" s="10">
+      <c r="A72" s="25">
         <v>1153479645</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" s="13">
+      <c r="C72" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A73" s="10">
+      <c r="A73" s="25">
         <v>1155524893</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" s="13">
+      <c r="C73" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A74" s="10">
+      <c r="A74" s="25">
         <v>1150599171</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D74" s="13">
+      <c r="C74" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A75" s="10">
+      <c r="A75" s="25">
         <v>1154873481</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D75" s="13">
+      <c r="C75" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A76" s="10">
+      <c r="A76" s="25">
         <v>1152884167</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76" s="13">
+      <c r="C76" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A77" s="10">
+      <c r="A77" s="25">
         <v>1152128029</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77" s="13">
+      <c r="C77" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A78" s="10">
+      <c r="A78" s="25">
         <v>1151910013</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D78" s="13">
+      <c r="C78" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A79" s="10">
+      <c r="A79" s="25">
         <v>1154287575</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79" s="13">
+      <c r="C79" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A80" s="10">
+      <c r="A80" s="25">
         <v>1152571822</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C80" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="13">
+      <c r="C80" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A81" s="10">
+      <c r="A81" s="25">
         <v>1150680112</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C81" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D81" s="13">
+      <c r="C81" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A82" s="10">
+      <c r="A82" s="25">
         <v>1150690798</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D82" s="13">
+      <c r="C82" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A83" s="10">
+      <c r="A83" s="25">
         <v>1151961511</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D83" s="13">
+      <c r="C83" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A84" s="10">
+      <c r="A84" s="25">
         <v>1149761460</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="13">
+      <c r="C84" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A85" s="10">
+      <c r="A85" s="25">
         <v>2297211076</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C85" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="13">
+      <c r="C85" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A86" s="10">
+      <c r="A86" s="25">
         <v>1153216211</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D86" s="13">
+      <c r="C86" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A87" s="10">
+      <c r="A87" s="25">
         <v>1152536460</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D87" s="13">
+      <c r="C87" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A88" s="10">
+      <c r="A88" s="25">
         <v>1152152763</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D88" s="13">
+      <c r="C88" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A89" s="10">
+      <c r="A89" s="25">
         <v>1156092080</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D89" s="13">
+      <c r="C89" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A90" s="10">
+      <c r="A90" s="25">
         <v>2510170026</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90" s="13">
+      <c r="C90" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A91" s="10">
+      <c r="A91" s="25">
         <v>1151404256</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D91" s="13">
+      <c r="C91" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="10">
+      <c r="A92" s="25">
         <v>1152224984</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D92" s="13">
+      <c r="C92" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D92" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A93" s="10">
+      <c r="A93" s="25">
         <v>1150781068</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93" s="13">
+      <c r="C93" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A94" s="10">
+      <c r="A94" s="25">
         <v>1150218970</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C94" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D94" s="13">
+      <c r="C94" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A95" s="10">
+      <c r="A95" s="25">
         <v>1153072044</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C95" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="13">
+      <c r="C95" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="10">
+      <c r="A96" s="25">
         <v>1153072069</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C96" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D96" s="13">
+      <c r="C96" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D96" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="10">
+      <c r="A97" s="25">
         <v>1149401059</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C97" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D97" s="13">
+      <c r="C97" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A98" s="10">
+      <c r="A98" s="25">
         <v>1153495591</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C98" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98" s="13">
+      <c r="C98" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A99" s="10">
+      <c r="A99" s="25">
         <v>1150973210</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C99" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D99" s="13">
+      <c r="C99" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A100" s="10">
+      <c r="A100" s="25">
         <v>1151704598</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="13">
+      <c r="C100" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A101" s="10">
+      <c r="A101" s="25">
         <v>1151845870</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C101" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D101" s="13">
+      <c r="C101" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A102" s="10">
+      <c r="A102" s="25">
         <v>1149888925</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C102" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D102" s="13">
+      <c r="C102" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A103" s="10">
+      <c r="A103" s="25">
         <v>1153380116</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D103" s="13">
+      <c r="C103" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A104" s="10">
+      <c r="A104" s="25">
         <v>1152305007</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C104" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D104" s="13">
+      <c r="C104" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A105" s="10">
+      <c r="A105" s="25">
         <v>1153607922</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D105" s="13">
+      <c r="C105" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A106" s="10">
+      <c r="A106" s="25">
         <v>1152853493</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C106" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D106" s="13">
+      <c r="C106" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A107" s="10">
+      <c r="A107" s="25">
         <v>1153534167</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D107" s="13">
+      <c r="C107" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D107" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A108" s="10">
+      <c r="A108" s="25">
         <v>1149855445</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C108" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D108" s="13">
+      <c r="C108" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A109" s="10">
+      <c r="A109" s="25">
         <v>1153291388</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C109" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D109" s="13">
+      <c r="C109" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D109" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A110" s="10">
+      <c r="A110" s="25">
         <v>1151814371</v>
       </c>
-      <c r="B110" s="15" t="s">
+      <c r="B110" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C110" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110" s="13">
+      <c r="C110" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A111" s="10">
+      <c r="A111" s="25">
         <v>1158612646</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C111" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D111" s="13">
+      <c r="C111" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D111" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A112" s="10">
+      <c r="A112" s="25">
         <v>1151003728</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C112" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D112" s="13">
+      <c r="C112" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D112" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A113" s="10">
+      <c r="A113" s="25">
         <v>1174052116</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D113" s="13">
+      <c r="C113" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A114" s="10">
+      <c r="A114" s="25">
         <v>1153013931</v>
       </c>
-      <c r="B114" s="15" t="s">
+      <c r="B114" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C114" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D114" s="13">
+      <c r="C114" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D114" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A115" s="10">
+      <c r="A115" s="25">
         <v>1150396081</v>
       </c>
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C115" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="13">
+      <c r="C115" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A116" s="10">
+      <c r="A116" s="25">
         <v>1150690699</v>
       </c>
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C116" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D116" s="13">
+      <c r="C116" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A117" s="10">
+      <c r="A117" s="25">
         <v>1152698252</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C117" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D117" s="13">
+      <c r="C117" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A118" s="10">
+      <c r="A118" s="25">
         <v>1153384795</v>
       </c>
-      <c r="B118" s="15" t="s">
+      <c r="B118" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D118" s="13">
+      <c r="C118" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A119" s="10">
+      <c r="A119" s="25">
         <v>1150304325</v>
       </c>
-      <c r="B119" s="15" t="s">
+      <c r="B119" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C119" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D119" s="13">
+      <c r="C119" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A120" s="10">
+      <c r="A120" s="25">
         <v>1152915870</v>
       </c>
-      <c r="B120" s="15" t="s">
+      <c r="B120" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C120" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="13">
+      <c r="C120" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A121" s="10">
+      <c r="A121" s="25">
         <v>1152367700</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C121" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D121" s="13">
+      <c r="C121" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A122" s="10">
+      <c r="A122" s="25">
         <v>1152775639</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C122" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D122" s="13">
+      <c r="C122" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D122" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A123" s="10">
+      <c r="A123" s="25">
         <v>1149182303</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C123" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D123" s="13">
+      <c r="C123" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D123" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A124" s="10">
+      <c r="A124" s="25">
         <v>1149628024</v>
       </c>
-      <c r="B124" s="15" t="s">
+      <c r="B124" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D124" s="13">
+      <c r="C124" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A125" s="10">
+      <c r="A125" s="25">
         <v>1152522833</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125" s="13">
+      <c r="C125" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A126" s="10">
+      <c r="A126" s="25">
         <v>2382166136</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C126" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D126" s="13">
+      <c r="C126" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D126" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A127" s="10">
+      <c r="A127" s="25">
         <v>1151669510</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D127" s="13">
+      <c r="C127" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D127" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A128" s="10">
+      <c r="A128" s="25">
         <v>1155012543</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D128" s="13">
+      <c r="C128" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D128" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A129" s="10">
+      <c r="A129" s="25">
         <v>1150763322</v>
       </c>
-      <c r="B129" s="15" t="s">
+      <c r="B129" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D129" s="13">
+      <c r="C129" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A130" s="10">
+      <c r="A130" s="25">
         <v>1150527107</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130" s="13">
+      <c r="C130" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A131" s="10">
+      <c r="A131" s="25">
         <v>1171859398</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D131" s="13">
+      <c r="C131" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D131" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A132" s="10">
+      <c r="A132" s="25">
         <v>1151485529</v>
       </c>
-      <c r="B132" s="15" t="s">
+      <c r="B132" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D132" s="13">
+      <c r="C132" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A133" s="10">
+      <c r="A133" s="25">
         <v>1153562317</v>
       </c>
-      <c r="B133" s="15" t="s">
+      <c r="B133" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C133" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D133" s="13">
+      <c r="C133" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D133" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A134" s="10">
+      <c r="A134" s="25">
         <v>1153018385</v>
       </c>
-      <c r="B134" s="15" t="s">
+      <c r="B134" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D134" s="13">
+      <c r="C134" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A135" s="10">
+      <c r="A135" s="25">
         <v>2288260736</v>
       </c>
-      <c r="B135" s="15" t="s">
+      <c r="B135" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135" s="13">
+      <c r="C135" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A136" s="10">
+      <c r="A136" s="25">
         <v>1152156905</v>
       </c>
-      <c r="B136" s="15" t="s">
+      <c r="B136" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C136" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D136" s="13">
+      <c r="C136" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D136" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A137" s="10">
+      <c r="A137" s="25">
         <v>1152746895</v>
       </c>
-      <c r="B137" s="15" t="s">
+      <c r="B137" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C137" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D137" s="13">
+      <c r="C137" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D137" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A138" s="10">
+      <c r="A138" s="25">
         <v>1153259260</v>
       </c>
-      <c r="B138" s="15" t="s">
+      <c r="B138" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C138" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D138" s="13">
+      <c r="C138" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A139" s="10">
+      <c r="A139" s="25">
         <v>1153491590</v>
       </c>
-      <c r="B139" s="15" t="s">
+      <c r="B139" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C139" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139" s="13">
+      <c r="C139" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A140" s="10">
+      <c r="A140" s="25">
         <v>1148755273</v>
       </c>
-      <c r="B140" s="15" t="s">
+      <c r="B140" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C140" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D140" s="13">
+      <c r="C140" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D140" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A141" s="10">
+      <c r="A141" s="25">
         <v>1146774821</v>
       </c>
-      <c r="B141" s="15" t="s">
+      <c r="B141" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C141" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D141" s="13">
+      <c r="C141" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A142" s="10">
+      <c r="A142" s="25">
         <v>1146165780</v>
       </c>
-      <c r="B142" s="15" t="s">
+      <c r="B142" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C142" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D142" s="13">
+      <c r="C142" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A143" s="10">
+      <c r="A143" s="25">
         <v>1147913071</v>
       </c>
-      <c r="B143" s="15" t="s">
+      <c r="B143" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C143" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D143" s="13">
+      <c r="C143" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A144" s="10">
+      <c r="A144" s="25">
         <v>1149665844</v>
       </c>
-      <c r="B144" s="15" t="s">
+      <c r="B144" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C144" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D144" s="13">
+      <c r="C144" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A145" s="10">
+      <c r="A145" s="25">
         <v>2282375720</v>
       </c>
-      <c r="B145" s="15" t="s">
+      <c r="B145" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C145" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D145" s="13">
+      <c r="C145" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A146" s="10">
+      <c r="A146" s="25">
         <v>2415139746</v>
       </c>
-      <c r="B146" s="15" t="s">
+      <c r="B146" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C146" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D146" s="13">
+      <c r="C146" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A147" s="10">
+      <c r="A147" s="25">
         <v>1146628035</v>
       </c>
-      <c r="B147" s="15" t="s">
+      <c r="B147" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C147" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D147" s="13">
+      <c r="C147" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A148" s="10">
+      <c r="A148" s="25">
         <v>1148873159</v>
       </c>
-      <c r="B148" s="15" t="s">
+      <c r="B148" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C148" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D148" s="13">
+      <c r="C148" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A149" s="10">
+      <c r="A149" s="25">
         <v>2275349674</v>
       </c>
-      <c r="B149" s="15" t="s">
+      <c r="B149" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C149" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D149" s="13">
+      <c r="C149" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A150" s="10">
+      <c r="A150" s="25">
         <v>1145487730</v>
       </c>
-      <c r="B150" s="15" t="s">
+      <c r="B150" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C150" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D150" s="13">
+      <c r="C150" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A151" s="10">
+      <c r="A151" s="25">
         <v>1146809536</v>
       </c>
-      <c r="B151" s="15" t="s">
+      <c r="B151" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C151" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D151" s="13">
+      <c r="C151" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A152" s="10">
+      <c r="A152" s="25">
         <v>1164976993</v>
       </c>
-      <c r="B152" s="15" t="s">
+      <c r="B152" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C152" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D152" s="13">
+      <c r="C152" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D152" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A153" s="10">
+      <c r="A153" s="25">
         <v>1146821820</v>
       </c>
-      <c r="B153" s="15" t="s">
+      <c r="B153" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C153" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D153" s="13">
+      <c r="C153" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D153" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A154" s="10">
+      <c r="A154" s="25">
         <v>1146526668</v>
       </c>
-      <c r="B154" s="15" t="s">
+      <c r="B154" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C154" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D154" s="13">
+      <c r="C154" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A155" s="10">
+      <c r="A155" s="25">
         <v>1149762419</v>
       </c>
-      <c r="B155" s="15" t="s">
+      <c r="B155" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C155" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D155" s="13">
+      <c r="C155" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D155" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A156" s="10">
+      <c r="A156" s="25">
         <v>1146972862</v>
       </c>
-      <c r="B156" s="15" t="s">
+      <c r="B156" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C156" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D156" s="13">
+      <c r="C156" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D156" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A157" s="10">
+      <c r="A157" s="25">
         <v>1148273418</v>
       </c>
-      <c r="B157" s="15" t="s">
+      <c r="B157" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C157" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D157" s="13">
+      <c r="C157" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D157" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A158" s="10">
+      <c r="A158" s="25">
         <v>1148688326</v>
       </c>
-      <c r="B158" s="15" t="s">
+      <c r="B158" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C158" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D158" s="13">
+      <c r="C158" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D158" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A159" s="10">
+      <c r="A159" s="25">
         <v>1146775844</v>
       </c>
-      <c r="B159" s="15" t="s">
+      <c r="B159" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C159" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D159" s="13">
+      <c r="C159" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D159" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A160" s="10">
+      <c r="A160" s="25">
         <v>2344822255</v>
       </c>
-      <c r="B160" s="15" t="s">
+      <c r="B160" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C160" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D160" s="13">
+      <c r="C160" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A161" s="10">
+      <c r="A161" s="25">
         <v>1150838223</v>
       </c>
-      <c r="B161" s="15" t="s">
+      <c r="B161" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C161" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D161" s="13">
+      <c r="C161" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D161" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A162" s="10">
+      <c r="A162" s="25">
         <v>1146376064</v>
       </c>
-      <c r="B162" s="15" t="s">
+      <c r="B162" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D162" s="13">
+      <c r="C162" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D162" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A163" s="10">
+      <c r="A163" s="25">
         <v>1144789813</v>
       </c>
-      <c r="B163" s="15" t="s">
+      <c r="B163" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C163" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D163" s="13">
+      <c r="C163" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D163" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A164" s="10">
+      <c r="A164" s="25">
         <v>1146471519</v>
       </c>
-      <c r="B164" s="15" t="s">
+      <c r="B164" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C164" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D164" s="13">
+      <c r="C164" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D164" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A165" s="10">
+      <c r="A165" s="25">
         <v>1145431654</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D165" s="13">
+      <c r="C165" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D165" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A166" s="10">
+      <c r="A166" s="25">
         <v>1148252990</v>
       </c>
-      <c r="B166" s="15" t="s">
+      <c r="B166" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C166" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D166" s="13">
+      <c r="C166" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D166" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="10">
+      <c r="A167" s="25">
         <v>1149306225</v>
       </c>
-      <c r="B167" s="15" t="s">
+      <c r="B167" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C167" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D167" s="13">
+      <c r="C167" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D167" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A168" s="10">
+      <c r="A168" s="25">
         <v>1151264437</v>
       </c>
-      <c r="B168" s="15" t="s">
+      <c r="B168" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D168" s="13">
+      <c r="C168" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D168" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A169" s="10">
+      <c r="A169" s="25">
         <v>1150158754</v>
       </c>
-      <c r="B169" s="15" t="s">
+      <c r="B169" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C169" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D169" s="13">
+      <c r="C169" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D169" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A170" s="10">
+      <c r="A170" s="25">
         <v>1148596271</v>
       </c>
-      <c r="B170" s="15" t="s">
+      <c r="B170" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C170" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D170" s="13">
+      <c r="C170" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D170" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A171" s="10">
+      <c r="A171" s="25">
         <v>1147407355</v>
       </c>
-      <c r="B171" s="15" t="s">
+      <c r="B171" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C171" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D171" s="13">
+      <c r="C171" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D171" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A172" s="10">
+      <c r="A172" s="25">
         <v>1146987373</v>
       </c>
-      <c r="B172" s="15" t="s">
+      <c r="B172" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C172" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D172" s="13">
+      <c r="C172" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D172" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A173" s="10">
+      <c r="A173" s="25">
         <v>1142858388</v>
       </c>
-      <c r="B173" s="15" t="s">
+      <c r="B173" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C173" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D173" s="13">
+      <c r="C173" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D173" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A174" s="10">
+      <c r="A174" s="25">
         <v>1148535568</v>
       </c>
-      <c r="B174" s="15" t="s">
+      <c r="B174" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C174" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D174" s="13">
+      <c r="C174" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D174" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A175" s="10">
+      <c r="A175" s="25">
         <v>1147255028</v>
       </c>
-      <c r="B175" s="15" t="s">
+      <c r="B175" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D175" s="13">
+      <c r="C175" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D175" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A176" s="10">
+      <c r="A176" s="25">
         <v>1147682353</v>
       </c>
-      <c r="B176" s="15" t="s">
+      <c r="B176" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C176" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D176" s="13">
+      <c r="C176" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D176" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A177" s="10">
+      <c r="A177" s="25">
         <v>1146380868</v>
       </c>
-      <c r="B177" s="15" t="s">
+      <c r="B177" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C177" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D177" s="13">
+      <c r="C177" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D177" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A178" s="10">
+      <c r="A178" s="25">
         <v>1149234906</v>
       </c>
-      <c r="B178" s="15" t="s">
+      <c r="B178" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D178" s="13">
+      <c r="C178" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D178" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A179" s="10">
+      <c r="A179" s="25">
         <v>1145460539</v>
       </c>
-      <c r="B179" s="17" t="s">
+      <c r="B179" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="C179" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D179" s="13">
+      <c r="C179" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D179" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A180" s="10">
+      <c r="A180" s="25">
         <v>1146879539</v>
       </c>
-      <c r="B180" s="15" t="s">
+      <c r="B180" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C180" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D180" s="13">
+      <c r="C180" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D180" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A181" s="10">
+      <c r="A181" s="25">
         <v>1146061013</v>
       </c>
-      <c r="B181" s="15" t="s">
+      <c r="B181" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C181" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D181" s="13">
+      <c r="C181" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D181" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A182" s="10">
+      <c r="A182" s="25">
         <v>1161327497</v>
       </c>
-      <c r="B182" s="15" t="s">
+      <c r="B182" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C182" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D182" s="13">
+      <c r="C182" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D182" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A183" s="10">
+      <c r="A183" s="25">
         <v>1146546294</v>
       </c>
-      <c r="B183" s="15" t="s">
+      <c r="B183" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C183" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D183" s="13">
+      <c r="C183" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D183" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A184" s="10">
+      <c r="A184" s="25">
         <v>1147314809</v>
       </c>
-      <c r="B184" s="15" t="s">
+      <c r="B184" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C184" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D184" s="13">
+      <c r="C184" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D184" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A185" s="10">
+      <c r="A185" s="25">
         <v>1148907890</v>
       </c>
-      <c r="B185" s="15" t="s">
+      <c r="B185" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C185" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D185" s="13">
+      <c r="C185" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D185" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A186" s="10">
+      <c r="A186" s="25">
         <v>1148220138</v>
       </c>
-      <c r="B186" s="15" t="s">
+      <c r="B186" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C186" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D186" s="13">
+      <c r="C186" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D186" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A187" s="10">
+      <c r="A187" s="25">
         <v>1149587360</v>
       </c>
-      <c r="B187" s="15" t="s">
+      <c r="B187" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D187" s="13">
+      <c r="C187" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D187" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A188" s="10">
+      <c r="A188" s="25">
         <v>1149826164</v>
       </c>
-      <c r="B188" s="15" t="s">
+      <c r="B188" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D188" s="13">
+      <c r="C188" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D188" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A189" s="10">
+      <c r="A189" s="25">
         <v>2337878892</v>
       </c>
-      <c r="B189" s="15" t="s">
+      <c r="B189" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D189" s="13">
+      <c r="C189" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D189" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A190" s="10">
+      <c r="A190" s="25">
         <v>1149812065</v>
       </c>
-      <c r="B190" s="18" t="s">
+      <c r="B190" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C190" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D190" s="13">
+      <c r="C190" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D190" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A191" s="10">
+      <c r="A191" s="25">
         <v>1147392706</v>
       </c>
-      <c r="B191" s="15" t="s">
+      <c r="B191" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D191" s="13">
+      <c r="C191" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D191" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A192" s="10">
+      <c r="A192" s="25">
         <v>1145344212</v>
       </c>
-      <c r="B192" s="15" t="s">
+      <c r="B192" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C192" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D192" s="13">
+      <c r="C192" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D192" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A193" s="10">
+      <c r="A193" s="25">
         <v>1151073234</v>
       </c>
-      <c r="B193" s="15" t="s">
+      <c r="B193" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C193" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D193" s="13">
+      <c r="C193" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D193" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A194" s="10">
+      <c r="A194" s="25">
         <v>1149661421</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B194" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C194" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D194" s="13">
+      <c r="C194" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D194" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A195" s="10">
+      <c r="A195" s="25">
         <v>1147116089</v>
       </c>
-      <c r="B195" s="15" t="s">
+      <c r="B195" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C195" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D195" s="13">
+      <c r="C195" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D195" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A196" s="10">
+      <c r="A196" s="25">
         <v>1147116014</v>
       </c>
-      <c r="B196" s="15" t="s">
+      <c r="B196" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C196" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D196" s="13">
+      <c r="C196" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D196" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A197" s="10">
+      <c r="A197" s="25">
         <v>1147138059</v>
       </c>
-      <c r="B197" s="15" t="s">
+      <c r="B197" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C197" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D197" s="13">
+      <c r="C197" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D197" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A198" s="10">
+      <c r="A198" s="25">
         <v>1146518921</v>
       </c>
-      <c r="B198" s="15" t="s">
+      <c r="B198" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C198" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D198" s="13">
+      <c r="C198" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D198" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A199" s="10">
+      <c r="A199" s="25">
         <v>1154144388</v>
       </c>
-      <c r="B199" s="15" t="s">
+      <c r="B199" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D199" s="13">
+      <c r="C199" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D199" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A200" s="10">
+      <c r="A200" s="25">
         <v>1147117111</v>
       </c>
-      <c r="B200" s="14" t="s">
+      <c r="B200" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D200" s="13">
+      <c r="C200" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D200" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A201" s="10">
+      <c r="A201" s="25">
         <v>1147073637</v>
       </c>
-      <c r="B201" s="15" t="s">
+      <c r="B201" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C201" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D201" s="13">
+      <c r="C201" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D201" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A202" s="10">
+      <c r="A202" s="25">
         <v>1149366534</v>
       </c>
-      <c r="B202" s="15" t="s">
+      <c r="B202" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C202" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D202" s="13">
+      <c r="C202" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D202" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A203" s="10">
+      <c r="A203" s="25">
         <v>1151122668</v>
       </c>
-      <c r="B203" s="15" t="s">
+      <c r="B203" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C203" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D203" s="13">
+      <c r="C203" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D203" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A204" s="10">
+      <c r="A204" s="25">
         <v>1147318826</v>
       </c>
-      <c r="B204" s="15" t="s">
+      <c r="B204" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C204" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D204" s="13">
+      <c r="C204" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D204" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A205" s="10">
+      <c r="A205" s="25">
         <v>2282275516</v>
       </c>
-      <c r="B205" s="15" t="s">
+      <c r="B205" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C205" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D205" s="13">
+      <c r="C205" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D205" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A206" s="10">
+      <c r="A206" s="25">
         <v>1148331737</v>
       </c>
-      <c r="B206" s="15" t="s">
+      <c r="B206" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C206" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D206" s="13">
+      <c r="C206" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D206" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A207" s="10">
+      <c r="A207" s="25">
         <v>1148003252</v>
       </c>
-      <c r="B207" s="15" t="s">
+      <c r="B207" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C207" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D207" s="13">
+      <c r="C207" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D207" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A208" s="10">
+      <c r="A208" s="25">
         <v>1146792161</v>
       </c>
-      <c r="B208" s="15" t="s">
+      <c r="B208" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C208" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D208" s="13">
+      <c r="C208" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D208" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A209" s="10">
+      <c r="A209" s="25">
         <v>1148196452</v>
       </c>
-      <c r="B209" s="15" t="s">
+      <c r="B209" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C209" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D209" s="13">
+      <c r="C209" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D209" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A210" s="10">
+      <c r="A210" s="25">
         <v>1146902935</v>
       </c>
-      <c r="B210" s="15" t="s">
+      <c r="B210" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="C210" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D210" s="13">
+      <c r="C210" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D210" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A211" s="10">
+      <c r="A211" s="25">
         <v>1145718209</v>
       </c>
-      <c r="B211" s="15" t="s">
+      <c r="B211" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C211" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D211" s="13">
+      <c r="C211" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A212" s="10">
+      <c r="A212" s="25">
         <v>1148921412</v>
       </c>
-      <c r="B212" s="15" t="s">
+      <c r="B212" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C212" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D212" s="13">
+      <c r="C212" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D212" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A213" s="10">
+      <c r="A213" s="25">
         <v>1150070421</v>
       </c>
-      <c r="B213" s="15" t="s">
+      <c r="B213" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C213" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D213" s="13">
+      <c r="C213" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D213" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A214" s="10">
+      <c r="A214" s="25">
         <v>1169254040</v>
       </c>
-      <c r="B214" s="15" t="s">
+      <c r="B214" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="C214" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D214" s="13">
+      <c r="C214" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D214" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A215" s="10">
+      <c r="A215" s="25">
         <v>1145733752</v>
       </c>
-      <c r="B215" s="15" t="s">
+      <c r="B215" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C215" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D215" s="13">
+      <c r="C215" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D215" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A216" s="10">
+      <c r="A216" s="25">
         <v>1146851652</v>
       </c>
-      <c r="B216" s="15" t="s">
+      <c r="B216" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C216" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D216" s="13">
+      <c r="C216" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D216" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A217" s="10">
+      <c r="A217" s="25">
         <v>1146339948</v>
       </c>
-      <c r="B217" s="15" t="s">
+      <c r="B217" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C217" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D217" s="13">
+      <c r="C217" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D217" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A218" s="10">
+      <c r="A218" s="25">
         <v>1156163931</v>
       </c>
-      <c r="B218" s="15" t="s">
+      <c r="B218" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C218" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D218" s="13">
+      <c r="C218" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D218" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A219" s="10">
+      <c r="A219" s="25">
         <v>1148066275</v>
       </c>
-      <c r="B219" s="15" t="s">
+      <c r="B219" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C219" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D219" s="13">
+      <c r="C219" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D219" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A220" s="10">
+      <c r="A220" s="25">
         <v>1148850710</v>
       </c>
-      <c r="B220" s="15" t="s">
+      <c r="B220" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="C220" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D220" s="13">
+      <c r="C220" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D220" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A221" s="10">
+      <c r="A221" s="25">
         <v>1146399652</v>
       </c>
-      <c r="B221" s="15" t="s">
+      <c r="B221" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C221" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D221" s="13">
+      <c r="C221" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D221" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A222" s="10">
+      <c r="A222" s="25">
         <v>1148398181</v>
       </c>
-      <c r="B222" s="15" t="s">
+      <c r="B222" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C222" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D222" s="13">
+      <c r="C222" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D222" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A223" s="10">
+      <c r="A223" s="25">
         <v>1145648166</v>
       </c>
-      <c r="B223" s="15" t="s">
+      <c r="B223" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C223" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D223" s="13">
+      <c r="C223" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D223" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A224" s="10">
+      <c r="A224" s="25">
         <v>1147594236</v>
       </c>
-      <c r="B224" s="15" t="s">
+      <c r="B224" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C224" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D224" s="13">
+      <c r="C224" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D224" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A225" s="10">
+      <c r="A225" s="25">
         <v>1146766389</v>
       </c>
-      <c r="B225" s="15" t="s">
+      <c r="B225" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C225" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D225" s="13">
+      <c r="C225" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D225" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A226" s="10">
+      <c r="A226" s="25">
         <v>1148766015</v>
       </c>
-      <c r="B226" s="17" t="s">
+      <c r="B226" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C226" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D226" s="13">
+      <c r="C226" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D226" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A227" s="10">
+      <c r="A227" s="25">
         <v>1161794449</v>
       </c>
-      <c r="B227" s="15" t="s">
+      <c r="B227" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C227" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D227" s="13">
+      <c r="C227" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D227" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A228" s="10">
+      <c r="A228" s="25">
         <v>1149400937</v>
       </c>
-      <c r="B228" s="15" t="s">
+      <c r="B228" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C228" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D228" s="13">
+      <c r="C228" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D228" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A229" s="10">
+      <c r="A229" s="25">
         <v>1148097148</v>
       </c>
-      <c r="B229" s="15" t="s">
+      <c r="B229" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C229" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D229" s="13">
+      <c r="C229" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D229" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A230" s="10">
+      <c r="A230" s="25">
         <v>1149512558</v>
       </c>
-      <c r="B230" s="15" t="s">
+      <c r="B230" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C230" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D230" s="13">
+      <c r="C230" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D230" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A231" s="10">
+      <c r="A231" s="25">
         <v>1148636135</v>
       </c>
-      <c r="B231" s="15" t="s">
+      <c r="B231" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C231" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D231" s="13">
+      <c r="C231" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D231" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A232" s="10">
+      <c r="A232" s="25">
         <v>1148833708</v>
       </c>
-      <c r="B232" s="15" t="s">
+      <c r="B232" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="C232" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D232" s="13">
+      <c r="C232" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A233" s="10">
+      <c r="A233" s="25">
         <v>1145244214</v>
       </c>
-      <c r="B233" s="15" t="s">
+      <c r="B233" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C233" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D233" s="13">
+      <c r="C233" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D233" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A234" s="10">
+      <c r="A234" s="25">
         <v>1149415935</v>
       </c>
-      <c r="B234" s="15" t="s">
+      <c r="B234" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="C234" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D234" s="13">
+      <c r="C234" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D234" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A235" s="10">
+      <c r="A235" s="25">
         <v>2282843446</v>
       </c>
-      <c r="B235" s="15" t="s">
+      <c r="B235" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C235" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D235" s="13">
+      <c r="C235" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A236" s="10">
+      <c r="A236" s="25">
         <v>1147952509</v>
       </c>
-      <c r="B236" s="15" t="s">
+      <c r="B236" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="C236" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D236" s="13">
+      <c r="C236" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D236" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A237" s="10">
+      <c r="A237" s="25">
         <v>1149342303</v>
       </c>
-      <c r="B237" s="20" t="s">
+      <c r="B237" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C237" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D237" s="13">
+      <c r="C237" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D237" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A238" s="10">
+      <c r="A238" s="25">
         <v>1147346579</v>
       </c>
-      <c r="B238" s="15" t="s">
+      <c r="B238" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C238" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D238" s="13">
+      <c r="C238" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D238" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A239" s="10">
+      <c r="A239" s="25">
         <v>1146982663</v>
       </c>
-      <c r="B239" s="20" t="s">
+      <c r="B239" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C239" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D239" s="13">
+      <c r="C239" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D239" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A240" s="10">
+      <c r="A240" s="25">
         <v>1148895673</v>
       </c>
-      <c r="B240" s="15" t="s">
+      <c r="B240" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="C240" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D240" s="13">
+      <c r="C240" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D240" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A241" s="6">
+      <c r="A241" s="24">
         <v>1147803256</v>
       </c>
-      <c r="B241" s="21" t="s">
+      <c r="B241" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="C241" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D241" s="9">
+      <c r="C241" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D241" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A242" s="10">
+      <c r="A242" s="25">
         <v>1147817827</v>
       </c>
-      <c r="B242" s="15" t="s">
+      <c r="B242" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C242" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D242" s="13">
+      <c r="C242" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D242" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A243" s="10">
+      <c r="A243" s="25">
         <v>2317822274</v>
       </c>
-      <c r="B243" s="15" t="s">
+      <c r="B243" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C243" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D243" s="13">
+      <c r="C243" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D243" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A244" s="10">
+      <c r="A244" s="25">
         <v>2368543738</v>
       </c>
-      <c r="B244" s="15" t="s">
+      <c r="B244" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="C244" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D244" s="13">
+      <c r="C244" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D244" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A245" s="10">
+      <c r="A245" s="25">
         <v>1147244998</v>
       </c>
-      <c r="B245" s="15" t="s">
+      <c r="B245" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C245" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D245" s="13">
+      <c r="C245" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D245" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A246" s="10">
+      <c r="A246" s="25">
         <v>1147138414</v>
       </c>
-      <c r="B246" s="15" t="s">
+      <c r="B246" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C246" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D246" s="13">
+      <c r="C246" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D246" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A247" s="10">
+      <c r="A247" s="25">
         <v>1147800385</v>
       </c>
-      <c r="B247" s="15" t="s">
+      <c r="B247" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C247" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D247" s="13">
+      <c r="C247" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D247" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A248" s="10">
+      <c r="A248" s="25">
         <v>1145124374</v>
       </c>
-      <c r="B248" s="15" t="s">
+      <c r="B248" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C248" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="13">
+      <c r="C248" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D248" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A249" s="10">
+      <c r="A249" s="25">
         <v>1146362445</v>
       </c>
-      <c r="B249" s="15" t="s">
+      <c r="B249" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C249" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D249" s="13">
+      <c r="C249" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D249" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A250" s="10">
+      <c r="A250" s="25">
         <v>1149064972</v>
       </c>
-      <c r="B250" s="15" t="s">
+      <c r="B250" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C250" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D250" s="13">
+      <c r="C250" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D250" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A251" s="10">
+      <c r="A251" s="25">
         <v>1146726300</v>
       </c>
-      <c r="B251" s="15" t="s">
+      <c r="B251" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C251" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D251" s="13">
+      <c r="C251" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D251" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A252" s="10">
+      <c r="A252" s="25">
         <v>1149452821</v>
       </c>
-      <c r="B252" s="15" t="s">
+      <c r="B252" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C252" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D252" s="13">
+      <c r="C252" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D252" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A253" s="10">
+      <c r="A253" s="25">
         <v>1146907470</v>
       </c>
-      <c r="B253" s="15" t="s">
+      <c r="B253" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C253" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D253" s="13">
+      <c r="C253" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D253" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A254" s="10">
+      <c r="A254" s="25">
         <v>1145545081</v>
       </c>
-      <c r="B254" s="15" t="s">
+      <c r="B254" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C254" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D254" s="13">
+      <c r="C254" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D254" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A255" s="10">
+      <c r="A255" s="25">
         <v>1149931006</v>
       </c>
-      <c r="B255" s="15" t="s">
+      <c r="B255" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="C255" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D255" s="13">
+      <c r="C255" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D255" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A256" s="10">
+      <c r="A256" s="25">
         <v>2277240962</v>
       </c>
-      <c r="B256" s="15" t="s">
+      <c r="B256" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C256" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D256" s="13">
+      <c r="C256" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D256" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A257" s="10">
+      <c r="A257" s="25">
         <v>1145922330</v>
       </c>
-      <c r="B257" s="15" t="s">
+      <c r="B257" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="C257" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D257" s="13">
+      <c r="C257" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D257" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A258" s="10">
+      <c r="A258" s="25">
         <v>1168345146</v>
       </c>
-      <c r="B258" s="15" t="s">
+      <c r="B258" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="C258" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D258" s="13">
+      <c r="C258" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D258" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A259" s="10">
+      <c r="A259" s="25">
         <v>2395502558</v>
       </c>
-      <c r="B259" s="15" t="s">
+      <c r="B259" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="C259" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D259" s="13">
+      <c r="C259" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D259" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A260" s="10">
+      <c r="A260" s="25">
         <v>1146162415</v>
       </c>
-      <c r="B260" s="15" t="s">
+      <c r="B260" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C260" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D260" s="13">
+      <c r="C260" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D260" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A261" s="10">
+      <c r="A261" s="25">
         <v>1152946875</v>
       </c>
-      <c r="B261" s="15" t="s">
+      <c r="B261" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C261" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D261" s="13">
+      <c r="C261" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D261" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A262" s="10">
+      <c r="A262" s="25">
         <v>1150772208</v>
       </c>
-      <c r="B262" s="15" t="s">
+      <c r="B262" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="C262" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D262" s="13">
+      <c r="C262" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D262" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A263" s="10">
+      <c r="A263" s="25">
         <v>1148980897</v>
       </c>
-      <c r="B263" s="15" t="s">
+      <c r="B263" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="C263" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D263" s="13">
+      <c r="C263" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D263" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A264" s="10">
+      <c r="A264" s="25">
         <v>1146607773</v>
       </c>
-      <c r="B264" s="15" t="s">
+      <c r="B264" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="C264" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D264" s="13">
+      <c r="C264" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D264" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A265" s="10">
+      <c r="A265" s="25">
         <v>1146979255</v>
       </c>
-      <c r="B265" s="15" t="s">
+      <c r="B265" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C265" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D265" s="13">
+      <c r="C265" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D265" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A266" s="10">
+      <c r="A266" s="25">
         <v>1149811893</v>
       </c>
-      <c r="B266" s="15" t="s">
+      <c r="B266" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="C266" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D266" s="13">
+      <c r="C266" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D266" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A267" s="22">
+      <c r="A267" s="27">
         <v>1149339077</v>
       </c>
-      <c r="B267" s="23" t="s">
+      <c r="B267" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="C267" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D267" s="25">
+      <c r="C267" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D267" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A268" s="22">
+      <c r="A268" s="27">
         <v>1149508598</v>
       </c>
-      <c r="B268" s="26" t="s">
+      <c r="B268" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="C268" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D268" s="25">
+      <c r="C268" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D268" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A269" s="22">
+      <c r="A269" s="27">
         <v>1147789356</v>
       </c>
-      <c r="B269" s="26" t="s">
+      <c r="B269" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="C269" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D269" s="25">
+      <c r="C269" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D269" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A270" s="22">
+      <c r="A270" s="27">
         <v>1146611726</v>
       </c>
-      <c r="B270" s="26" t="s">
+      <c r="B270" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="C270" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D270" s="25">
+      <c r="C270" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D270" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A271" s="22">
+      <c r="A271" s="27">
         <v>1147262016</v>
       </c>
-      <c r="B271" s="26" t="s">
+      <c r="B271" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="C271" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D271" s="25">
+      <c r="C271" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D271" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A272" s="22">
+      <c r="A272" s="27">
         <v>1147494130</v>
       </c>
-      <c r="B272" s="26" t="s">
+      <c r="B272" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="C272" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D272" s="25">
+      <c r="C272" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D272" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A273" s="22">
+      <c r="A273" s="27">
         <v>1148272907</v>
       </c>
-      <c r="B273" s="26" t="s">
+      <c r="B273" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="C273" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D273" s="25">
+      <c r="C273" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D273" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A274" s="22">
+      <c r="A274" s="27">
         <v>1149254607</v>
       </c>
-      <c r="B274" s="26" t="s">
+      <c r="B274" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="C274" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D274" s="25">
+      <c r="C274" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D274" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A275" s="22">
+      <c r="A275" s="27">
         <v>1149049734</v>
       </c>
-      <c r="B275" s="26" t="s">
+      <c r="B275" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="C275" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D275" s="25">
+      <c r="C275" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D275" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A276" s="22">
+      <c r="A276" s="27">
         <v>1147396244</v>
       </c>
-      <c r="B276" s="26" t="s">
+      <c r="B276" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="C276" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D276" s="25">
+      <c r="C276" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D276" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A277" s="22">
+      <c r="A277" s="27">
         <v>1146310931</v>
       </c>
-      <c r="B277" s="26" t="s">
+      <c r="B277" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="C277" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D277" s="25">
+      <c r="C277" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D277" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A278" s="22">
+      <c r="A278" s="27">
         <v>1145927230</v>
       </c>
-      <c r="B278" s="26" t="s">
+      <c r="B278" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="C278" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D278" s="25">
+      <c r="C278" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D278" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A279" s="22">
+      <c r="A279" s="27">
         <v>1148274754</v>
       </c>
-      <c r="B279" s="26" t="s">
+      <c r="B279" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="C279" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D279" s="25">
+      <c r="C279" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D279" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A280" s="22">
+      <c r="A280" s="27">
         <v>1147544322</v>
       </c>
-      <c r="B280" s="26" t="s">
+      <c r="B280" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="C280" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D280" s="25">
+      <c r="C280" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D280" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A281" s="22">
+      <c r="A281" s="27">
         <v>1146374598</v>
       </c>
-      <c r="B281" s="26" t="s">
+      <c r="B281" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="C281" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D281" s="25">
+      <c r="C281" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D281" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A282" s="22">
+      <c r="A282" s="27">
         <v>1150177127</v>
       </c>
-      <c r="B282" s="26" t="s">
+      <c r="B282" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="C282" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D282" s="25">
+      <c r="C282" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D282" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A283" s="22">
+      <c r="A283" s="27">
         <v>1147539728</v>
       </c>
-      <c r="B283" s="26" t="s">
+      <c r="B283" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="C283" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D283" s="25">
+      <c r="C283" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D283" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A284" s="22">
+      <c r="A284" s="27">
         <v>1147293839</v>
       </c>
-      <c r="B284" s="26" t="s">
+      <c r="B284" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C284" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D284" s="25">
+      <c r="C284" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D284" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A285" s="22">
+      <c r="A285" s="27">
         <v>1148251356</v>
       </c>
-      <c r="B285" s="26" t="s">
+      <c r="B285" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="C285" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D285" s="25">
+      <c r="C285" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D285" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A286" s="22">
+      <c r="A286" s="27">
         <v>1147637472</v>
       </c>
-      <c r="B286" s="26" t="s">
+      <c r="B286" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="C286" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D286" s="25">
+      <c r="C286" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D286" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A287" s="22">
+      <c r="A287" s="27">
         <v>1149530295</v>
       </c>
-      <c r="B287" s="26" t="s">
+      <c r="B287" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C287" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D287" s="25">
+      <c r="C287" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D287" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A288" s="22">
+      <c r="A288" s="27">
         <v>1148778382</v>
       </c>
-      <c r="B288" s="26" t="s">
+      <c r="B288" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="C288" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D288" s="25">
+      <c r="C288" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D288" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A289" s="22">
+      <c r="A289" s="27">
         <v>1147236846</v>
       </c>
-      <c r="B289" s="26" t="s">
+      <c r="B289" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="C289" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D289" s="25">
+      <c r="C289" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D289" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A290" s="22">
+      <c r="A290" s="27">
         <v>2389352689</v>
       </c>
-      <c r="B290" s="26" t="s">
+      <c r="B290" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="C290" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D290" s="25">
+      <c r="C290" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D290" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A291" s="22">
+      <c r="A291" s="27">
         <v>2319640955</v>
       </c>
-      <c r="B291" s="26" t="s">
+      <c r="B291" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="C291" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D291" s="25">
+      <c r="C291" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D291" s="21">
         <v>6</v>
       </c>
     </row>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6B45F7-936D-4B26-B4BA-177B01E72F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B85E2EA-5343-4D6B-A808-5984E1F6E2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1129,25 +1129,22 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -2319,7 +2316,7 @@
   <wetp:taskpane dockstate="right" visibility="0" width="525" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="1" width="525" row="5">
+  <wetp:taskpane dockstate="right" visibility="1" width="525" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2366,7 +2363,7 @@
   <dimension ref="A1:F291"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.7265625" style="5" bestFit="1" customWidth="1"/>
@@ -2375,7 +2372,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2395,7 +2392,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="24">
+      <c r="A2" s="23">
         <v>1150436838</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -2413,7 +2410,7 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="25">
+      <c r="A3" s="24">
         <v>1152217368</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -2431,7 +2428,7 @@
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="25">
+      <c r="A4" s="24">
         <v>1152502371</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -2445,7 +2442,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A5" s="25">
+      <c r="A5" s="24">
         <v>1152327969</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -2459,7 +2456,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>2302448127</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -2473,7 +2470,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A7" s="25">
+      <c r="A7" s="24">
         <v>1153472889</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -2487,7 +2484,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>1152518682</v>
       </c>
       <c r="B8" s="13" t="s">
@@ -2501,7 +2498,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A9" s="25">
+      <c r="A9" s="24">
         <v>1158331023</v>
       </c>
       <c r="B9" s="12" t="s">
@@ -2515,7 +2512,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>1157900240</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -2529,7 +2526,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="25">
+      <c r="A11" s="24">
         <v>1150731048</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -2543,7 +2540,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A12" s="25">
+      <c r="A12" s="24">
         <v>2293198442</v>
       </c>
       <c r="B12" s="13" t="s">
@@ -2557,7 +2554,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A13" s="25">
+      <c r="A13" s="24">
         <v>1174946861</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -2571,7 +2568,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>1152820641</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -2585,7 +2582,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A15" s="25">
+      <c r="A15" s="24">
         <v>1149366963</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -2599,7 +2596,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>1152734123</v>
       </c>
       <c r="B16" s="13" t="s">
@@ -2613,7 +2610,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <v>1152480891</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -2627,7 +2624,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>1153507684</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -2641,7 +2638,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <v>1150008413</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -2655,7 +2652,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>1152989354</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -2669,7 +2666,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <v>1152061618</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -2683,7 +2680,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>1149206417</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -2697,7 +2694,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <v>1151880513</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -2711,7 +2708,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>2290421144</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -2725,7 +2722,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <v>1160061816</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -2739,7 +2736,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>1152890750</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -2753,7 +2750,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <v>1151773627</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -2767,7 +2764,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>1152536601</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -2781,7 +2778,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A29" s="25">
+      <c r="A29" s="24">
         <v>1150018610</v>
       </c>
       <c r="B29" s="13" t="s">
@@ -2795,7 +2792,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A30" s="25">
+      <c r="A30" s="24">
         <v>1146587298</v>
       </c>
       <c r="B30" s="13" t="s">
@@ -2809,7 +2806,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A31" s="25">
+      <c r="A31" s="24">
         <v>1150743167</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -2823,7 +2820,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A32" s="25">
+      <c r="A32" s="24">
         <v>1151146907</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -2837,7 +2834,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A33" s="25">
+      <c r="A33" s="24">
         <v>2443189093</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -2851,7 +2848,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A34" s="25">
+      <c r="A34" s="24">
         <v>1151434659</v>
       </c>
       <c r="B34" s="13" t="s">
@@ -2865,7 +2862,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A35" s="25">
+      <c r="A35" s="24">
         <v>1152565972</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -2879,7 +2876,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A36" s="25">
+      <c r="A36" s="24">
         <v>1154025124</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -2893,7 +2890,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A37" s="25">
+      <c r="A37" s="24">
         <v>1154153991</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -2907,7 +2904,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A38" s="25">
+      <c r="A38" s="24">
         <v>1149486605</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -2921,7 +2918,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A39" s="25">
+      <c r="A39" s="24">
         <v>1152472815</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -2935,7 +2932,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A40" s="25">
+      <c r="A40" s="24">
         <v>1150396164</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -2949,7 +2946,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A41" s="25">
+      <c r="A41" s="24">
         <v>1150491064</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -2963,7 +2960,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A42" s="25">
+      <c r="A42" s="24">
         <v>1152786958</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -2977,7 +2974,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A43" s="25">
+      <c r="A43" s="24">
         <v>1149922534</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -2991,7 +2988,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A44" s="25">
+      <c r="A44" s="24">
         <v>2269053001</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -3005,7 +3002,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A45" s="25">
+      <c r="A45" s="24">
         <v>1157238989</v>
       </c>
       <c r="B45" s="12" t="s">
@@ -3019,7 +3016,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A46" s="25">
+      <c r="A46" s="24">
         <v>1153155559</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -3033,7 +3030,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A47" s="25">
+      <c r="A47" s="24">
         <v>1149465245</v>
       </c>
       <c r="B47" s="13" t="s">
@@ -3047,7 +3044,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A48" s="25">
+      <c r="A48" s="24">
         <v>1155938150</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -3061,7 +3058,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="25">
+      <c r="A49" s="24">
         <v>1149696633</v>
       </c>
       <c r="B49" s="13" t="s">
@@ -3075,7 +3072,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="25">
+      <c r="A50" s="24">
         <v>1155454240</v>
       </c>
       <c r="B50" s="13" t="s">
@@ -3089,7 +3086,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A51" s="25">
+      <c r="A51" s="24">
         <v>1150039038</v>
       </c>
       <c r="B51" s="13" t="s">
@@ -3103,7 +3100,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A52" s="25">
+      <c r="A52" s="24">
         <v>1152218085</v>
       </c>
       <c r="B52" s="13" t="s">
@@ -3117,7 +3114,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="25">
+      <c r="A53" s="24">
         <v>1147013252</v>
       </c>
       <c r="B53" s="13" t="s">
@@ -3131,7 +3128,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A54" s="25">
+      <c r="A54" s="24">
         <v>1154169450</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -3145,7 +3142,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="25">
+      <c r="A55" s="24">
         <v>1151233614</v>
       </c>
       <c r="B55" s="13" t="s">
@@ -3159,7 +3156,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="25">
+      <c r="A56" s="24">
         <v>1151650809</v>
       </c>
       <c r="B56" s="13" t="s">
@@ -3173,7 +3170,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="25">
+      <c r="A57" s="24">
         <v>1151119201</v>
       </c>
       <c r="B57" s="13" t="s">
@@ -3187,7 +3184,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="25">
+      <c r="A58" s="24">
         <v>1152878417</v>
       </c>
       <c r="B58" s="13" t="s">
@@ -3201,7 +3198,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="25">
+      <c r="A59" s="24">
         <v>1152574958</v>
       </c>
       <c r="B59" s="13" t="s">
@@ -3215,7 +3212,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A60" s="25">
+      <c r="A60" s="24">
         <v>1152986681</v>
       </c>
       <c r="B60" s="13" t="s">
@@ -3229,7 +3226,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A61" s="25">
+      <c r="A61" s="24">
         <v>1151154455</v>
       </c>
       <c r="B61" s="13" t="s">
@@ -3243,7 +3240,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A62" s="25">
+      <c r="A62" s="24">
         <v>1159289287</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -3257,7 +3254,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A63" s="25">
+      <c r="A63" s="24">
         <v>1153334618</v>
       </c>
       <c r="B63" s="13" t="s">
@@ -3271,7 +3268,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A64" s="25">
+      <c r="A64" s="24">
         <v>1152212658</v>
       </c>
       <c r="B64" s="13" t="s">
@@ -3285,7 +3282,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A65" s="25">
+      <c r="A65" s="24">
         <v>1152410336</v>
       </c>
       <c r="B65" s="13" t="s">
@@ -3299,7 +3296,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A66" s="25">
+      <c r="A66" s="24">
         <v>1154207904</v>
       </c>
       <c r="B66" s="13" t="s">
@@ -3313,7 +3310,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A67" s="25">
+      <c r="A67" s="24">
         <v>1168345245</v>
       </c>
       <c r="B67" s="13" t="s">
@@ -3327,7 +3324,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A68" s="25">
+      <c r="A68" s="24">
         <v>1149893040</v>
       </c>
       <c r="B68" s="13" t="s">
@@ -3341,7 +3338,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A69" s="25">
+      <c r="A69" s="24">
         <v>1151849807</v>
       </c>
       <c r="B69" s="13" t="s">
@@ -3355,7 +3352,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A70" s="25">
+      <c r="A70" s="24">
         <v>1152284103</v>
       </c>
       <c r="B70" s="13" t="s">
@@ -3369,7 +3366,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A71" s="25">
+      <c r="A71" s="24">
         <v>1167082591</v>
       </c>
       <c r="B71" s="13" t="s">
@@ -3383,7 +3380,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A72" s="25">
+      <c r="A72" s="24">
         <v>1153479645</v>
       </c>
       <c r="B72" s="13" t="s">
@@ -3397,7 +3394,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A73" s="25">
+      <c r="A73" s="24">
         <v>1155524893</v>
       </c>
       <c r="B73" s="13" t="s">
@@ -3411,7 +3408,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A74" s="25">
+      <c r="A74" s="24">
         <v>1150599171</v>
       </c>
       <c r="B74" s="12" t="s">
@@ -3425,7 +3422,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A75" s="25">
+      <c r="A75" s="24">
         <v>1154873481</v>
       </c>
       <c r="B75" s="13" t="s">
@@ -3439,7 +3436,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A76" s="25">
+      <c r="A76" s="24">
         <v>1152884167</v>
       </c>
       <c r="B76" s="13" t="s">
@@ -3453,7 +3450,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A77" s="25">
+      <c r="A77" s="24">
         <v>1152128029</v>
       </c>
       <c r="B77" s="13" t="s">
@@ -3467,7 +3464,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A78" s="25">
+      <c r="A78" s="24">
         <v>1151910013</v>
       </c>
       <c r="B78" s="13" t="s">
@@ -3481,7 +3478,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A79" s="25">
+      <c r="A79" s="24">
         <v>1154287575</v>
       </c>
       <c r="B79" s="13" t="s">
@@ -3495,7 +3492,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A80" s="25">
+      <c r="A80" s="24">
         <v>1152571822</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -3509,7 +3506,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A81" s="25">
+      <c r="A81" s="24">
         <v>1150680112</v>
       </c>
       <c r="B81" s="13" t="s">
@@ -3523,7 +3520,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A82" s="25">
+      <c r="A82" s="24">
         <v>1150690798</v>
       </c>
       <c r="B82" s="13" t="s">
@@ -3537,7 +3534,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A83" s="25">
+      <c r="A83" s="24">
         <v>1151961511</v>
       </c>
       <c r="B83" s="13" t="s">
@@ -3551,7 +3548,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A84" s="25">
+      <c r="A84" s="24">
         <v>1149761460</v>
       </c>
       <c r="B84" s="13" t="s">
@@ -3565,7 +3562,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A85" s="25">
+      <c r="A85" s="24">
         <v>2297211076</v>
       </c>
       <c r="B85" s="13" t="s">
@@ -3579,7 +3576,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A86" s="25">
+      <c r="A86" s="24">
         <v>1153216211</v>
       </c>
       <c r="B86" s="13" t="s">
@@ -3593,7 +3590,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A87" s="25">
+      <c r="A87" s="24">
         <v>1152536460</v>
       </c>
       <c r="B87" s="13" t="s">
@@ -3607,7 +3604,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A88" s="25">
+      <c r="A88" s="24">
         <v>1152152763</v>
       </c>
       <c r="B88" s="13" t="s">
@@ -3621,7 +3618,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A89" s="25">
+      <c r="A89" s="24">
         <v>1156092080</v>
       </c>
       <c r="B89" s="13" t="s">
@@ -3635,7 +3632,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A90" s="25">
+      <c r="A90" s="24">
         <v>2510170026</v>
       </c>
       <c r="B90" s="13" t="s">
@@ -3649,7 +3646,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A91" s="25">
+      <c r="A91" s="24">
         <v>1151404256</v>
       </c>
       <c r="B91" s="13" t="s">
@@ -3663,7 +3660,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="25">
+      <c r="A92" s="24">
         <v>1152224984</v>
       </c>
       <c r="B92" s="13" t="s">
@@ -3677,7 +3674,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A93" s="25">
+      <c r="A93" s="24">
         <v>1150781068</v>
       </c>
       <c r="B93" s="13" t="s">
@@ -3691,7 +3688,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A94" s="25">
+      <c r="A94" s="24">
         <v>1150218970</v>
       </c>
       <c r="B94" s="13" t="s">
@@ -3705,7 +3702,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A95" s="25">
+      <c r="A95" s="24">
         <v>1153072044</v>
       </c>
       <c r="B95" s="13" t="s">
@@ -3719,7 +3716,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="25">
+      <c r="A96" s="24">
         <v>1153072069</v>
       </c>
       <c r="B96" s="13" t="s">
@@ -3733,7 +3730,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="25">
+      <c r="A97" s="24">
         <v>1149401059</v>
       </c>
       <c r="B97" s="13" t="s">
@@ -3747,7 +3744,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A98" s="25">
+      <c r="A98" s="24">
         <v>1153495591</v>
       </c>
       <c r="B98" s="13" t="s">
@@ -3761,7 +3758,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A99" s="25">
+      <c r="A99" s="24">
         <v>1150973210</v>
       </c>
       <c r="B99" s="13" t="s">
@@ -3775,7 +3772,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A100" s="25">
+      <c r="A100" s="24">
         <v>1151704598</v>
       </c>
       <c r="B100" s="13" t="s">
@@ -3789,7 +3786,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A101" s="25">
+      <c r="A101" s="24">
         <v>1151845870</v>
       </c>
       <c r="B101" s="13" t="s">
@@ -3803,7 +3800,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A102" s="25">
+      <c r="A102" s="24">
         <v>1149888925</v>
       </c>
       <c r="B102" s="13" t="s">
@@ -3817,7 +3814,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A103" s="25">
+      <c r="A103" s="24">
         <v>1153380116</v>
       </c>
       <c r="B103" s="13" t="s">
@@ -3831,7 +3828,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A104" s="25">
+      <c r="A104" s="24">
         <v>1152305007</v>
       </c>
       <c r="B104" s="13" t="s">
@@ -3845,7 +3842,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A105" s="25">
+      <c r="A105" s="24">
         <v>1153607922</v>
       </c>
       <c r="B105" s="13" t="s">
@@ -3859,7 +3856,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A106" s="25">
+      <c r="A106" s="24">
         <v>1152853493</v>
       </c>
       <c r="B106" s="13" t="s">
@@ -3873,7 +3870,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A107" s="25">
+      <c r="A107" s="24">
         <v>1153534167</v>
       </c>
       <c r="B107" s="13" t="s">
@@ -3887,7 +3884,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A108" s="25">
+      <c r="A108" s="24">
         <v>1149855445</v>
       </c>
       <c r="B108" s="13" t="s">
@@ -3901,7 +3898,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A109" s="25">
+      <c r="A109" s="24">
         <v>1153291388</v>
       </c>
       <c r="B109" s="13" t="s">
@@ -3915,7 +3912,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A110" s="25">
+      <c r="A110" s="24">
         <v>1151814371</v>
       </c>
       <c r="B110" s="13" t="s">
@@ -3929,7 +3926,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A111" s="25">
+      <c r="A111" s="24">
         <v>1158612646</v>
       </c>
       <c r="B111" s="13" t="s">
@@ -3943,7 +3940,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A112" s="25">
+      <c r="A112" s="24">
         <v>1151003728</v>
       </c>
       <c r="B112" s="13" t="s">
@@ -3957,7 +3954,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A113" s="25">
+      <c r="A113" s="24">
         <v>1174052116</v>
       </c>
       <c r="B113" s="13" t="s">
@@ -3971,7 +3968,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A114" s="25">
+      <c r="A114" s="24">
         <v>1153013931</v>
       </c>
       <c r="B114" s="13" t="s">
@@ -3985,7 +3982,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A115" s="25">
+      <c r="A115" s="24">
         <v>1150396081</v>
       </c>
       <c r="B115" s="13" t="s">
@@ -3999,7 +3996,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A116" s="25">
+      <c r="A116" s="24">
         <v>1150690699</v>
       </c>
       <c r="B116" s="13" t="s">
@@ -4013,7 +4010,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A117" s="25">
+      <c r="A117" s="24">
         <v>1152698252</v>
       </c>
       <c r="B117" s="13" t="s">
@@ -4027,7 +4024,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A118" s="25">
+      <c r="A118" s="24">
         <v>1153384795</v>
       </c>
       <c r="B118" s="13" t="s">
@@ -4041,7 +4038,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A119" s="25">
+      <c r="A119" s="24">
         <v>1150304325</v>
       </c>
       <c r="B119" s="13" t="s">
@@ -4055,7 +4052,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A120" s="25">
+      <c r="A120" s="24">
         <v>1152915870</v>
       </c>
       <c r="B120" s="13" t="s">
@@ -4069,7 +4066,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A121" s="25">
+      <c r="A121" s="24">
         <v>1152367700</v>
       </c>
       <c r="B121" s="13" t="s">
@@ -4083,7 +4080,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A122" s="25">
+      <c r="A122" s="24">
         <v>1152775639</v>
       </c>
       <c r="B122" s="13" t="s">
@@ -4097,7 +4094,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A123" s="25">
+      <c r="A123" s="24">
         <v>1149182303</v>
       </c>
       <c r="B123" s="13" t="s">
@@ -4111,7 +4108,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A124" s="25">
+      <c r="A124" s="24">
         <v>1149628024</v>
       </c>
       <c r="B124" s="13" t="s">
@@ -4125,7 +4122,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A125" s="25">
+      <c r="A125" s="24">
         <v>1152522833</v>
       </c>
       <c r="B125" s="13" t="s">
@@ -4139,7 +4136,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A126" s="25">
+      <c r="A126" s="24">
         <v>2382166136</v>
       </c>
       <c r="B126" s="13" t="s">
@@ -4153,7 +4150,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A127" s="25">
+      <c r="A127" s="24">
         <v>1151669510</v>
       </c>
       <c r="B127" s="13" t="s">
@@ -4167,7 +4164,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A128" s="25">
+      <c r="A128" s="24">
         <v>1155012543</v>
       </c>
       <c r="B128" s="13" t="s">
@@ -4181,7 +4178,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A129" s="25">
+      <c r="A129" s="24">
         <v>1150763322</v>
       </c>
       <c r="B129" s="13" t="s">
@@ -4195,7 +4192,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A130" s="25">
+      <c r="A130" s="24">
         <v>1150527107</v>
       </c>
       <c r="B130" s="12" t="s">
@@ -4209,7 +4206,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A131" s="25">
+      <c r="A131" s="24">
         <v>1171859398</v>
       </c>
       <c r="B131" s="13" t="s">
@@ -4223,7 +4220,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A132" s="25">
+      <c r="A132" s="24">
         <v>1151485529</v>
       </c>
       <c r="B132" s="13" t="s">
@@ -4237,7 +4234,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A133" s="25">
+      <c r="A133" s="24">
         <v>1153562317</v>
       </c>
       <c r="B133" s="13" t="s">
@@ -4251,7 +4248,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A134" s="25">
+      <c r="A134" s="24">
         <v>1153018385</v>
       </c>
       <c r="B134" s="13" t="s">
@@ -4265,7 +4262,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A135" s="25">
+      <c r="A135" s="24">
         <v>2288260736</v>
       </c>
       <c r="B135" s="13" t="s">
@@ -4279,7 +4276,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A136" s="25">
+      <c r="A136" s="24">
         <v>1152156905</v>
       </c>
       <c r="B136" s="13" t="s">
@@ -4293,7 +4290,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A137" s="25">
+      <c r="A137" s="24">
         <v>1152746895</v>
       </c>
       <c r="B137" s="13" t="s">
@@ -4307,7 +4304,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A138" s="25">
+      <c r="A138" s="24">
         <v>1153259260</v>
       </c>
       <c r="B138" s="13" t="s">
@@ -4321,7 +4318,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A139" s="25">
+      <c r="A139" s="24">
         <v>1153491590</v>
       </c>
       <c r="B139" s="13" t="s">
@@ -4335,7 +4332,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A140" s="25">
+      <c r="A140" s="24">
         <v>1148755273</v>
       </c>
       <c r="B140" s="13" t="s">
@@ -4349,7 +4346,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A141" s="25">
+      <c r="A141" s="24">
         <v>1146774821</v>
       </c>
       <c r="B141" s="13" t="s">
@@ -4363,7 +4360,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A142" s="25">
+      <c r="A142" s="24">
         <v>1146165780</v>
       </c>
       <c r="B142" s="13" t="s">
@@ -4377,7 +4374,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A143" s="25">
+      <c r="A143" s="24">
         <v>1147913071</v>
       </c>
       <c r="B143" s="13" t="s">
@@ -4391,7 +4388,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A144" s="25">
+      <c r="A144" s="24">
         <v>1149665844</v>
       </c>
       <c r="B144" s="13" t="s">
@@ -4405,7 +4402,7 @@
       </c>
     </row>
     <row r="145" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A145" s="25">
+      <c r="A145" s="24">
         <v>2282375720</v>
       </c>
       <c r="B145" s="13" t="s">
@@ -4419,7 +4416,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A146" s="25">
+      <c r="A146" s="24">
         <v>2415139746</v>
       </c>
       <c r="B146" s="13" t="s">
@@ -4433,7 +4430,7 @@
       </c>
     </row>
     <row r="147" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A147" s="25">
+      <c r="A147" s="24">
         <v>1146628035</v>
       </c>
       <c r="B147" s="13" t="s">
@@ -4447,7 +4444,7 @@
       </c>
     </row>
     <row r="148" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A148" s="25">
+      <c r="A148" s="24">
         <v>1148873159</v>
       </c>
       <c r="B148" s="13" t="s">
@@ -4461,7 +4458,7 @@
       </c>
     </row>
     <row r="149" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A149" s="25">
+      <c r="A149" s="24">
         <v>2275349674</v>
       </c>
       <c r="B149" s="13" t="s">
@@ -4475,7 +4472,7 @@
       </c>
     </row>
     <row r="150" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A150" s="25">
+      <c r="A150" s="24">
         <v>1145487730</v>
       </c>
       <c r="B150" s="13" t="s">
@@ -4489,7 +4486,7 @@
       </c>
     </row>
     <row r="151" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A151" s="25">
+      <c r="A151" s="24">
         <v>1146809536</v>
       </c>
       <c r="B151" s="13" t="s">
@@ -4503,7 +4500,7 @@
       </c>
     </row>
     <row r="152" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A152" s="25">
+      <c r="A152" s="24">
         <v>1164976993</v>
       </c>
       <c r="B152" s="13" t="s">
@@ -4517,7 +4514,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A153" s="25">
+      <c r="A153" s="24">
         <v>1146821820</v>
       </c>
       <c r="B153" s="13" t="s">
@@ -4531,7 +4528,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A154" s="25">
+      <c r="A154" s="24">
         <v>1146526668</v>
       </c>
       <c r="B154" s="13" t="s">
@@ -4545,7 +4542,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A155" s="25">
+      <c r="A155" s="24">
         <v>1149762419</v>
       </c>
       <c r="B155" s="13" t="s">
@@ -4559,7 +4556,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A156" s="25">
+      <c r="A156" s="24">
         <v>1146972862</v>
       </c>
       <c r="B156" s="13" t="s">
@@ -4573,7 +4570,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A157" s="25">
+      <c r="A157" s="24">
         <v>1148273418</v>
       </c>
       <c r="B157" s="13" t="s">
@@ -4587,7 +4584,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A158" s="25">
+      <c r="A158" s="24">
         <v>1148688326</v>
       </c>
       <c r="B158" s="13" t="s">
@@ -4601,7 +4598,7 @@
       </c>
     </row>
     <row r="159" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A159" s="25">
+      <c r="A159" s="24">
         <v>1146775844</v>
       </c>
       <c r="B159" s="13" t="s">
@@ -4615,7 +4612,7 @@
       </c>
     </row>
     <row r="160" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A160" s="25">
+      <c r="A160" s="24">
         <v>2344822255</v>
       </c>
       <c r="B160" s="13" t="s">
@@ -4629,7 +4626,7 @@
       </c>
     </row>
     <row r="161" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A161" s="25">
+      <c r="A161" s="24">
         <v>1150838223</v>
       </c>
       <c r="B161" s="13" t="s">
@@ -4643,7 +4640,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A162" s="25">
+      <c r="A162" s="24">
         <v>1146376064</v>
       </c>
       <c r="B162" s="13" t="s">
@@ -4657,7 +4654,7 @@
       </c>
     </row>
     <row r="163" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A163" s="25">
+      <c r="A163" s="24">
         <v>1144789813</v>
       </c>
       <c r="B163" s="13" t="s">
@@ -4671,7 +4668,7 @@
       </c>
     </row>
     <row r="164" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A164" s="25">
+      <c r="A164" s="24">
         <v>1146471519</v>
       </c>
       <c r="B164" s="13" t="s">
@@ -4685,7 +4682,7 @@
       </c>
     </row>
     <row r="165" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A165" s="25">
+      <c r="A165" s="24">
         <v>1145431654</v>
       </c>
       <c r="B165" s="9" t="s">
@@ -4699,7 +4696,7 @@
       </c>
     </row>
     <row r="166" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A166" s="25">
+      <c r="A166" s="24">
         <v>1148252990</v>
       </c>
       <c r="B166" s="13" t="s">
@@ -4713,7 +4710,7 @@
       </c>
     </row>
     <row r="167" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="25">
+      <c r="A167" s="24">
         <v>1149306225</v>
       </c>
       <c r="B167" s="13" t="s">
@@ -4727,7 +4724,7 @@
       </c>
     </row>
     <row r="168" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A168" s="25">
+      <c r="A168" s="24">
         <v>1151264437</v>
       </c>
       <c r="B168" s="13" t="s">
@@ -4741,7 +4738,7 @@
       </c>
     </row>
     <row r="169" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A169" s="25">
+      <c r="A169" s="24">
         <v>1150158754</v>
       </c>
       <c r="B169" s="13" t="s">
@@ -4755,7 +4752,7 @@
       </c>
     </row>
     <row r="170" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A170" s="25">
+      <c r="A170" s="24">
         <v>1148596271</v>
       </c>
       <c r="B170" s="13" t="s">
@@ -4769,7 +4766,7 @@
       </c>
     </row>
     <row r="171" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A171" s="25">
+      <c r="A171" s="24">
         <v>1147407355</v>
       </c>
       <c r="B171" s="13" t="s">
@@ -4783,7 +4780,7 @@
       </c>
     </row>
     <row r="172" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A172" s="25">
+      <c r="A172" s="24">
         <v>1146987373</v>
       </c>
       <c r="B172" s="13" t="s">
@@ -4797,7 +4794,7 @@
       </c>
     </row>
     <row r="173" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A173" s="25">
+      <c r="A173" s="24">
         <v>1142858388</v>
       </c>
       <c r="B173" s="13" t="s">
@@ -4811,7 +4808,7 @@
       </c>
     </row>
     <row r="174" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A174" s="25">
+      <c r="A174" s="24">
         <v>1148535568</v>
       </c>
       <c r="B174" s="13" t="s">
@@ -4825,7 +4822,7 @@
       </c>
     </row>
     <row r="175" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A175" s="25">
+      <c r="A175" s="24">
         <v>1147255028</v>
       </c>
       <c r="B175" s="13" t="s">
@@ -4839,7 +4836,7 @@
       </c>
     </row>
     <row r="176" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A176" s="25">
+      <c r="A176" s="24">
         <v>1147682353</v>
       </c>
       <c r="B176" s="13" t="s">
@@ -4853,7 +4850,7 @@
       </c>
     </row>
     <row r="177" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A177" s="25">
+      <c r="A177" s="24">
         <v>1146380868</v>
       </c>
       <c r="B177" s="13" t="s">
@@ -4867,7 +4864,7 @@
       </c>
     </row>
     <row r="178" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A178" s="25">
+      <c r="A178" s="24">
         <v>1149234906</v>
       </c>
       <c r="B178" s="13" t="s">
@@ -4881,7 +4878,7 @@
       </c>
     </row>
     <row r="179" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A179" s="25">
+      <c r="A179" s="24">
         <v>1145460539</v>
       </c>
       <c r="B179" s="14" t="s">
@@ -4895,7 +4892,7 @@
       </c>
     </row>
     <row r="180" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A180" s="25">
+      <c r="A180" s="24">
         <v>1146879539</v>
       </c>
       <c r="B180" s="13" t="s">
@@ -4909,7 +4906,7 @@
       </c>
     </row>
     <row r="181" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A181" s="25">
+      <c r="A181" s="24">
         <v>1146061013</v>
       </c>
       <c r="B181" s="13" t="s">
@@ -4923,7 +4920,7 @@
       </c>
     </row>
     <row r="182" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A182" s="25">
+      <c r="A182" s="24">
         <v>1161327497</v>
       </c>
       <c r="B182" s="13" t="s">
@@ -4937,7 +4934,7 @@
       </c>
     </row>
     <row r="183" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A183" s="25">
+      <c r="A183" s="24">
         <v>1146546294</v>
       </c>
       <c r="B183" s="13" t="s">
@@ -4951,7 +4948,7 @@
       </c>
     </row>
     <row r="184" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A184" s="25">
+      <c r="A184" s="24">
         <v>1147314809</v>
       </c>
       <c r="B184" s="13" t="s">
@@ -4965,7 +4962,7 @@
       </c>
     </row>
     <row r="185" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A185" s="25">
+      <c r="A185" s="24">
         <v>1148907890</v>
       </c>
       <c r="B185" s="13" t="s">
@@ -4979,7 +4976,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A186" s="25">
+      <c r="A186" s="24">
         <v>1148220138</v>
       </c>
       <c r="B186" s="13" t="s">
@@ -4993,7 +4990,7 @@
       </c>
     </row>
     <row r="187" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A187" s="25">
+      <c r="A187" s="24">
         <v>1149587360</v>
       </c>
       <c r="B187" s="13" t="s">
@@ -5007,7 +5004,7 @@
       </c>
     </row>
     <row r="188" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A188" s="25">
+      <c r="A188" s="24">
         <v>1149826164</v>
       </c>
       <c r="B188" s="13" t="s">
@@ -5021,7 +5018,7 @@
       </c>
     </row>
     <row r="189" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A189" s="25">
+      <c r="A189" s="24">
         <v>2337878892</v>
       </c>
       <c r="B189" s="13" t="s">
@@ -5035,7 +5032,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A190" s="25">
+      <c r="A190" s="24">
         <v>1149812065</v>
       </c>
       <c r="B190" s="15" t="s">
@@ -5049,7 +5046,7 @@
       </c>
     </row>
     <row r="191" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A191" s="25">
+      <c r="A191" s="24">
         <v>1147392706</v>
       </c>
       <c r="B191" s="13" t="s">
@@ -5063,7 +5060,7 @@
       </c>
     </row>
     <row r="192" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A192" s="25">
+      <c r="A192" s="24">
         <v>1145344212</v>
       </c>
       <c r="B192" s="13" t="s">
@@ -5077,7 +5074,7 @@
       </c>
     </row>
     <row r="193" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A193" s="25">
+      <c r="A193" s="24">
         <v>1151073234</v>
       </c>
       <c r="B193" s="13" t="s">
@@ -5091,7 +5088,7 @@
       </c>
     </row>
     <row r="194" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A194" s="25">
+      <c r="A194" s="24">
         <v>1149661421</v>
       </c>
       <c r="B194" s="12" t="s">
@@ -5105,7 +5102,7 @@
       </c>
     </row>
     <row r="195" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A195" s="25">
+      <c r="A195" s="24">
         <v>1147116089</v>
       </c>
       <c r="B195" s="13" t="s">
@@ -5119,7 +5116,7 @@
       </c>
     </row>
     <row r="196" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A196" s="25">
+      <c r="A196" s="24">
         <v>1147116014</v>
       </c>
       <c r="B196" s="13" t="s">
@@ -5133,7 +5130,7 @@
       </c>
     </row>
     <row r="197" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A197" s="25">
+      <c r="A197" s="24">
         <v>1147138059</v>
       </c>
       <c r="B197" s="13" t="s">
@@ -5147,7 +5144,7 @@
       </c>
     </row>
     <row r="198" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A198" s="25">
+      <c r="A198" s="24">
         <v>1146518921</v>
       </c>
       <c r="B198" s="13" t="s">
@@ -5161,7 +5158,7 @@
       </c>
     </row>
     <row r="199" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A199" s="25">
+      <c r="A199" s="24">
         <v>1154144388</v>
       </c>
       <c r="B199" s="13" t="s">
@@ -5175,7 +5172,7 @@
       </c>
     </row>
     <row r="200" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A200" s="25">
+      <c r="A200" s="24">
         <v>1147117111</v>
       </c>
       <c r="B200" s="12" t="s">
@@ -5189,7 +5186,7 @@
       </c>
     </row>
     <row r="201" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A201" s="25">
+      <c r="A201" s="24">
         <v>1147073637</v>
       </c>
       <c r="B201" s="13" t="s">
@@ -5203,7 +5200,7 @@
       </c>
     </row>
     <row r="202" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A202" s="25">
+      <c r="A202" s="24">
         <v>1149366534</v>
       </c>
       <c r="B202" s="13" t="s">
@@ -5217,7 +5214,7 @@
       </c>
     </row>
     <row r="203" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A203" s="25">
+      <c r="A203" s="24">
         <v>1151122668</v>
       </c>
       <c r="B203" s="13" t="s">
@@ -5231,7 +5228,7 @@
       </c>
     </row>
     <row r="204" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A204" s="25">
+      <c r="A204" s="24">
         <v>1147318826</v>
       </c>
       <c r="B204" s="13" t="s">
@@ -5245,7 +5242,7 @@
       </c>
     </row>
     <row r="205" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A205" s="25">
+      <c r="A205" s="24">
         <v>2282275516</v>
       </c>
       <c r="B205" s="13" t="s">
@@ -5259,7 +5256,7 @@
       </c>
     </row>
     <row r="206" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A206" s="25">
+      <c r="A206" s="24">
         <v>1148331737</v>
       </c>
       <c r="B206" s="13" t="s">
@@ -5273,7 +5270,7 @@
       </c>
     </row>
     <row r="207" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A207" s="25">
+      <c r="A207" s="24">
         <v>1148003252</v>
       </c>
       <c r="B207" s="13" t="s">
@@ -5287,7 +5284,7 @@
       </c>
     </row>
     <row r="208" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A208" s="25">
+      <c r="A208" s="24">
         <v>1146792161</v>
       </c>
       <c r="B208" s="13" t="s">
@@ -5301,7 +5298,7 @@
       </c>
     </row>
     <row r="209" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A209" s="25">
+      <c r="A209" s="24">
         <v>1148196452</v>
       </c>
       <c r="B209" s="13" t="s">
@@ -5315,7 +5312,7 @@
       </c>
     </row>
     <row r="210" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A210" s="25">
+      <c r="A210" s="24">
         <v>1146902935</v>
       </c>
       <c r="B210" s="13" t="s">
@@ -5329,7 +5326,7 @@
       </c>
     </row>
     <row r="211" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A211" s="25">
+      <c r="A211" s="24">
         <v>1145718209</v>
       </c>
       <c r="B211" s="13" t="s">
@@ -5343,7 +5340,7 @@
       </c>
     </row>
     <row r="212" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A212" s="25">
+      <c r="A212" s="24">
         <v>1148921412</v>
       </c>
       <c r="B212" s="13" t="s">
@@ -5357,7 +5354,7 @@
       </c>
     </row>
     <row r="213" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A213" s="25">
+      <c r="A213" s="24">
         <v>1150070421</v>
       </c>
       <c r="B213" s="13" t="s">
@@ -5371,7 +5368,7 @@
       </c>
     </row>
     <row r="214" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A214" s="25">
+      <c r="A214" s="24">
         <v>1169254040</v>
       </c>
       <c r="B214" s="13" t="s">
@@ -5385,7 +5382,7 @@
       </c>
     </row>
     <row r="215" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A215" s="25">
+      <c r="A215" s="24">
         <v>1145733752</v>
       </c>
       <c r="B215" s="13" t="s">
@@ -5399,7 +5396,7 @@
       </c>
     </row>
     <row r="216" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A216" s="25">
+      <c r="A216" s="24">
         <v>1146851652</v>
       </c>
       <c r="B216" s="13" t="s">
@@ -5413,7 +5410,7 @@
       </c>
     </row>
     <row r="217" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A217" s="25">
+      <c r="A217" s="24">
         <v>1146339948</v>
       </c>
       <c r="B217" s="13" t="s">
@@ -5427,7 +5424,7 @@
       </c>
     </row>
     <row r="218" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A218" s="25">
+      <c r="A218" s="24">
         <v>1156163931</v>
       </c>
       <c r="B218" s="13" t="s">
@@ -5441,7 +5438,7 @@
       </c>
     </row>
     <row r="219" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A219" s="25">
+      <c r="A219" s="24">
         <v>1148066275</v>
       </c>
       <c r="B219" s="13" t="s">
@@ -5455,7 +5452,7 @@
       </c>
     </row>
     <row r="220" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A220" s="25">
+      <c r="A220" s="24">
         <v>1148850710</v>
       </c>
       <c r="B220" s="13" t="s">
@@ -5469,7 +5466,7 @@
       </c>
     </row>
     <row r="221" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A221" s="25">
+      <c r="A221" s="24">
         <v>1146399652</v>
       </c>
       <c r="B221" s="13" t="s">
@@ -5483,7 +5480,7 @@
       </c>
     </row>
     <row r="222" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A222" s="25">
+      <c r="A222" s="24">
         <v>1148398181</v>
       </c>
       <c r="B222" s="13" t="s">
@@ -5497,7 +5494,7 @@
       </c>
     </row>
     <row r="223" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A223" s="25">
+      <c r="A223" s="24">
         <v>1145648166</v>
       </c>
       <c r="B223" s="13" t="s">
@@ -5511,7 +5508,7 @@
       </c>
     </row>
     <row r="224" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A224" s="25">
+      <c r="A224" s="24">
         <v>1147594236</v>
       </c>
       <c r="B224" s="13" t="s">
@@ -5525,7 +5522,7 @@
       </c>
     </row>
     <row r="225" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A225" s="25">
+      <c r="A225" s="24">
         <v>1146766389</v>
       </c>
       <c r="B225" s="13" t="s">
@@ -5539,7 +5536,7 @@
       </c>
     </row>
     <row r="226" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A226" s="25">
+      <c r="A226" s="24">
         <v>1148766015</v>
       </c>
       <c r="B226" s="14" t="s">
@@ -5553,7 +5550,7 @@
       </c>
     </row>
     <row r="227" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A227" s="25">
+      <c r="A227" s="24">
         <v>1161794449</v>
       </c>
       <c r="B227" s="13" t="s">
@@ -5567,7 +5564,7 @@
       </c>
     </row>
     <row r="228" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A228" s="25">
+      <c r="A228" s="24">
         <v>1149400937</v>
       </c>
       <c r="B228" s="13" t="s">
@@ -5581,7 +5578,7 @@
       </c>
     </row>
     <row r="229" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A229" s="25">
+      <c r="A229" s="24">
         <v>1148097148</v>
       </c>
       <c r="B229" s="13" t="s">
@@ -5595,7 +5592,7 @@
       </c>
     </row>
     <row r="230" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A230" s="25">
+      <c r="A230" s="24">
         <v>1149512558</v>
       </c>
       <c r="B230" s="13" t="s">
@@ -5609,7 +5606,7 @@
       </c>
     </row>
     <row r="231" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A231" s="25">
+      <c r="A231" s="24">
         <v>1148636135</v>
       </c>
       <c r="B231" s="13" t="s">
@@ -5623,7 +5620,7 @@
       </c>
     </row>
     <row r="232" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A232" s="25">
+      <c r="A232" s="24">
         <v>1148833708</v>
       </c>
       <c r="B232" s="13" t="s">
@@ -5637,7 +5634,7 @@
       </c>
     </row>
     <row r="233" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A233" s="25">
+      <c r="A233" s="24">
         <v>1145244214</v>
       </c>
       <c r="B233" s="13" t="s">
@@ -5651,7 +5648,7 @@
       </c>
     </row>
     <row r="234" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A234" s="25">
+      <c r="A234" s="24">
         <v>1149415935</v>
       </c>
       <c r="B234" s="13" t="s">
@@ -5665,7 +5662,7 @@
       </c>
     </row>
     <row r="235" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A235" s="25">
+      <c r="A235" s="24">
         <v>2282843446</v>
       </c>
       <c r="B235" s="13" t="s">
@@ -5679,7 +5676,7 @@
       </c>
     </row>
     <row r="236" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A236" s="25">
+      <c r="A236" s="24">
         <v>1147952509</v>
       </c>
       <c r="B236" s="13" t="s">
@@ -5693,7 +5690,7 @@
       </c>
     </row>
     <row r="237" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A237" s="25">
+      <c r="A237" s="24">
         <v>1149342303</v>
       </c>
       <c r="B237" s="17" t="s">
@@ -5707,7 +5704,7 @@
       </c>
     </row>
     <row r="238" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A238" s="25">
+      <c r="A238" s="24">
         <v>1147346579</v>
       </c>
       <c r="B238" s="13" t="s">
@@ -5721,7 +5718,7 @@
       </c>
     </row>
     <row r="239" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A239" s="25">
+      <c r="A239" s="24">
         <v>1146982663</v>
       </c>
       <c r="B239" s="17" t="s">
@@ -5735,7 +5732,7 @@
       </c>
     </row>
     <row r="240" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A240" s="25">
+      <c r="A240" s="24">
         <v>1148895673</v>
       </c>
       <c r="B240" s="13" t="s">
@@ -5749,7 +5746,7 @@
       </c>
     </row>
     <row r="241" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A241" s="24">
+      <c r="A241" s="23">
         <v>1147803256</v>
       </c>
       <c r="B241" s="18" t="s">
@@ -5763,7 +5760,7 @@
       </c>
     </row>
     <row r="242" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A242" s="25">
+      <c r="A242" s="24">
         <v>1147817827</v>
       </c>
       <c r="B242" s="13" t="s">
@@ -5777,7 +5774,7 @@
       </c>
     </row>
     <row r="243" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A243" s="25">
+      <c r="A243" s="24">
         <v>2317822274</v>
       </c>
       <c r="B243" s="13" t="s">
@@ -5791,7 +5788,7 @@
       </c>
     </row>
     <row r="244" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A244" s="25">
+      <c r="A244" s="24">
         <v>2368543738</v>
       </c>
       <c r="B244" s="13" t="s">
@@ -5805,7 +5802,7 @@
       </c>
     </row>
     <row r="245" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A245" s="25">
+      <c r="A245" s="24">
         <v>1147244998</v>
       </c>
       <c r="B245" s="13" t="s">
@@ -5819,7 +5816,7 @@
       </c>
     </row>
     <row r="246" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A246" s="25">
+      <c r="A246" s="24">
         <v>1147138414</v>
       </c>
       <c r="B246" s="13" t="s">
@@ -5833,7 +5830,7 @@
       </c>
     </row>
     <row r="247" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A247" s="25">
+      <c r="A247" s="24">
         <v>1147800385</v>
       </c>
       <c r="B247" s="13" t="s">
@@ -5847,7 +5844,7 @@
       </c>
     </row>
     <row r="248" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A248" s="25">
+      <c r="A248" s="24">
         <v>1145124374</v>
       </c>
       <c r="B248" s="13" t="s">
@@ -5861,7 +5858,7 @@
       </c>
     </row>
     <row r="249" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A249" s="25">
+      <c r="A249" s="24">
         <v>1146362445</v>
       </c>
       <c r="B249" s="13" t="s">
@@ -5875,7 +5872,7 @@
       </c>
     </row>
     <row r="250" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A250" s="25">
+      <c r="A250" s="24">
         <v>1149064972</v>
       </c>
       <c r="B250" s="13" t="s">
@@ -5889,7 +5886,7 @@
       </c>
     </row>
     <row r="251" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A251" s="25">
+      <c r="A251" s="24">
         <v>1146726300</v>
       </c>
       <c r="B251" s="13" t="s">
@@ -5903,7 +5900,7 @@
       </c>
     </row>
     <row r="252" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A252" s="25">
+      <c r="A252" s="24">
         <v>1149452821</v>
       </c>
       <c r="B252" s="13" t="s">
@@ -5917,7 +5914,7 @@
       </c>
     </row>
     <row r="253" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A253" s="25">
+      <c r="A253" s="24">
         <v>1146907470</v>
       </c>
       <c r="B253" s="13" t="s">
@@ -5931,7 +5928,7 @@
       </c>
     </row>
     <row r="254" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A254" s="25">
+      <c r="A254" s="24">
         <v>1145545081</v>
       </c>
       <c r="B254" s="13" t="s">
@@ -5945,7 +5942,7 @@
       </c>
     </row>
     <row r="255" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A255" s="25">
+      <c r="A255" s="24">
         <v>1149931006</v>
       </c>
       <c r="B255" s="13" t="s">
@@ -5959,7 +5956,7 @@
       </c>
     </row>
     <row r="256" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A256" s="25">
+      <c r="A256" s="24">
         <v>2277240962</v>
       </c>
       <c r="B256" s="13" t="s">
@@ -5973,7 +5970,7 @@
       </c>
     </row>
     <row r="257" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A257" s="25">
+      <c r="A257" s="24">
         <v>1145922330</v>
       </c>
       <c r="B257" s="13" t="s">
@@ -5987,7 +5984,7 @@
       </c>
     </row>
     <row r="258" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A258" s="25">
+      <c r="A258" s="24">
         <v>1168345146</v>
       </c>
       <c r="B258" s="13" t="s">
@@ -6001,7 +5998,7 @@
       </c>
     </row>
     <row r="259" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A259" s="25">
+      <c r="A259" s="24">
         <v>2395502558</v>
       </c>
       <c r="B259" s="13" t="s">
@@ -6015,7 +6012,7 @@
       </c>
     </row>
     <row r="260" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A260" s="25">
+      <c r="A260" s="24">
         <v>1146162415</v>
       </c>
       <c r="B260" s="13" t="s">
@@ -6029,7 +6026,7 @@
       </c>
     </row>
     <row r="261" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A261" s="25">
+      <c r="A261" s="24">
         <v>1152946875</v>
       </c>
       <c r="B261" s="13" t="s">
@@ -6043,7 +6040,7 @@
       </c>
     </row>
     <row r="262" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A262" s="25">
+      <c r="A262" s="24">
         <v>1150772208</v>
       </c>
       <c r="B262" s="13" t="s">
@@ -6057,7 +6054,7 @@
       </c>
     </row>
     <row r="263" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A263" s="25">
+      <c r="A263" s="24">
         <v>1148980897</v>
       </c>
       <c r="B263" s="13" t="s">
@@ -6071,7 +6068,7 @@
       </c>
     </row>
     <row r="264" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A264" s="25">
+      <c r="A264" s="24">
         <v>1146607773</v>
       </c>
       <c r="B264" s="13" t="s">
@@ -6085,7 +6082,7 @@
       </c>
     </row>
     <row r="265" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A265" s="25">
+      <c r="A265" s="24">
         <v>1146979255</v>
       </c>
       <c r="B265" s="13" t="s">
@@ -6099,7 +6096,7 @@
       </c>
     </row>
     <row r="266" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A266" s="25">
+      <c r="A266" s="24">
         <v>1149811893</v>
       </c>
       <c r="B266" s="13" t="s">
@@ -6113,7 +6110,7 @@
       </c>
     </row>
     <row r="267" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A267" s="27">
+      <c r="A267" s="26">
         <v>1149339077</v>
       </c>
       <c r="B267" s="19" t="s">
@@ -6127,7 +6124,7 @@
       </c>
     </row>
     <row r="268" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A268" s="27">
+      <c r="A268" s="26">
         <v>1149508598</v>
       </c>
       <c r="B268" s="22" t="s">
@@ -6141,7 +6138,7 @@
       </c>
     </row>
     <row r="269" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A269" s="27">
+      <c r="A269" s="26">
         <v>1147789356</v>
       </c>
       <c r="B269" s="22" t="s">
@@ -6155,7 +6152,7 @@
       </c>
     </row>
     <row r="270" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A270" s="27">
+      <c r="A270" s="26">
         <v>1146611726</v>
       </c>
       <c r="B270" s="22" t="s">
@@ -6169,7 +6166,7 @@
       </c>
     </row>
     <row r="271" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A271" s="27">
+      <c r="A271" s="26">
         <v>1147262016</v>
       </c>
       <c r="B271" s="22" t="s">
@@ -6183,7 +6180,7 @@
       </c>
     </row>
     <row r="272" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A272" s="27">
+      <c r="A272" s="26">
         <v>1147494130</v>
       </c>
       <c r="B272" s="22" t="s">
@@ -6197,7 +6194,7 @@
       </c>
     </row>
     <row r="273" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A273" s="27">
+      <c r="A273" s="26">
         <v>1148272907</v>
       </c>
       <c r="B273" s="22" t="s">
@@ -6211,7 +6208,7 @@
       </c>
     </row>
     <row r="274" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A274" s="27">
+      <c r="A274" s="26">
         <v>1149254607</v>
       </c>
       <c r="B274" s="22" t="s">
@@ -6225,7 +6222,7 @@
       </c>
     </row>
     <row r="275" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A275" s="27">
+      <c r="A275" s="26">
         <v>1149049734</v>
       </c>
       <c r="B275" s="22" t="s">
@@ -6239,7 +6236,7 @@
       </c>
     </row>
     <row r="276" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A276" s="27">
+      <c r="A276" s="26">
         <v>1147396244</v>
       </c>
       <c r="B276" s="22" t="s">
@@ -6253,7 +6250,7 @@
       </c>
     </row>
     <row r="277" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A277" s="27">
+      <c r="A277" s="26">
         <v>1146310931</v>
       </c>
       <c r="B277" s="22" t="s">
@@ -6267,7 +6264,7 @@
       </c>
     </row>
     <row r="278" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A278" s="27">
+      <c r="A278" s="26">
         <v>1145927230</v>
       </c>
       <c r="B278" s="22" t="s">
@@ -6281,7 +6278,7 @@
       </c>
     </row>
     <row r="279" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A279" s="27">
+      <c r="A279" s="26">
         <v>1148274754</v>
       </c>
       <c r="B279" s="22" t="s">
@@ -6295,7 +6292,7 @@
       </c>
     </row>
     <row r="280" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A280" s="27">
+      <c r="A280" s="26">
         <v>1147544322</v>
       </c>
       <c r="B280" s="22" t="s">
@@ -6309,7 +6306,7 @@
       </c>
     </row>
     <row r="281" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A281" s="27">
+      <c r="A281" s="26">
         <v>1146374598</v>
       </c>
       <c r="B281" s="22" t="s">
@@ -6323,7 +6320,7 @@
       </c>
     </row>
     <row r="282" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A282" s="27">
+      <c r="A282" s="26">
         <v>1150177127</v>
       </c>
       <c r="B282" s="22" t="s">
@@ -6337,7 +6334,7 @@
       </c>
     </row>
     <row r="283" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A283" s="27">
+      <c r="A283" s="26">
         <v>1147539728</v>
       </c>
       <c r="B283" s="22" t="s">
@@ -6351,7 +6348,7 @@
       </c>
     </row>
     <row r="284" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A284" s="27">
+      <c r="A284" s="26">
         <v>1147293839</v>
       </c>
       <c r="B284" s="22" t="s">
@@ -6365,7 +6362,7 @@
       </c>
     </row>
     <row r="285" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A285" s="27">
+      <c r="A285" s="26">
         <v>1148251356</v>
       </c>
       <c r="B285" s="22" t="s">
@@ -6379,7 +6376,7 @@
       </c>
     </row>
     <row r="286" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A286" s="27">
+      <c r="A286" s="26">
         <v>1147637472</v>
       </c>
       <c r="B286" s="22" t="s">
@@ -6393,7 +6390,7 @@
       </c>
     </row>
     <row r="287" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A287" s="27">
+      <c r="A287" s="26">
         <v>1149530295</v>
       </c>
       <c r="B287" s="22" t="s">
@@ -6407,7 +6404,7 @@
       </c>
     </row>
     <row r="288" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A288" s="27">
+      <c r="A288" s="26">
         <v>1148778382</v>
       </c>
       <c r="B288" s="22" t="s">
@@ -6421,7 +6418,7 @@
       </c>
     </row>
     <row r="289" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A289" s="27">
+      <c r="A289" s="26">
         <v>1147236846</v>
       </c>
       <c r="B289" s="22" t="s">
@@ -6435,7 +6432,7 @@
       </c>
     </row>
     <row r="290" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A290" s="27">
+      <c r="A290" s="26">
         <v>2389352689</v>
       </c>
       <c r="B290" s="22" t="s">
@@ -6449,7 +6446,7 @@
       </c>
     </row>
     <row r="291" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A291" s="27">
+      <c r="A291" s="26">
         <v>2319640955</v>
       </c>
       <c r="B291" s="22" t="s">

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B85E2EA-5343-4D6B-A808-5984E1F6E2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D6FDD-88AE-4774-A517-3E151DE71BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1166,13 +1177,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12860</xdr:col>
+      <xdr:col>12858</xdr:col>
       <xdr:colOff>270503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1210,13 +1221,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>416553</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1254,13 +1265,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>16503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1298,13 +1309,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1342,13 +1353,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>441953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1386,13 +1397,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12860</xdr:col>
+      <xdr:col>12858</xdr:col>
       <xdr:colOff>270503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1430,13 +1441,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>416553</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1474,13 +1485,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>16503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1518,13 +1529,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1562,13 +1573,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>441953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -1606,13 +1617,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1650,13 +1661,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>187953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1694,13 +1705,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>397503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1738,13 +1749,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>422903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1782,13 +1793,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>213353</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1826,13 +1837,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12861</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1870,13 +1881,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>187953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1914,13 +1925,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>397503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12865</xdr:col>
+      <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1958,13 +1969,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>422903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12866</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2002,13 +2013,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>213353</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12867</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D6FDD-88AE-4774-A517-3E151DE71BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A036CC7D-ACB0-4EEA-BBCC-08A8F2522774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -938,14 +938,6 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -981,8 +973,14 @@
       <color theme="1"/>
       <name val="Sakkal Majalla"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -995,8 +993,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1005,49 +1009,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1056,106 +1027,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1185,8 +1125,8 @@
     <xdr:to>
       <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1229,8 +1169,8 @@
     <xdr:to>
       <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1273,8 +1213,8 @@
     <xdr:to>
       <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1317,8 +1257,8 @@
     <xdr:to>
       <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1361,8 +1301,8 @@
     <xdr:to>
       <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1405,8 +1345,8 @@
     <xdr:to>
       <xdr:col>12859</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1449,8 +1389,8 @@
     <xdr:to>
       <xdr:col>12860</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1493,8 +1433,8 @@
     <xdr:to>
       <xdr:col>12863</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1537,8 +1477,8 @@
     <xdr:to>
       <xdr:col>12864</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1581,8 +1521,8 @@
     <xdr:to>
       <xdr:col>12865</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2374,22 +2314,22 @@
   <dimension ref="A1:F291"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6328125" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -2398,2666 +2338,3040 @@
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="23">
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A2" s="4">
         <v>1150436838</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="C2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="8">
         <v>966554289816</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="24">
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="4">
         <v>1152217368</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="8">
         <v>966556732717</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="24">
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A4" s="4">
         <v>1152502371</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11">
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A5" s="24">
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A5" s="4">
         <v>1152327969</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="C5" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="24">
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A6" s="4">
         <v>2302448127</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="C6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A7" s="24">
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A7" s="4">
         <v>1153472889</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="C7" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A8" s="24">
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="4">
         <v>1152518682</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="C8" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A9" s="24">
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A9" s="4">
         <v>1158331023</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="C9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="24">
+      <c r="E9" s="11"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A10" s="4">
         <v>1157900240</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="24">
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="4">
         <v>1150731048</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="C11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A12" s="24">
+      <c r="E11" s="11"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="4">
         <v>2293198442</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A13" s="24">
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="4">
         <v>1174946861</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A14" s="24">
+      <c r="E13" s="11"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A14" s="4">
         <v>1152820641</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A15" s="24">
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A15" s="4">
         <v>1149366963</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="C15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="24">
+      <c r="E15" s="11"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A16" s="4">
         <v>1152734123</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="24">
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A17" s="4">
         <v>1152480891</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11">
+      <c r="C17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A18" s="24">
+      <c r="E17" s="11"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A18" s="4">
         <v>1153507684</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="11">
+      <c r="C18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="24">
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A19" s="4">
         <v>1150008413</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="C19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A20" s="24">
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A20" s="4">
         <v>1152989354</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="11">
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A21" s="24">
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A21" s="4">
         <v>1152061618</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11">
+      <c r="C21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="24">
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="4">
         <v>1149206417</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="C22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A23" s="24">
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A23" s="4">
         <v>1151880513</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="11">
+      <c r="C23" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A24" s="24">
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A24" s="4">
         <v>2290421144</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="11">
+      <c r="C24" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A25" s="24">
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A25" s="4">
         <v>1160061816</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="11">
+      <c r="C25" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A26" s="25">
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A26" s="14">
         <v>1152890750</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="11">
+      <c r="C26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A27" s="24">
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A27" s="4">
         <v>1151773627</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="11">
+      <c r="C27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A28" s="24">
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A28" s="4">
         <v>1152536601</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="11">
+      <c r="C28" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A29" s="24">
+      <c r="E28" s="11"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A29" s="4">
         <v>1150018610</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="11">
+      <c r="C29" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A30" s="24">
+      <c r="E29" s="11"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A30" s="4">
         <v>1146587298</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="11">
+      <c r="C30" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A31" s="24">
+      <c r="E30" s="11"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A31" s="4">
         <v>1150743167</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="11">
+      <c r="C31" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A32" s="24">
+      <c r="E31" s="11"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A32" s="4">
         <v>1151146907</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11">
+      <c r="C32" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A33" s="24">
+      <c r="E32" s="11"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A33" s="4">
         <v>2443189093</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33" s="11">
+      <c r="C33" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A34" s="24">
+      <c r="E33" s="11"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A34" s="4">
         <v>1151434659</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="11">
+      <c r="C34" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A35" s="24">
+      <c r="E34" s="11"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A35" s="4">
         <v>1152565972</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="C35" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A36" s="24">
+      <c r="E35" s="11"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A36" s="4">
         <v>1154025124</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="C36" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A37" s="24">
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A37" s="4">
         <v>1154153991</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37" s="11">
+      <c r="C37" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A38" s="24">
+      <c r="E37" s="11"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A38" s="4">
         <v>1149486605</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="11">
+      <c r="C38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A39" s="24">
+      <c r="E38" s="11"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A39" s="4">
         <v>1152472815</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="C39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A40" s="24">
+      <c r="E39" s="11"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A40" s="4">
         <v>1150396164</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="11">
+      <c r="C40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A41" s="24">
+      <c r="E40" s="11"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A41" s="4">
         <v>1150491064</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="11">
+      <c r="C41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A42" s="24">
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A42" s="4">
         <v>1152786958</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="11">
+      <c r="C42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A43" s="24">
+      <c r="E42" s="11"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A43" s="4">
         <v>1149922534</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43" s="11">
+      <c r="C43" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A44" s="24">
+      <c r="E43" s="11"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A44" s="4">
         <v>2269053001</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="11">
+      <c r="C44" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A45" s="24">
+      <c r="E44" s="11"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A45" s="4">
         <v>1157238989</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11">
+      <c r="C45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A46" s="24">
+      <c r="E45" s="11"/>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A46" s="4">
         <v>1153155559</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="11">
+      <c r="C46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A47" s="24">
+      <c r="E46" s="11"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A47" s="4">
         <v>1149465245</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="11">
+      <c r="C47" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A48" s="24">
+      <c r="E47" s="11"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A48" s="4">
         <v>1155938150</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="11">
+      <c r="C48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="24">
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A49" s="4">
         <v>1149696633</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="11">
+      <c r="C49" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="24">
+      <c r="E49" s="11"/>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A50" s="4">
         <v>1155454240</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="11">
+      <c r="C50" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A51" s="24">
+      <c r="E50" s="11"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A51" s="4">
         <v>1150039038</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="11">
+      <c r="C51" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A52" s="24">
+      <c r="E51" s="11"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A52" s="4">
         <v>1152218085</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="11">
+      <c r="C52" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A53" s="24">
+      <c r="E52" s="11"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A53" s="4">
         <v>1147013252</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="11">
+      <c r="C53" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A54" s="24">
+      <c r="E53" s="11"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A54" s="4">
         <v>1154169450</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="11">
+      <c r="C54" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A55" s="24">
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A55" s="4">
         <v>1151233614</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="11">
+      <c r="C55" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A56" s="24">
+      <c r="E55" s="11"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A56" s="4">
         <v>1151650809</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="11">
+      <c r="C56" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="24">
+      <c r="E56" s="11"/>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A57" s="4">
         <v>1151119201</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="11">
+      <c r="C57" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="24">
+      <c r="E57" s="11"/>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A58" s="4">
         <v>1152878417</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="11">
+      <c r="C58" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A59" s="24">
+      <c r="E58" s="11"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A59" s="4">
         <v>1152574958</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="11">
+      <c r="C59" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A60" s="24">
+      <c r="E59" s="11"/>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A60" s="4">
         <v>1152986681</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="11">
+      <c r="C60" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A61" s="24">
+      <c r="E60" s="11"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A61" s="4">
         <v>1151154455</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="11">
+      <c r="C61" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A62" s="24">
+      <c r="E61" s="11"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A62" s="4">
         <v>1159289287</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="11">
+      <c r="C62" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A63" s="24">
+      <c r="E62" s="11"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A63" s="4">
         <v>1153334618</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="11">
+      <c r="C63" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A64" s="24">
+      <c r="E63" s="11"/>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A64" s="4">
         <v>1152212658</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="11">
+      <c r="C64" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A65" s="24">
+      <c r="E64" s="11"/>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A65" s="4">
         <v>1152410336</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="11">
+      <c r="C65" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A66" s="24">
+      <c r="E65" s="11"/>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A66" s="4">
         <v>1154207904</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="11">
+      <c r="C66" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A67" s="24">
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A67" s="4">
         <v>1168345245</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" s="11">
+      <c r="C67" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A68" s="24">
+      <c r="E67" s="11"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A68" s="4">
         <v>1149893040</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="11">
+      <c r="C68" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A69" s="24">
+      <c r="E68" s="11"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A69" s="4">
         <v>1151849807</v>
       </c>
       <c r="B69" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" s="11">
+      <c r="C69" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A70" s="24">
+      <c r="E69" s="11"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A70" s="4">
         <v>1152284103</v>
       </c>
       <c r="B70" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="11">
+      <c r="C70" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A71" s="24">
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A71" s="4">
         <v>1167082591</v>
       </c>
       <c r="B71" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="11">
+      <c r="C71" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A72" s="24">
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A72" s="4">
         <v>1153479645</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" s="11">
+      <c r="C72" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A73" s="24">
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A73" s="4">
         <v>1155524893</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" s="11">
+      <c r="C73" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A74" s="24">
+      <c r="E73" s="11"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A74" s="4">
         <v>1150599171</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D74" s="11">
+      <c r="C74" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A75" s="24">
+      <c r="E74" s="11"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A75" s="4">
         <v>1154873481</v>
       </c>
       <c r="B75" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D75" s="11">
+      <c r="C75" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A76" s="24">
+      <c r="E75" s="11"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A76" s="4">
         <v>1152884167</v>
       </c>
       <c r="B76" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76" s="11">
+      <c r="C76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A77" s="24">
+      <c r="E76" s="11"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A77" s="4">
         <v>1152128029</v>
       </c>
       <c r="B77" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77" s="11">
+      <c r="C77" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A78" s="24">
+      <c r="E77" s="11"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A78" s="4">
         <v>1151910013</v>
       </c>
       <c r="B78" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D78" s="11">
+      <c r="C78" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A79" s="24">
+      <c r="E78" s="11"/>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A79" s="4">
         <v>1154287575</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79" s="11">
+      <c r="C79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A80" s="24">
+      <c r="E79" s="11"/>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A80" s="4">
         <v>1152571822</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="11">
+      <c r="C80" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A81" s="24">
+      <c r="E80" s="11"/>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A81" s="4">
         <v>1150680112</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D81" s="11">
+      <c r="C81" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A82" s="24">
+      <c r="E81" s="11"/>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A82" s="4">
         <v>1150690798</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D82" s="11">
+      <c r="C82" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A83" s="24">
+      <c r="E82" s="11"/>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A83" s="4">
         <v>1151961511</v>
       </c>
       <c r="B83" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D83" s="11">
+      <c r="C83" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A84" s="24">
+      <c r="E83" s="11"/>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A84" s="4">
         <v>1149761460</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="11">
+      <c r="C84" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A85" s="24">
+      <c r="E84" s="11"/>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A85" s="4">
         <v>2297211076</v>
       </c>
       <c r="B85" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="11">
+      <c r="C85" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A86" s="24">
+      <c r="E85" s="11"/>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A86" s="4">
         <v>1153216211</v>
       </c>
       <c r="B86" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D86" s="11">
+      <c r="C86" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A87" s="24">
+      <c r="E86" s="11"/>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A87" s="4">
         <v>1152536460</v>
       </c>
       <c r="B87" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D87" s="11">
+      <c r="C87" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A88" s="24">
+      <c r="E87" s="11"/>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A88" s="4">
         <v>1152152763</v>
       </c>
       <c r="B88" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D88" s="11">
+      <c r="C88" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A89" s="24">
+      <c r="E88" s="11"/>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A89" s="4">
         <v>1156092080</v>
       </c>
       <c r="B89" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D89" s="11">
+      <c r="C89" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A90" s="24">
+      <c r="E89" s="11"/>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A90" s="4">
         <v>2510170026</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90" s="11">
+      <c r="C90" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A91" s="24">
+      <c r="E90" s="11"/>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A91" s="4">
         <v>1151404256</v>
       </c>
       <c r="B91" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D91" s="11">
+      <c r="C91" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A92" s="24">
+      <c r="E91" s="11"/>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A92" s="4">
         <v>1152224984</v>
       </c>
       <c r="B92" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D92" s="11">
+      <c r="C92" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D92" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A93" s="24">
+      <c r="E92" s="11"/>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A93" s="4">
         <v>1150781068</v>
       </c>
       <c r="B93" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93" s="11">
+      <c r="C93" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A94" s="24">
+      <c r="E93" s="11"/>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A94" s="4">
         <v>1150218970</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D94" s="11">
+      <c r="C94" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A95" s="24">
+      <c r="E94" s="11"/>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A95" s="4">
         <v>1153072044</v>
       </c>
       <c r="B95" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="11">
+      <c r="C95" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A96" s="24">
+      <c r="E95" s="11"/>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A96" s="4">
         <v>1153072069</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D96" s="11">
+      <c r="C96" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D96" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A97" s="24">
+      <c r="E96" s="11"/>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A97" s="4">
         <v>1149401059</v>
       </c>
       <c r="B97" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D97" s="11">
+      <c r="C97" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A98" s="24">
+      <c r="E97" s="11"/>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A98" s="4">
         <v>1153495591</v>
       </c>
       <c r="B98" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98" s="11">
+      <c r="C98" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A99" s="24">
+      <c r="E98" s="11"/>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A99" s="4">
         <v>1150973210</v>
       </c>
       <c r="B99" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D99" s="11">
+      <c r="C99" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A100" s="24">
+      <c r="E99" s="11"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A100" s="4">
         <v>1151704598</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="11">
+      <c r="C100" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A101" s="24">
+      <c r="E100" s="11"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A101" s="4">
         <v>1151845870</v>
       </c>
       <c r="B101" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D101" s="11">
+      <c r="C101" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A102" s="24">
+      <c r="E101" s="11"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A102" s="4">
         <v>1149888925</v>
       </c>
       <c r="B102" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D102" s="11">
+      <c r="C102" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A103" s="24">
+      <c r="E102" s="11"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A103" s="4">
         <v>1153380116</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D103" s="11">
+      <c r="C103" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A104" s="24">
+      <c r="E103" s="11"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A104" s="4">
         <v>1152305007</v>
       </c>
       <c r="B104" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D104" s="11">
+      <c r="C104" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A105" s="24">
+      <c r="E104" s="11"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A105" s="4">
         <v>1153607922</v>
       </c>
       <c r="B105" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D105" s="11">
+      <c r="C105" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A106" s="24">
+      <c r="E105" s="11"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A106" s="4">
         <v>1152853493</v>
       </c>
       <c r="B106" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D106" s="11">
+      <c r="C106" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A107" s="24">
+      <c r="E106" s="11"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A107" s="4">
         <v>1153534167</v>
       </c>
       <c r="B107" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D107" s="11">
+      <c r="C107" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D107" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A108" s="24">
+      <c r="E107" s="11"/>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A108" s="4">
         <v>1149855445</v>
       </c>
       <c r="B108" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D108" s="11">
+      <c r="C108" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A109" s="24">
+      <c r="E108" s="11"/>
+      <c r="F108" s="12"/>
+    </row>
+    <row r="109" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A109" s="4">
         <v>1153291388</v>
       </c>
       <c r="B109" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D109" s="11">
+      <c r="C109" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D109" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A110" s="24">
+      <c r="E109" s="11"/>
+      <c r="F109" s="12"/>
+    </row>
+    <row r="110" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A110" s="4">
         <v>1151814371</v>
       </c>
       <c r="B110" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110" s="11">
+      <c r="C110" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A111" s="24">
+      <c r="E110" s="11"/>
+      <c r="F110" s="12"/>
+    </row>
+    <row r="111" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A111" s="4">
         <v>1158612646</v>
       </c>
       <c r="B111" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D111" s="11">
+      <c r="C111" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D111" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A112" s="24">
+      <c r="E111" s="11"/>
+      <c r="F111" s="12"/>
+    </row>
+    <row r="112" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A112" s="4">
         <v>1151003728</v>
       </c>
       <c r="B112" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D112" s="11">
+      <c r="C112" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D112" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A113" s="24">
+      <c r="E112" s="11"/>
+      <c r="F112" s="12"/>
+    </row>
+    <row r="113" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A113" s="4">
         <v>1174052116</v>
       </c>
       <c r="B113" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D113" s="11">
+      <c r="C113" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A114" s="24">
+      <c r="E113" s="11"/>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A114" s="4">
         <v>1153013931</v>
       </c>
       <c r="B114" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D114" s="11">
+      <c r="C114" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D114" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A115" s="24">
+      <c r="E114" s="11"/>
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A115" s="4">
         <v>1150396081</v>
       </c>
       <c r="B115" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="11">
+      <c r="C115" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A116" s="24">
+      <c r="E115" s="11"/>
+      <c r="F115" s="12"/>
+    </row>
+    <row r="116" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A116" s="4">
         <v>1150690699</v>
       </c>
       <c r="B116" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D116" s="11">
+      <c r="C116" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A117" s="24">
+      <c r="E116" s="11"/>
+      <c r="F116" s="12"/>
+    </row>
+    <row r="117" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A117" s="4">
         <v>1152698252</v>
       </c>
       <c r="B117" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D117" s="11">
+      <c r="C117" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A118" s="24">
+      <c r="E117" s="11"/>
+      <c r="F117" s="12"/>
+    </row>
+    <row r="118" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A118" s="4">
         <v>1153384795</v>
       </c>
       <c r="B118" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D118" s="11">
+      <c r="C118" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A119" s="24">
+      <c r="E118" s="11"/>
+      <c r="F118" s="12"/>
+    </row>
+    <row r="119" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A119" s="4">
         <v>1150304325</v>
       </c>
       <c r="B119" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D119" s="11">
+      <c r="C119" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A120" s="24">
+      <c r="E119" s="11"/>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A120" s="4">
         <v>1152915870</v>
       </c>
       <c r="B120" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="11">
+      <c r="C120" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A121" s="24">
+      <c r="E120" s="11"/>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A121" s="4">
         <v>1152367700</v>
       </c>
       <c r="B121" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D121" s="11">
+      <c r="C121" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A122" s="24">
+      <c r="E121" s="11"/>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A122" s="4">
         <v>1152775639</v>
       </c>
       <c r="B122" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D122" s="11">
+      <c r="C122" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D122" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A123" s="24">
+      <c r="E122" s="11"/>
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A123" s="4">
         <v>1149182303</v>
       </c>
       <c r="B123" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D123" s="11">
+      <c r="C123" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D123" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A124" s="24">
+      <c r="E123" s="11"/>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A124" s="4">
         <v>1149628024</v>
       </c>
       <c r="B124" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D124" s="11">
+      <c r="C124" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A125" s="24">
+      <c r="E124" s="11"/>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A125" s="4">
         <v>1152522833</v>
       </c>
       <c r="B125" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125" s="11">
+      <c r="C125" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A126" s="24">
+      <c r="E125" s="11"/>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A126" s="4">
         <v>2382166136</v>
       </c>
       <c r="B126" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D126" s="11">
+      <c r="C126" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D126" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A127" s="24">
+      <c r="E126" s="11"/>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A127" s="4">
         <v>1151669510</v>
       </c>
       <c r="B127" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D127" s="11">
+      <c r="C127" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D127" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A128" s="24">
+      <c r="E127" s="11"/>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A128" s="4">
         <v>1155012543</v>
       </c>
       <c r="B128" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D128" s="11">
+      <c r="C128" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D128" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A129" s="24">
+      <c r="E128" s="11"/>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A129" s="4">
         <v>1150763322</v>
       </c>
       <c r="B129" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D129" s="11">
+      <c r="C129" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A130" s="24">
+      <c r="E129" s="11"/>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A130" s="4">
         <v>1150527107</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130" s="11">
+      <c r="C130" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A131" s="24">
+      <c r="E130" s="11"/>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A131" s="4">
         <v>1171859398</v>
       </c>
       <c r="B131" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D131" s="11">
+      <c r="C131" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D131" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A132" s="24">
+      <c r="E131" s="11"/>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A132" s="4">
         <v>1151485529</v>
       </c>
       <c r="B132" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D132" s="11">
+      <c r="C132" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A133" s="24">
+      <c r="E132" s="11"/>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A133" s="4">
         <v>1153562317</v>
       </c>
       <c r="B133" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D133" s="11">
+      <c r="C133" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D133" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A134" s="24">
+      <c r="E133" s="11"/>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A134" s="4">
         <v>1153018385</v>
       </c>
       <c r="B134" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D134" s="11">
+      <c r="C134" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A135" s="24">
+      <c r="E134" s="11"/>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A135" s="4">
         <v>2288260736</v>
       </c>
       <c r="B135" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C135" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135" s="11">
+      <c r="C135" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A136" s="24">
+      <c r="E135" s="11"/>
+      <c r="F135" s="12"/>
+    </row>
+    <row r="136" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A136" s="4">
         <v>1152156905</v>
       </c>
       <c r="B136" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D136" s="11">
+      <c r="C136" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D136" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A137" s="24">
+      <c r="E136" s="11"/>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A137" s="4">
         <v>1152746895</v>
       </c>
       <c r="B137" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D137" s="11">
+      <c r="C137" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D137" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A138" s="24">
+      <c r="E137" s="11"/>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A138" s="4">
         <v>1153259260</v>
       </c>
       <c r="B138" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D138" s="11">
+      <c r="C138" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A139" s="24">
+      <c r="E138" s="11"/>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A139" s="4">
         <v>1153491590</v>
       </c>
       <c r="B139" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139" s="11">
+      <c r="C139" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A140" s="24">
+      <c r="E139" s="11"/>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A140" s="4">
         <v>1148755273</v>
       </c>
       <c r="B140" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D140" s="11">
+      <c r="C140" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D140" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A141" s="24">
+      <c r="E140" s="11"/>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A141" s="4">
         <v>1146774821</v>
       </c>
       <c r="B141" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D141" s="11">
+      <c r="C141" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A142" s="24">
+      <c r="E141" s="11"/>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A142" s="4">
         <v>1146165780</v>
       </c>
       <c r="B142" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D142" s="11">
+      <c r="C142" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A143" s="24">
+      <c r="E142" s="11"/>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A143" s="4">
         <v>1147913071</v>
       </c>
       <c r="B143" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D143" s="11">
+      <c r="C143" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A144" s="24">
+      <c r="E143" s="11"/>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A144" s="4">
         <v>1149665844</v>
       </c>
       <c r="B144" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C144" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D144" s="11">
+      <c r="C144" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A145" s="24">
+      <c r="E144" s="11"/>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A145" s="4">
         <v>2282375720</v>
       </c>
       <c r="B145" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D145" s="11">
+      <c r="C145" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A146" s="24">
+      <c r="E145" s="11"/>
+      <c r="F145" s="12"/>
+    </row>
+    <row r="146" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A146" s="4">
         <v>2415139746</v>
       </c>
       <c r="B146" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D146" s="11">
+      <c r="C146" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A147" s="24">
+      <c r="E146" s="11"/>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A147" s="4">
         <v>1146628035</v>
       </c>
       <c r="B147" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D147" s="11">
+      <c r="C147" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A148" s="24">
+      <c r="E147" s="11"/>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A148" s="4">
         <v>1148873159</v>
       </c>
       <c r="B148" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D148" s="11">
+      <c r="C148" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A149" s="24">
+      <c r="E148" s="11"/>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A149" s="4">
         <v>2275349674</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D149" s="11">
+      <c r="C149" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A150" s="24">
+      <c r="E149" s="11"/>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A150" s="4">
         <v>1145487730</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D150" s="11">
+      <c r="C150" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A151" s="24">
+      <c r="E150" s="11"/>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A151" s="4">
         <v>1146809536</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D151" s="11">
+      <c r="C151" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A152" s="24">
+      <c r="E151" s="11"/>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A152" s="4">
         <v>1164976993</v>
       </c>
       <c r="B152" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D152" s="11">
+      <c r="C152" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D152" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A153" s="24">
+      <c r="E152" s="11"/>
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A153" s="4">
         <v>1146821820</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C153" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D153" s="11">
+      <c r="C153" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D153" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A154" s="24">
+      <c r="E153" s="11"/>
+      <c r="F153" s="12"/>
+    </row>
+    <row r="154" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A154" s="4">
         <v>1146526668</v>
       </c>
       <c r="B154" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D154" s="11">
+      <c r="C154" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A155" s="24">
+      <c r="E154" s="11"/>
+      <c r="F154" s="12"/>
+    </row>
+    <row r="155" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A155" s="4">
         <v>1149762419</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D155" s="11">
+      <c r="C155" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D155" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A156" s="24">
+      <c r="E155" s="11"/>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A156" s="4">
         <v>1146972862</v>
       </c>
       <c r="B156" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D156" s="11">
+      <c r="C156" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D156" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A157" s="24">
+      <c r="E156" s="11"/>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A157" s="4">
         <v>1148273418</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D157" s="11">
+      <c r="C157" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D157" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A158" s="24">
+      <c r="E157" s="11"/>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="158" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A158" s="4">
         <v>1148688326</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D158" s="11">
+      <c r="C158" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D158" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A159" s="24">
+      <c r="E158" s="11"/>
+      <c r="F158" s="12"/>
+    </row>
+    <row r="159" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A159" s="4">
         <v>1146775844</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D159" s="11">
+      <c r="C159" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D159" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A160" s="24">
+      <c r="E159" s="11"/>
+      <c r="F159" s="12"/>
+    </row>
+    <row r="160" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A160" s="4">
         <v>2344822255</v>
       </c>
       <c r="B160" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C160" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D160" s="11">
+      <c r="C160" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A161" s="24">
+      <c r="E160" s="11"/>
+      <c r="F160" s="12"/>
+    </row>
+    <row r="161" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A161" s="4">
         <v>1150838223</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C161" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D161" s="11">
+      <c r="C161" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D161" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A162" s="24">
+      <c r="E161" s="11"/>
+      <c r="F161" s="12"/>
+    </row>
+    <row r="162" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A162" s="4">
         <v>1146376064</v>
       </c>
       <c r="B162" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D162" s="11">
+      <c r="C162" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D162" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A163" s="24">
+      <c r="E162" s="11"/>
+      <c r="F162" s="12"/>
+    </row>
+    <row r="163" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A163" s="4">
         <v>1144789813</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D163" s="11">
+      <c r="C163" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D163" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A164" s="24">
+      <c r="E163" s="11"/>
+      <c r="F163" s="12"/>
+    </row>
+    <row r="164" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A164" s="4">
         <v>1146471519</v>
       </c>
       <c r="B164" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D164" s="11">
+      <c r="C164" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D164" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A165" s="24">
+      <c r="E164" s="11"/>
+      <c r="F164" s="12"/>
+    </row>
+    <row r="165" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A165" s="4">
         <v>1145431654</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B165" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D165" s="11">
+      <c r="C165" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D165" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A166" s="24">
+      <c r="E165" s="11"/>
+      <c r="F165" s="12"/>
+    </row>
+    <row r="166" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A166" s="4">
         <v>1148252990</v>
       </c>
       <c r="B166" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D166" s="11">
+      <c r="C166" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D166" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A167" s="24">
+      <c r="E166" s="11"/>
+      <c r="F166" s="12"/>
+    </row>
+    <row r="167" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A167" s="4">
         <v>1149306225</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C167" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D167" s="11">
+      <c r="C167" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D167" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A168" s="24">
+      <c r="E167" s="11"/>
+      <c r="F167" s="12"/>
+    </row>
+    <row r="168" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A168" s="4">
         <v>1151264437</v>
       </c>
       <c r="B168" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D168" s="11">
+      <c r="C168" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D168" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A169" s="24">
+      <c r="E168" s="11"/>
+      <c r="F168" s="12"/>
+    </row>
+    <row r="169" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A169" s="4">
         <v>1150158754</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C169" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D169" s="11">
+      <c r="C169" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D169" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A170" s="24">
+      <c r="E169" s="11"/>
+      <c r="F169" s="12"/>
+    </row>
+    <row r="170" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A170" s="4">
         <v>1148596271</v>
       </c>
       <c r="B170" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C170" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D170" s="11">
+      <c r="C170" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D170" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A171" s="24">
+      <c r="E170" s="11"/>
+      <c r="F170" s="12"/>
+    </row>
+    <row r="171" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A171" s="4">
         <v>1147407355</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C171" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D171" s="11">
+      <c r="C171" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D171" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A172" s="24">
+      <c r="E171" s="11"/>
+      <c r="F171" s="12"/>
+    </row>
+    <row r="172" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A172" s="4">
         <v>1146987373</v>
       </c>
       <c r="B172" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D172" s="11">
+      <c r="C172" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D172" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A173" s="24">
+      <c r="E172" s="11"/>
+      <c r="F172" s="12"/>
+    </row>
+    <row r="173" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A173" s="4">
         <v>1142858388</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C173" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D173" s="11">
+      <c r="C173" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D173" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A174" s="24">
+      <c r="E173" s="11"/>
+      <c r="F173" s="12"/>
+    </row>
+    <row r="174" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A174" s="4">
         <v>1148535568</v>
       </c>
       <c r="B174" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C174" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D174" s="11">
+      <c r="C174" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D174" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A175" s="24">
+      <c r="E174" s="11"/>
+      <c r="F174" s="12"/>
+    </row>
+    <row r="175" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A175" s="4">
         <v>1147255028</v>
       </c>
       <c r="B175" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D175" s="11">
+      <c r="C175" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D175" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A176" s="24">
+      <c r="E175" s="11"/>
+      <c r="F175" s="12"/>
+    </row>
+    <row r="176" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A176" s="4">
         <v>1147682353</v>
       </c>
       <c r="B176" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C176" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D176" s="11">
+      <c r="C176" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D176" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A177" s="24">
+      <c r="E176" s="11"/>
+      <c r="F176" s="12"/>
+    </row>
+    <row r="177" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A177" s="4">
         <v>1146380868</v>
       </c>
       <c r="B177" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C177" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D177" s="11">
+      <c r="C177" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D177" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A178" s="24">
+      <c r="E177" s="11"/>
+      <c r="F177" s="12"/>
+    </row>
+    <row r="178" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A178" s="4">
         <v>1149234906</v>
       </c>
       <c r="B178" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D178" s="11">
+      <c r="C178" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D178" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A179" s="24">
+      <c r="E178" s="11"/>
+      <c r="F178" s="12"/>
+    </row>
+    <row r="179" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A179" s="4">
         <v>1145460539</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C179" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D179" s="11">
+      <c r="C179" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D179" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A180" s="24">
+      <c r="E179" s="11"/>
+      <c r="F179" s="12"/>
+    </row>
+    <row r="180" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A180" s="4">
         <v>1146879539</v>
       </c>
       <c r="B180" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C180" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D180" s="11">
+      <c r="C180" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D180" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A181" s="24">
+      <c r="E180" s="11"/>
+      <c r="F180" s="12"/>
+    </row>
+    <row r="181" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A181" s="4">
         <v>1146061013</v>
       </c>
       <c r="B181" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C181" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D181" s="11">
+      <c r="C181" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D181" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A182" s="24">
+      <c r="E181" s="11"/>
+      <c r="F181" s="12"/>
+    </row>
+    <row r="182" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A182" s="4">
         <v>1161327497</v>
       </c>
       <c r="B182" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C182" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D182" s="11">
+      <c r="C182" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D182" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A183" s="24">
+      <c r="E182" s="11"/>
+      <c r="F182" s="12"/>
+    </row>
+    <row r="183" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A183" s="4">
         <v>1146546294</v>
       </c>
       <c r="B183" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C183" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D183" s="11">
+      <c r="C183" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D183" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A184" s="24">
+      <c r="E183" s="11"/>
+      <c r="F183" s="12"/>
+    </row>
+    <row r="184" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A184" s="4">
         <v>1147314809</v>
       </c>
       <c r="B184" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C184" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D184" s="11">
+      <c r="C184" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D184" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A185" s="24">
+      <c r="E184" s="11"/>
+      <c r="F184" s="12"/>
+    </row>
+    <row r="185" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A185" s="4">
         <v>1148907890</v>
       </c>
       <c r="B185" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C185" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D185" s="11">
+      <c r="C185" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D185" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A186" s="24">
+      <c r="E185" s="11"/>
+      <c r="F185" s="12"/>
+    </row>
+    <row r="186" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A186" s="4">
         <v>1148220138</v>
       </c>
       <c r="B186" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C186" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D186" s="11">
+      <c r="C186" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D186" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A187" s="24">
+      <c r="E186" s="11"/>
+      <c r="F186" s="12"/>
+    </row>
+    <row r="187" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A187" s="4">
         <v>1149587360</v>
       </c>
       <c r="B187" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D187" s="11">
+      <c r="C187" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D187" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A188" s="24">
+      <c r="E187" s="11"/>
+      <c r="F187" s="12"/>
+    </row>
+    <row r="188" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A188" s="4">
         <v>1149826164</v>
       </c>
       <c r="B188" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D188" s="11">
+      <c r="C188" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D188" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A189" s="24">
+      <c r="E188" s="11"/>
+      <c r="F188" s="12"/>
+    </row>
+    <row r="189" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A189" s="4">
         <v>2337878892</v>
       </c>
       <c r="B189" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D189" s="11">
+      <c r="C189" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D189" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A190" s="24">
+      <c r="E189" s="11"/>
+      <c r="F189" s="12"/>
+    </row>
+    <row r="190" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A190" s="4">
         <v>1149812065</v>
       </c>
-      <c r="B190" s="15" t="s">
+      <c r="B190" s="13" t="s">
         <v>196</v>
       </c>
       <c r="C190" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D190" s="11">
+      <c r="D190" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A191" s="24">
+      <c r="E190" s="11"/>
+      <c r="F190" s="12"/>
+    </row>
+    <row r="191" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A191" s="4">
         <v>1147392706</v>
       </c>
       <c r="B191" s="13" t="s">
@@ -5066,12 +5380,14 @@
       <c r="C191" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A192" s="24">
+      <c r="E191" s="11"/>
+      <c r="F191" s="12"/>
+    </row>
+    <row r="192" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A192" s="4">
         <v>1145344212</v>
       </c>
       <c r="B192" s="13" t="s">
@@ -5080,12 +5396,14 @@
       <c r="C192" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D192" s="11">
+      <c r="D192" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A193" s="24">
+      <c r="E192" s="11"/>
+      <c r="F192" s="12"/>
+    </row>
+    <row r="193" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A193" s="4">
         <v>1151073234</v>
       </c>
       <c r="B193" s="13" t="s">
@@ -5094,1381 +5412,1579 @@
       <c r="C193" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A194" s="24">
+      <c r="E193" s="11"/>
+      <c r="F193" s="12"/>
+    </row>
+    <row r="194" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A194" s="4">
         <v>1149661421</v>
       </c>
-      <c r="B194" s="12" t="s">
+      <c r="B194" s="10" t="s">
         <v>200</v>
       </c>
       <c r="C194" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D194" s="11">
+      <c r="D194" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A195" s="24">
+      <c r="E194" s="11"/>
+      <c r="F194" s="12"/>
+    </row>
+    <row r="195" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A195" s="4">
         <v>1147116089</v>
       </c>
       <c r="B195" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D195" s="11">
+      <c r="C195" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D195" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A196" s="24">
+      <c r="E195" s="11"/>
+      <c r="F195" s="12"/>
+    </row>
+    <row r="196" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A196" s="4">
         <v>1147116014</v>
       </c>
       <c r="B196" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C196" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D196" s="11">
+      <c r="C196" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D196" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A197" s="24">
+      <c r="E196" s="11"/>
+      <c r="F196" s="12"/>
+    </row>
+    <row r="197" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A197" s="4">
         <v>1147138059</v>
       </c>
       <c r="B197" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D197" s="11">
+      <c r="C197" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D197" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A198" s="24">
+      <c r="E197" s="11"/>
+      <c r="F197" s="12"/>
+    </row>
+    <row r="198" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A198" s="4">
         <v>1146518921</v>
       </c>
       <c r="B198" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C198" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D198" s="11">
+      <c r="C198" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D198" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A199" s="24">
+      <c r="E198" s="11"/>
+      <c r="F198" s="12"/>
+    </row>
+    <row r="199" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A199" s="4">
         <v>1154144388</v>
       </c>
       <c r="B199" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D199" s="11">
+      <c r="C199" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D199" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A200" s="24">
+      <c r="E199" s="11"/>
+      <c r="F199" s="12"/>
+    </row>
+    <row r="200" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A200" s="4">
         <v>1147117111</v>
       </c>
-      <c r="B200" s="12" t="s">
+      <c r="B200" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D200" s="11">
+      <c r="C200" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D200" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A201" s="24">
+      <c r="E200" s="11"/>
+      <c r="F200" s="12"/>
+    </row>
+    <row r="201" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A201" s="4">
         <v>1147073637</v>
       </c>
       <c r="B201" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C201" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D201" s="11">
+      <c r="C201" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D201" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A202" s="24">
+      <c r="E201" s="11"/>
+      <c r="F201" s="12"/>
+    </row>
+    <row r="202" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A202" s="4">
         <v>1149366534</v>
       </c>
       <c r="B202" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D202" s="11">
+      <c r="C202" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D202" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A203" s="24">
+      <c r="E202" s="11"/>
+      <c r="F202" s="12"/>
+    </row>
+    <row r="203" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A203" s="4">
         <v>1151122668</v>
       </c>
       <c r="B203" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D203" s="11">
+      <c r="C203" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D203" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A204" s="24">
+      <c r="E203" s="11"/>
+      <c r="F203" s="12"/>
+    </row>
+    <row r="204" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A204" s="4">
         <v>1147318826</v>
       </c>
       <c r="B204" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C204" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D204" s="11">
+      <c r="C204" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D204" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A205" s="24">
+      <c r="E204" s="11"/>
+      <c r="F204" s="12"/>
+    </row>
+    <row r="205" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A205" s="4">
         <v>2282275516</v>
       </c>
       <c r="B205" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C205" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D205" s="11">
+      <c r="C205" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D205" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A206" s="24">
+      <c r="E205" s="11"/>
+      <c r="F205" s="12"/>
+    </row>
+    <row r="206" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A206" s="4">
         <v>1148331737</v>
       </c>
       <c r="B206" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C206" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D206" s="11">
+      <c r="C206" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D206" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A207" s="24">
+      <c r="E206" s="11"/>
+      <c r="F206" s="12"/>
+    </row>
+    <row r="207" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A207" s="4">
         <v>1148003252</v>
       </c>
       <c r="B207" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C207" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D207" s="11">
+      <c r="C207" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D207" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A208" s="24">
+      <c r="E207" s="11"/>
+      <c r="F207" s="12"/>
+    </row>
+    <row r="208" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A208" s="4">
         <v>1146792161</v>
       </c>
       <c r="B208" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C208" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D208" s="11">
+      <c r="C208" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D208" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A209" s="24">
+      <c r="E208" s="11"/>
+      <c r="F208" s="12"/>
+    </row>
+    <row r="209" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A209" s="4">
         <v>1148196452</v>
       </c>
       <c r="B209" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C209" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D209" s="11">
+      <c r="C209" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D209" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A210" s="24">
+      <c r="E209" s="11"/>
+      <c r="F209" s="12"/>
+    </row>
+    <row r="210" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A210" s="4">
         <v>1146902935</v>
       </c>
       <c r="B210" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="C210" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D210" s="11">
+      <c r="C210" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D210" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A211" s="24">
+      <c r="E210" s="11"/>
+      <c r="F210" s="12"/>
+    </row>
+    <row r="211" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A211" s="4">
         <v>1145718209</v>
       </c>
       <c r="B211" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C211" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D211" s="11">
+      <c r="C211" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A212" s="24">
+      <c r="E211" s="11"/>
+      <c r="F211" s="12"/>
+    </row>
+    <row r="212" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A212" s="4">
         <v>1148921412</v>
       </c>
       <c r="B212" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C212" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D212" s="11">
+      <c r="C212" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D212" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A213" s="24">
+      <c r="E212" s="11"/>
+      <c r="F212" s="12"/>
+    </row>
+    <row r="213" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A213" s="4">
         <v>1150070421</v>
       </c>
       <c r="B213" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C213" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D213" s="11">
+      <c r="C213" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D213" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A214" s="24">
+      <c r="E213" s="11"/>
+      <c r="F213" s="12"/>
+    </row>
+    <row r="214" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A214" s="4">
         <v>1169254040</v>
       </c>
       <c r="B214" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="C214" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D214" s="11">
+      <c r="C214" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D214" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A215" s="24">
+      <c r="E214" s="11"/>
+      <c r="F214" s="12"/>
+    </row>
+    <row r="215" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A215" s="4">
         <v>1145733752</v>
       </c>
       <c r="B215" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C215" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D215" s="11">
+      <c r="C215" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D215" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A216" s="24">
+      <c r="E215" s="11"/>
+      <c r="F215" s="12"/>
+    </row>
+    <row r="216" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A216" s="4">
         <v>1146851652</v>
       </c>
       <c r="B216" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C216" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D216" s="11">
+      <c r="C216" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D216" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A217" s="24">
+      <c r="E216" s="11"/>
+      <c r="F216" s="12"/>
+    </row>
+    <row r="217" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A217" s="4">
         <v>1146339948</v>
       </c>
       <c r="B217" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C217" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D217" s="11">
+      <c r="C217" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D217" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A218" s="24">
+      <c r="E217" s="11"/>
+      <c r="F217" s="12"/>
+    </row>
+    <row r="218" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A218" s="4">
         <v>1156163931</v>
       </c>
       <c r="B218" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C218" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D218" s="11">
+      <c r="C218" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D218" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A219" s="24">
+      <c r="E218" s="11"/>
+      <c r="F218" s="12"/>
+    </row>
+    <row r="219" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A219" s="4">
         <v>1148066275</v>
       </c>
       <c r="B219" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C219" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D219" s="11">
+      <c r="C219" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D219" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A220" s="24">
+      <c r="E219" s="11"/>
+      <c r="F219" s="12"/>
+    </row>
+    <row r="220" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A220" s="4">
         <v>1148850710</v>
       </c>
       <c r="B220" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="C220" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D220" s="11">
+      <c r="C220" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D220" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A221" s="24">
+      <c r="E220" s="11"/>
+      <c r="F220" s="12"/>
+    </row>
+    <row r="221" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A221" s="4">
         <v>1146399652</v>
       </c>
       <c r="B221" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C221" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D221" s="11">
+      <c r="C221" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D221" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A222" s="24">
+      <c r="E221" s="11"/>
+      <c r="F221" s="12"/>
+    </row>
+    <row r="222" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A222" s="4">
         <v>1148398181</v>
       </c>
       <c r="B222" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C222" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D222" s="11">
+      <c r="C222" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D222" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A223" s="24">
+      <c r="E222" s="11"/>
+      <c r="F222" s="12"/>
+    </row>
+    <row r="223" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A223" s="4">
         <v>1145648166</v>
       </c>
       <c r="B223" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C223" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D223" s="11">
+      <c r="C223" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D223" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A224" s="24">
+      <c r="E223" s="11"/>
+      <c r="F223" s="12"/>
+    </row>
+    <row r="224" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A224" s="4">
         <v>1147594236</v>
       </c>
       <c r="B224" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C224" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D224" s="11">
+      <c r="C224" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D224" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A225" s="24">
+      <c r="E224" s="11"/>
+      <c r="F224" s="12"/>
+    </row>
+    <row r="225" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A225" s="4">
         <v>1146766389</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C225" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D225" s="11">
+      <c r="C225" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D225" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A226" s="24">
+      <c r="E225" s="11"/>
+      <c r="F225" s="12"/>
+    </row>
+    <row r="226" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A226" s="4">
         <v>1148766015</v>
       </c>
-      <c r="B226" s="14" t="s">
+      <c r="B226" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C226" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D226" s="11">
+      <c r="C226" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D226" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A227" s="24">
+      <c r="E226" s="11"/>
+      <c r="F226" s="12"/>
+    </row>
+    <row r="227" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A227" s="4">
         <v>1161794449</v>
       </c>
       <c r="B227" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C227" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D227" s="11">
+      <c r="C227" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D227" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A228" s="24">
+      <c r="E227" s="11"/>
+      <c r="F227" s="12"/>
+    </row>
+    <row r="228" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A228" s="4">
         <v>1149400937</v>
       </c>
       <c r="B228" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C228" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D228" s="11">
+      <c r="C228" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D228" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A229" s="24">
+      <c r="E228" s="11"/>
+      <c r="F228" s="12"/>
+    </row>
+    <row r="229" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A229" s="4">
         <v>1148097148</v>
       </c>
       <c r="B229" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C229" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D229" s="11">
+      <c r="C229" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D229" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A230" s="24">
+      <c r="E229" s="11"/>
+      <c r="F229" s="12"/>
+    </row>
+    <row r="230" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A230" s="4">
         <v>1149512558</v>
       </c>
       <c r="B230" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C230" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D230" s="11">
+      <c r="C230" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D230" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A231" s="24">
+      <c r="E230" s="11"/>
+      <c r="F230" s="12"/>
+    </row>
+    <row r="231" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A231" s="4">
         <v>1148636135</v>
       </c>
       <c r="B231" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C231" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D231" s="11">
+      <c r="C231" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D231" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A232" s="24">
+      <c r="E231" s="11"/>
+      <c r="F231" s="12"/>
+    </row>
+    <row r="232" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A232" s="4">
         <v>1148833708</v>
       </c>
       <c r="B232" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="C232" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D232" s="11">
+      <c r="C232" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A233" s="24">
+      <c r="E232" s="11"/>
+      <c r="F232" s="12"/>
+    </row>
+    <row r="233" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A233" s="4">
         <v>1145244214</v>
       </c>
       <c r="B233" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C233" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D233" s="11">
+      <c r="C233" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D233" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A234" s="24">
+      <c r="E233" s="11"/>
+      <c r="F233" s="12"/>
+    </row>
+    <row r="234" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A234" s="4">
         <v>1149415935</v>
       </c>
       <c r="B234" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="C234" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D234" s="11">
+      <c r="C234" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D234" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A235" s="24">
+      <c r="E234" s="11"/>
+      <c r="F234" s="12"/>
+    </row>
+    <row r="235" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A235" s="4">
         <v>2282843446</v>
       </c>
       <c r="B235" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C235" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D235" s="11">
+      <c r="C235" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A236" s="24">
+      <c r="E235" s="11"/>
+      <c r="F235" s="12"/>
+    </row>
+    <row r="236" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A236" s="4">
         <v>1147952509</v>
       </c>
       <c r="B236" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="C236" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D236" s="11">
+      <c r="C236" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D236" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A237" s="24">
+      <c r="E236" s="11"/>
+      <c r="F236" s="12"/>
+    </row>
+    <row r="237" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A237" s="4">
         <v>1149342303</v>
       </c>
-      <c r="B237" s="17" t="s">
+      <c r="B237" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="C237" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D237" s="11">
+      <c r="C237" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D237" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A238" s="24">
+      <c r="E237" s="11"/>
+      <c r="F237" s="12"/>
+    </row>
+    <row r="238" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A238" s="4">
         <v>1147346579</v>
       </c>
       <c r="B238" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C238" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D238" s="11">
+      <c r="C238" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D238" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A239" s="24">
+      <c r="E238" s="11"/>
+      <c r="F238" s="12"/>
+    </row>
+    <row r="239" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A239" s="4">
         <v>1146982663</v>
       </c>
-      <c r="B239" s="17" t="s">
+      <c r="B239" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C239" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D239" s="11">
+      <c r="C239" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D239" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A240" s="24">
+      <c r="E239" s="11"/>
+      <c r="F239" s="12"/>
+    </row>
+    <row r="240" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A240" s="4">
         <v>1148895673</v>
       </c>
       <c r="B240" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="C240" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D240" s="11">
+      <c r="C240" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D240" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A241" s="23">
+      <c r="E240" s="11"/>
+      <c r="F240" s="12"/>
+    </row>
+    <row r="241" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A241" s="4">
         <v>1147803256</v>
       </c>
-      <c r="B241" s="18" t="s">
+      <c r="B241" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C241" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D241" s="8">
+      <c r="C241" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D241" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A242" s="24">
+      <c r="E241" s="11"/>
+      <c r="F241" s="12"/>
+    </row>
+    <row r="242" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A242" s="4">
         <v>1147817827</v>
       </c>
       <c r="B242" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C242" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D242" s="11">
+      <c r="C242" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D242" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A243" s="24">
+      <c r="E242" s="11"/>
+      <c r="F242" s="12"/>
+    </row>
+    <row r="243" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A243" s="4">
         <v>2317822274</v>
       </c>
       <c r="B243" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C243" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D243" s="11">
+      <c r="C243" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D243" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A244" s="24">
+      <c r="E243" s="11"/>
+      <c r="F243" s="12"/>
+    </row>
+    <row r="244" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A244" s="4">
         <v>2368543738</v>
       </c>
       <c r="B244" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="C244" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D244" s="11">
+      <c r="C244" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D244" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A245" s="24">
+      <c r="E244" s="11"/>
+      <c r="F244" s="12"/>
+    </row>
+    <row r="245" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A245" s="4">
         <v>1147244998</v>
       </c>
       <c r="B245" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C245" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D245" s="11">
+      <c r="C245" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D245" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A246" s="24">
+      <c r="E245" s="11"/>
+      <c r="F245" s="12"/>
+    </row>
+    <row r="246" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A246" s="4">
         <v>1147138414</v>
       </c>
       <c r="B246" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C246" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D246" s="11">
+      <c r="C246" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D246" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A247" s="24">
+      <c r="E246" s="11"/>
+      <c r="F246" s="12"/>
+    </row>
+    <row r="247" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A247" s="4">
         <v>1147800385</v>
       </c>
       <c r="B247" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C247" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D247" s="11">
+      <c r="C247" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D247" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A248" s="24">
+      <c r="E247" s="11"/>
+      <c r="F247" s="12"/>
+    </row>
+    <row r="248" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A248" s="4">
         <v>1145124374</v>
       </c>
       <c r="B248" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C248" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="11">
+      <c r="C248" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D248" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A249" s="24">
+      <c r="E248" s="11"/>
+      <c r="F248" s="12"/>
+    </row>
+    <row r="249" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A249" s="4">
         <v>1146362445</v>
       </c>
       <c r="B249" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C249" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D249" s="11">
+      <c r="C249" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D249" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A250" s="24">
+      <c r="E249" s="11"/>
+      <c r="F249" s="12"/>
+    </row>
+    <row r="250" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A250" s="4">
         <v>1149064972</v>
       </c>
       <c r="B250" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C250" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D250" s="11">
+      <c r="C250" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D250" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A251" s="24">
+      <c r="E250" s="11"/>
+      <c r="F250" s="12"/>
+    </row>
+    <row r="251" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A251" s="4">
         <v>1146726300</v>
       </c>
       <c r="B251" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C251" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D251" s="11">
+      <c r="C251" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D251" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A252" s="24">
+      <c r="E251" s="11"/>
+      <c r="F251" s="12"/>
+    </row>
+    <row r="252" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A252" s="4">
         <v>1149452821</v>
       </c>
       <c r="B252" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C252" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D252" s="11">
+      <c r="C252" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D252" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A253" s="24">
+      <c r="E252" s="11"/>
+      <c r="F252" s="12"/>
+    </row>
+    <row r="253" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A253" s="4">
         <v>1146907470</v>
       </c>
       <c r="B253" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D253" s="11">
+      <c r="C253" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D253" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A254" s="24">
+      <c r="E253" s="11"/>
+      <c r="F253" s="12"/>
+    </row>
+    <row r="254" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A254" s="4">
         <v>1145545081</v>
       </c>
       <c r="B254" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C254" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D254" s="11">
+      <c r="C254" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D254" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A255" s="24">
+      <c r="E254" s="11"/>
+      <c r="F254" s="12"/>
+    </row>
+    <row r="255" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A255" s="4">
         <v>1149931006</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="C255" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D255" s="11">
+      <c r="C255" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D255" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A256" s="24">
+      <c r="E255" s="11"/>
+      <c r="F255" s="12"/>
+    </row>
+    <row r="256" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A256" s="4">
         <v>2277240962</v>
       </c>
       <c r="B256" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C256" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D256" s="11">
+      <c r="C256" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D256" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A257" s="24">
+      <c r="E256" s="11"/>
+      <c r="F256" s="12"/>
+    </row>
+    <row r="257" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A257" s="4">
         <v>1145922330</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D257" s="11">
+      <c r="C257" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D257" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A258" s="24">
+      <c r="E257" s="11"/>
+      <c r="F257" s="12"/>
+    </row>
+    <row r="258" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A258" s="4">
         <v>1168345146</v>
       </c>
       <c r="B258" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="C258" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D258" s="11">
+      <c r="C258" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D258" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A259" s="24">
+      <c r="E258" s="11"/>
+      <c r="F258" s="12"/>
+    </row>
+    <row r="259" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A259" s="4">
         <v>2395502558</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="C259" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D259" s="11">
+      <c r="C259" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D259" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A260" s="24">
+      <c r="E259" s="11"/>
+      <c r="F259" s="12"/>
+    </row>
+    <row r="260" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A260" s="4">
         <v>1146162415</v>
       </c>
       <c r="B260" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C260" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D260" s="11">
+      <c r="C260" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D260" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A261" s="24">
+      <c r="E260" s="11"/>
+      <c r="F260" s="12"/>
+    </row>
+    <row r="261" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A261" s="4">
         <v>1152946875</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D261" s="11">
+      <c r="C261" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D261" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A262" s="24">
+      <c r="E261" s="11"/>
+      <c r="F261" s="12"/>
+    </row>
+    <row r="262" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A262" s="4">
         <v>1150772208</v>
       </c>
       <c r="B262" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="C262" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D262" s="11">
+      <c r="C262" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D262" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A263" s="24">
+      <c r="E262" s="11"/>
+      <c r="F262" s="12"/>
+    </row>
+    <row r="263" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A263" s="4">
         <v>1148980897</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="C263" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D263" s="11">
+      <c r="C263" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D263" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A264" s="24">
+      <c r="E263" s="11"/>
+      <c r="F263" s="12"/>
+    </row>
+    <row r="264" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A264" s="4">
         <v>1146607773</v>
       </c>
       <c r="B264" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="C264" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D264" s="11">
+      <c r="C264" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D264" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A265" s="24">
+      <c r="E264" s="11"/>
+      <c r="F264" s="12"/>
+    </row>
+    <row r="265" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A265" s="4">
         <v>1146979255</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C265" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D265" s="11">
+      <c r="C265" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D265" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A266" s="24">
+      <c r="E265" s="11"/>
+      <c r="F265" s="12"/>
+    </row>
+    <row r="266" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A266" s="4">
         <v>1149811893</v>
       </c>
       <c r="B266" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="C266" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D266" s="11">
+      <c r="C266" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D266" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A267" s="26">
+      <c r="E266" s="11"/>
+      <c r="F266" s="12"/>
+    </row>
+    <row r="267" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A267" s="17">
         <v>1149339077</v>
       </c>
-      <c r="B267" s="19" t="s">
+      <c r="B267" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C267" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D267" s="21">
+      <c r="C267" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D267" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A268" s="26">
+      <c r="E267" s="11"/>
+      <c r="F267" s="12"/>
+    </row>
+    <row r="268" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A268" s="17">
         <v>1149508598</v>
       </c>
-      <c r="B268" s="22" t="s">
+      <c r="B268" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="C268" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D268" s="21">
+      <c r="C268" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D268" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A269" s="26">
+      <c r="E268" s="11"/>
+      <c r="F268" s="12"/>
+    </row>
+    <row r="269" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A269" s="17">
         <v>1147789356</v>
       </c>
-      <c r="B269" s="22" t="s">
+      <c r="B269" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="C269" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D269" s="21">
+      <c r="C269" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D269" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A270" s="26">
+      <c r="E269" s="11"/>
+      <c r="F269" s="12"/>
+    </row>
+    <row r="270" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A270" s="17">
         <v>1146611726</v>
       </c>
-      <c r="B270" s="22" t="s">
+      <c r="B270" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C270" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D270" s="21">
+      <c r="C270" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D270" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A271" s="26">
+      <c r="E270" s="11"/>
+      <c r="F270" s="12"/>
+    </row>
+    <row r="271" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A271" s="17">
         <v>1147262016</v>
       </c>
-      <c r="B271" s="22" t="s">
+      <c r="B271" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="C271" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D271" s="21">
+      <c r="C271" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D271" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A272" s="26">
+      <c r="E271" s="11"/>
+      <c r="F271" s="12"/>
+    </row>
+    <row r="272" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A272" s="17">
         <v>1147494130</v>
       </c>
-      <c r="B272" s="22" t="s">
+      <c r="B272" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C272" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D272" s="21">
+      <c r="C272" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D272" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A273" s="26">
+      <c r="E272" s="11"/>
+      <c r="F272" s="12"/>
+    </row>
+    <row r="273" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A273" s="17">
         <v>1148272907</v>
       </c>
-      <c r="B273" s="22" t="s">
+      <c r="B273" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="C273" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D273" s="21">
+      <c r="C273" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D273" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A274" s="26">
+      <c r="E273" s="11"/>
+      <c r="F273" s="12"/>
+    </row>
+    <row r="274" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A274" s="17">
         <v>1149254607</v>
       </c>
-      <c r="B274" s="22" t="s">
+      <c r="B274" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C274" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D274" s="21">
+      <c r="C274" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D274" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A275" s="26">
+      <c r="E274" s="11"/>
+      <c r="F274" s="12"/>
+    </row>
+    <row r="275" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A275" s="17">
         <v>1149049734</v>
       </c>
-      <c r="B275" s="22" t="s">
+      <c r="B275" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C275" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D275" s="21">
+      <c r="C275" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D275" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A276" s="26">
+      <c r="E275" s="11"/>
+      <c r="F275" s="12"/>
+    </row>
+    <row r="276" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A276" s="17">
         <v>1147396244</v>
       </c>
-      <c r="B276" s="22" t="s">
+      <c r="B276" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C276" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D276" s="21">
+      <c r="C276" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D276" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A277" s="26">
+      <c r="E276" s="11"/>
+      <c r="F276" s="12"/>
+    </row>
+    <row r="277" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A277" s="17">
         <v>1146310931</v>
       </c>
-      <c r="B277" s="22" t="s">
+      <c r="B277" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="C277" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D277" s="21">
+      <c r="C277" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D277" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A278" s="26">
+      <c r="E277" s="11"/>
+      <c r="F277" s="12"/>
+    </row>
+    <row r="278" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A278" s="17">
         <v>1145927230</v>
       </c>
-      <c r="B278" s="22" t="s">
+      <c r="B278" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C278" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D278" s="21">
+      <c r="C278" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D278" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A279" s="26">
+      <c r="E278" s="11"/>
+      <c r="F278" s="12"/>
+    </row>
+    <row r="279" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A279" s="17">
         <v>1148274754</v>
       </c>
-      <c r="B279" s="22" t="s">
+      <c r="B279" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C279" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D279" s="21">
+      <c r="C279" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D279" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A280" s="26">
+      <c r="E279" s="11"/>
+      <c r="F279" s="12"/>
+    </row>
+    <row r="280" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A280" s="17">
         <v>1147544322</v>
       </c>
-      <c r="B280" s="22" t="s">
+      <c r="B280" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C280" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D280" s="21">
+      <c r="C280" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D280" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A281" s="26">
+      <c r="E280" s="11"/>
+      <c r="F280" s="12"/>
+    </row>
+    <row r="281" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A281" s="17">
         <v>1146374598</v>
       </c>
-      <c r="B281" s="22" t="s">
+      <c r="B281" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="C281" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D281" s="21">
+      <c r="C281" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D281" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A282" s="26">
+      <c r="E281" s="11"/>
+      <c r="F281" s="12"/>
+    </row>
+    <row r="282" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A282" s="17">
         <v>1150177127</v>
       </c>
-      <c r="B282" s="22" t="s">
+      <c r="B282" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C282" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D282" s="21">
+      <c r="C282" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D282" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A283" s="26">
+      <c r="E282" s="11"/>
+      <c r="F282" s="12"/>
+    </row>
+    <row r="283" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A283" s="17">
         <v>1147539728</v>
       </c>
-      <c r="B283" s="22" t="s">
+      <c r="B283" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="C283" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D283" s="21">
+      <c r="C283" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D283" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A284" s="26">
+      <c r="E283" s="11"/>
+      <c r="F283" s="12"/>
+    </row>
+    <row r="284" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A284" s="17">
         <v>1147293839</v>
       </c>
-      <c r="B284" s="22" t="s">
+      <c r="B284" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C284" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D284" s="21">
+      <c r="C284" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D284" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A285" s="26">
+      <c r="E284" s="11"/>
+      <c r="F284" s="12"/>
+    </row>
+    <row r="285" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A285" s="17">
         <v>1148251356</v>
       </c>
-      <c r="B285" s="22" t="s">
+      <c r="B285" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C285" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D285" s="21">
+      <c r="C285" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D285" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A286" s="26">
+      <c r="E285" s="11"/>
+      <c r="F285" s="12"/>
+    </row>
+    <row r="286" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A286" s="17">
         <v>1147637472</v>
       </c>
-      <c r="B286" s="22" t="s">
+      <c r="B286" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C286" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D286" s="21">
+      <c r="C286" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D286" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A287" s="26">
+      <c r="E286" s="11"/>
+      <c r="F286" s="12"/>
+    </row>
+    <row r="287" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A287" s="17">
         <v>1149530295</v>
       </c>
-      <c r="B287" s="22" t="s">
+      <c r="B287" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="C287" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D287" s="21">
+      <c r="C287" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D287" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A288" s="26">
+      <c r="E287" s="11"/>
+      <c r="F287" s="12"/>
+    </row>
+    <row r="288" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A288" s="17">
         <v>1148778382</v>
       </c>
-      <c r="B288" s="22" t="s">
+      <c r="B288" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="C288" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D288" s="21">
+      <c r="C288" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D288" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="289" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A289" s="26">
+      <c r="E288" s="11"/>
+      <c r="F288" s="12"/>
+    </row>
+    <row r="289" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A289" s="17">
         <v>1147236846</v>
       </c>
-      <c r="B289" s="22" t="s">
+      <c r="B289" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="C289" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D289" s="21">
+      <c r="C289" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D289" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="290" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A290" s="26">
+      <c r="E289" s="11"/>
+      <c r="F289" s="12"/>
+    </row>
+    <row r="290" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A290" s="17">
         <v>2389352689</v>
       </c>
-      <c r="B290" s="22" t="s">
+      <c r="B290" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="C290" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D290" s="21">
+      <c r="C290" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D290" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A291" s="26">
+      <c r="E290" s="11"/>
+      <c r="F290" s="12"/>
+    </row>
+    <row r="291" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A291" s="17">
         <v>2319640955</v>
       </c>
-      <c r="B291" s="22" t="s">
+      <c r="B291" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="C291" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D291" s="21">
+      <c r="C291" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D291" s="20">
         <v>6</v>
       </c>
+      <c r="E291" s="11"/>
+      <c r="F291" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A036CC7D-ACB0-4EEA-BBCC-08A8F2522774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB4B39F-7A73-4107-8987-F3E7CFA98FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="299">
   <si>
     <t>الأول الثانوي</t>
   </si>
@@ -930,13 +930,16 @@
   </si>
   <si>
     <t>يوسف محمود عبدالمجيد بخش</t>
+  </si>
+  <si>
+    <t>parent_phone</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -946,38 +949,34 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Sakkal Majalla"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Sakkal Majalla"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="Sakkal Majalla"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Sakkal Majalla"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Sakkal Majalla"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="Quote-cjk-patch"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1027,74 +1026,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment readingOrder="2"/>
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2267,7 +2260,7 @@
   <wetp:taskpane dockstate="right" visibility="0" width="525" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="1" width="525" row="0">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2311,4680 +2304,4973 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F291"/>
-  <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G291"/>
+  <sheetFormatPr defaultRowHeight="19" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.1796875" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="19" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A2" s="4">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A2" s="8">
         <v>1150436838</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="C2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="4">
         <v>966554289816</v>
       </c>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="4">
+      <c r="F2" s="12"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" ht="19" customHeight="1">
+      <c r="A3" s="8">
         <v>1152217368</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="4">
         <v>966556732717</v>
       </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A4" s="4">
+      <c r="F3" s="12"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="19" customHeight="1">
+      <c r="A4" s="8">
         <v>1152502371</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A5" s="4">
+      <c r="E4" s="5"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" ht="19" customHeight="1">
+      <c r="A5" s="8">
         <v>1152327969</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A6" s="4">
+      <c r="E5" s="5"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" ht="19" customHeight="1">
+      <c r="A6" s="8">
         <v>2302448127</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A7" s="4">
+      <c r="E6" s="5"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7" ht="19" customHeight="1">
+      <c r="A7" s="8">
         <v>1153472889</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="C7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="4">
+      <c r="E7" s="5"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:7" ht="19" customHeight="1">
+      <c r="A8" s="8">
         <v>1152518682</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A9" s="4">
+      <c r="E8" s="5"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:7" ht="19" customHeight="1">
+      <c r="A9" s="8">
         <v>1158331023</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
         <v>1</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A10" s="4">
+      <c r="E9" s="5"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" ht="19" customHeight="1">
+      <c r="A10" s="8">
         <v>1157900240</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
         <v>1</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A11" s="4">
+      <c r="E10" s="5"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" ht="19" customHeight="1">
+      <c r="A11" s="8">
         <v>1150731048</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A12" s="4">
+      <c r="E11" s="5"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" ht="19" customHeight="1">
+      <c r="A12" s="8">
         <v>2293198442</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A13" s="4">
+      <c r="E12" s="5"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:7" ht="19" customHeight="1">
+      <c r="A13" s="8">
         <v>1174946861</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A14" s="4">
+      <c r="E13" s="5"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" ht="19" customHeight="1">
+      <c r="A14" s="8">
         <v>1152820641</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A15" s="4">
+      <c r="E14" s="5"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:7" ht="19" customHeight="1">
+      <c r="A15" s="8">
         <v>1149366963</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
         <v>1</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A16" s="4">
+      <c r="E15" s="5"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:7" ht="19" customHeight="1">
+      <c r="A16" s="8">
         <v>1152734123</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
         <v>1</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A17" s="4">
+      <c r="E16" s="5"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="1:7" ht="19" customHeight="1">
+      <c r="A17" s="8">
         <v>1152480891</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="C17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A18" s="4">
+      <c r="E17" s="5"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:7" ht="19" customHeight="1">
+      <c r="A18" s="8">
         <v>1153507684</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
         <v>1</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A19" s="4">
+      <c r="E18" s="5"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="1:7" ht="19" customHeight="1">
+      <c r="A19" s="8">
         <v>1150008413</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A20" s="4">
+      <c r="E19" s="5"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" ht="19" customHeight="1">
+      <c r="A20" s="8">
         <v>1152989354</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="C20" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A21" s="4">
+      <c r="E20" s="5"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" spans="1:7" ht="19" customHeight="1">
+      <c r="A21" s="8">
         <v>1152061618</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7">
+      <c r="C21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A22" s="4">
+      <c r="E21" s="5"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" ht="19" customHeight="1">
+      <c r="A22" s="8">
         <v>1149206417</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="C22" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A23" s="4">
+      <c r="E22" s="5"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" spans="1:7" ht="19" customHeight="1">
+      <c r="A23" s="8">
         <v>1151880513</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A24" s="4">
+      <c r="E23" s="5"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" spans="1:7" ht="19" customHeight="1">
+      <c r="A24" s="8">
         <v>2290421144</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A25" s="4">
+      <c r="E24" s="5"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" ht="19" customHeight="1">
+      <c r="A25" s="8">
         <v>1160061816</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="C25" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
         <v>1</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A26" s="14">
+      <c r="E25" s="5"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" spans="1:7" ht="19" customHeight="1">
+      <c r="A26" s="6">
         <v>1152890750</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
         <v>1</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A27" s="4">
+      <c r="E26" s="5"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" spans="1:7" ht="19" customHeight="1">
+      <c r="A27" s="8">
         <v>1151773627</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="C27" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
         <v>1</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A28" s="4">
+      <c r="E27" s="5"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:7" ht="19" customHeight="1">
+      <c r="A28" s="8">
         <v>1152536601</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
         <v>1</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A29" s="4">
+      <c r="E28" s="5"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="19" customHeight="1">
+      <c r="A29" s="8">
         <v>1150018610</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
         <v>1</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A30" s="4">
+      <c r="E29" s="5"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="30" spans="1:7" ht="19" customHeight="1">
+      <c r="A30" s="8">
         <v>1146587298</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="C30" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
         <v>1</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A31" s="4">
+      <c r="E30" s="5"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="31" spans="1:7" ht="19" customHeight="1">
+      <c r="A31" s="8">
         <v>1150743167</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="C31" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3">
         <v>2</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A32" s="4">
+      <c r="E31" s="5"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" spans="1:7" ht="19" customHeight="1">
+      <c r="A32" s="8">
         <v>1151146907</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
         <v>2</v>
       </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A33" s="4">
+      <c r="E32" s="5"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" ht="19" customHeight="1">
+      <c r="A33" s="8">
         <v>2443189093</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="C33" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
         <v>2</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A34" s="4">
+      <c r="E33" s="5"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" spans="1:7" ht="19" customHeight="1">
+      <c r="A34" s="8">
         <v>1151434659</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="C34" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
         <v>2</v>
       </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A35" s="4">
+      <c r="E34" s="5"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" spans="1:7" ht="19" customHeight="1">
+      <c r="A35" s="8">
         <v>1152565972</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="7">
+      <c r="C35" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
         <v>2</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A36" s="4">
+      <c r="E35" s="5"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="36" spans="1:7" ht="19" customHeight="1">
+      <c r="A36" s="8">
         <v>1154025124</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36" s="11"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A37" s="4">
+      <c r="E36" s="5"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" spans="1:7" ht="19" customHeight="1">
+      <c r="A37" s="8">
         <v>1154153991</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37" s="7">
+      <c r="C37" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
         <v>2</v>
       </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A38" s="4">
+      <c r="E37" s="5"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="38" spans="1:7" ht="19" customHeight="1">
+      <c r="A38" s="8">
         <v>1149486605</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="C38" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
         <v>2</v>
       </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A39" s="4">
+      <c r="E38" s="5"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" spans="1:7" ht="19" customHeight="1">
+      <c r="A39" s="8">
         <v>1152472815</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="7">
+      <c r="C39" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3">
         <v>2</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A40" s="4">
+      <c r="E39" s="5"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="40" spans="1:7" ht="19" customHeight="1">
+      <c r="A40" s="8">
         <v>1150396164</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7">
+      <c r="C40" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3">
         <v>2</v>
       </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A41" s="4">
+      <c r="E40" s="5"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="1:7" ht="19" customHeight="1">
+      <c r="A41" s="8">
         <v>1150491064</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="7">
+      <c r="C41" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3">
         <v>2</v>
       </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A42" s="4">
+      <c r="E41" s="5"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" spans="1:7" ht="19" customHeight="1">
+      <c r="A42" s="8">
         <v>1152786958</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="7">
+      <c r="C42" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3">
         <v>2</v>
       </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A43" s="4">
+      <c r="E42" s="5"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="1:7" ht="19" customHeight="1">
+      <c r="A43" s="8">
         <v>1149922534</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43" s="7">
+      <c r="C43" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3">
         <v>2</v>
       </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A44" s="4">
+      <c r="E43" s="5"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="18"/>
+    </row>
+    <row r="44" spans="1:7" ht="19" customHeight="1">
+      <c r="A44" s="8">
         <v>2269053001</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7">
+      <c r="C44" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3">
         <v>2</v>
       </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A45" s="4">
+      <c r="E44" s="5"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="18"/>
+    </row>
+    <row r="45" spans="1:7" ht="19" customHeight="1">
+      <c r="A45" s="8">
         <v>1157238989</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="C45" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3">
         <v>2</v>
       </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12"/>
-    </row>
-    <row r="46" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A46" s="4">
+      <c r="E45" s="5"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="18"/>
+    </row>
+    <row r="46" spans="1:7" ht="19" customHeight="1">
+      <c r="A46" s="8">
         <v>1153155559</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="C46" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
         <v>2</v>
       </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A47" s="4">
+      <c r="E46" s="5"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="18"/>
+    </row>
+    <row r="47" spans="1:7" ht="19" customHeight="1">
+      <c r="A47" s="8">
         <v>1149465245</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3">
         <v>2</v>
       </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A48" s="4">
+      <c r="E47" s="5"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="18"/>
+    </row>
+    <row r="48" spans="1:7" ht="19" customHeight="1">
+      <c r="A48" s="8">
         <v>1155938150</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="C48" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3">
         <v>2</v>
       </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A49" s="4">
+      <c r="E48" s="5"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="18"/>
+    </row>
+    <row r="49" spans="1:7" ht="19" customHeight="1">
+      <c r="A49" s="8">
         <v>1149696633</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="C49" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3">
         <v>2</v>
       </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A50" s="4">
+      <c r="E49" s="5"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="18"/>
+    </row>
+    <row r="50" spans="1:7" ht="19" customHeight="1">
+      <c r="A50" s="8">
         <v>1155454240</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="C50" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3">
         <v>2</v>
       </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="12"/>
-    </row>
-    <row r="51" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A51" s="4">
+      <c r="E50" s="5"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="18"/>
+    </row>
+    <row r="51" spans="1:7" ht="19" customHeight="1">
+      <c r="A51" s="8">
         <v>1150039038</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="C51" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3">
         <v>2</v>
       </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="12"/>
-    </row>
-    <row r="52" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A52" s="4">
+      <c r="E51" s="5"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="18"/>
+    </row>
+    <row r="52" spans="1:7" ht="19" customHeight="1">
+      <c r="A52" s="8">
         <v>1152218085</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="C52" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
         <v>2</v>
       </c>
-      <c r="E52" s="11"/>
-      <c r="F52" s="12"/>
-    </row>
-    <row r="53" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A53" s="4">
+      <c r="E52" s="5"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="18"/>
+    </row>
+    <row r="53" spans="1:7" ht="19" customHeight="1">
+      <c r="A53" s="8">
         <v>1147013252</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="C53" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3">
         <v>2</v>
       </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
-    </row>
-    <row r="54" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A54" s="4">
+      <c r="E53" s="5"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="18"/>
+    </row>
+    <row r="54" spans="1:7" ht="19" customHeight="1">
+      <c r="A54" s="8">
         <v>1154169450</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="C54" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3">
         <v>2</v>
       </c>
-      <c r="E54" s="11"/>
-      <c r="F54" s="12"/>
-    </row>
-    <row r="55" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A55" s="4">
+      <c r="E54" s="5"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="18"/>
+    </row>
+    <row r="55" spans="1:7" ht="19" customHeight="1">
+      <c r="A55" s="8">
         <v>1151233614</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="C55" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3">
         <v>2</v>
       </c>
-      <c r="E55" s="11"/>
-      <c r="F55" s="12"/>
-    </row>
-    <row r="56" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A56" s="4">
+      <c r="E55" s="5"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="18"/>
+    </row>
+    <row r="56" spans="1:7" ht="19" customHeight="1">
+      <c r="A56" s="8">
         <v>1151650809</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="C56" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3">
         <v>2</v>
       </c>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
-    </row>
-    <row r="57" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A57" s="4">
+      <c r="E56" s="5"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="18"/>
+    </row>
+    <row r="57" spans="1:7" ht="19" customHeight="1">
+      <c r="A57" s="8">
         <v>1151119201</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7">
+      <c r="C57" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3">
         <v>2</v>
       </c>
-      <c r="E57" s="11"/>
-      <c r="F57" s="12"/>
-    </row>
-    <row r="58" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A58" s="4">
+      <c r="E57" s="5"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="18"/>
+    </row>
+    <row r="58" spans="1:7" ht="19" customHeight="1">
+      <c r="A58" s="8">
         <v>1152878417</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="7">
+      <c r="C58" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3">
         <v>3</v>
       </c>
-      <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
-    </row>
-    <row r="59" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A59" s="4">
+      <c r="E58" s="5"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="18"/>
+    </row>
+    <row r="59" spans="1:7" ht="19" customHeight="1">
+      <c r="A59" s="8">
         <v>1152574958</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="7">
+      <c r="C59" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3">
         <v>3</v>
       </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A60" s="4">
+      <c r="E59" s="5"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="18"/>
+    </row>
+    <row r="60" spans="1:7" ht="19" customHeight="1">
+      <c r="A60" s="8">
         <v>1152986681</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="7">
+      <c r="C60" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3">
         <v>3</v>
       </c>
-      <c r="E60" s="11"/>
-      <c r="F60" s="12"/>
-    </row>
-    <row r="61" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A61" s="4">
+      <c r="E60" s="5"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="18"/>
+    </row>
+    <row r="61" spans="1:7" ht="19" customHeight="1">
+      <c r="A61" s="8">
         <v>1151154455</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="C61" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3">
         <v>3</v>
       </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="12"/>
-    </row>
-    <row r="62" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A62" s="4">
+      <c r="E61" s="5"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="18"/>
+    </row>
+    <row r="62" spans="1:7" ht="19" customHeight="1">
+      <c r="A62" s="8">
         <v>1159289287</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="7">
+      <c r="C62" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3">
         <v>3</v>
       </c>
-      <c r="E62" s="11"/>
-      <c r="F62" s="12"/>
-    </row>
-    <row r="63" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A63" s="4">
+      <c r="E62" s="5"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="18"/>
+    </row>
+    <row r="63" spans="1:7" ht="19" customHeight="1">
+      <c r="A63" s="8">
         <v>1153334618</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="C63" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3">
         <v>3</v>
       </c>
-      <c r="E63" s="11"/>
-      <c r="F63" s="12"/>
-    </row>
-    <row r="64" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A64" s="4">
+      <c r="E63" s="5"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="18"/>
+    </row>
+    <row r="64" spans="1:7" ht="19" customHeight="1">
+      <c r="A64" s="8">
         <v>1152212658</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="C64" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3">
         <v>3</v>
       </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="12"/>
-    </row>
-    <row r="65" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A65" s="4">
+      <c r="E64" s="5"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="18"/>
+    </row>
+    <row r="65" spans="1:7" ht="19" customHeight="1">
+      <c r="A65" s="8">
         <v>1152410336</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="C65" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3">
         <v>3</v>
       </c>
-      <c r="E65" s="11"/>
-      <c r="F65" s="12"/>
-    </row>
-    <row r="66" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A66" s="4">
+      <c r="E65" s="5"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="18"/>
+    </row>
+    <row r="66" spans="1:7" ht="19" customHeight="1">
+      <c r="A66" s="8">
         <v>1154207904</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="7">
+      <c r="C66" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3">
         <v>3</v>
       </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A67" s="4">
+      <c r="E66" s="5"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="18"/>
+    </row>
+    <row r="67" spans="1:7" ht="19" customHeight="1">
+      <c r="A67" s="8">
         <v>1168345245</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" s="7">
+      <c r="C67" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3">
         <v>3</v>
       </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A68" s="4">
+      <c r="E67" s="5"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="18"/>
+    </row>
+    <row r="68" spans="1:7" ht="19" customHeight="1">
+      <c r="A68" s="8">
         <v>1149893040</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7">
+      <c r="C68" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3">
         <v>3</v>
       </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A69" s="4">
+      <c r="E68" s="5"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="18"/>
+    </row>
+    <row r="69" spans="1:7" ht="19" customHeight="1">
+      <c r="A69" s="8">
         <v>1151849807</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" s="7">
+      <c r="C69" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3">
         <v>3</v>
       </c>
-      <c r="E69" s="11"/>
-      <c r="F69" s="12"/>
-    </row>
-    <row r="70" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A70" s="4">
+      <c r="E69" s="5"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="18"/>
+    </row>
+    <row r="70" spans="1:7" ht="19" customHeight="1">
+      <c r="A70" s="8">
         <v>1152284103</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="7">
+      <c r="C70" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3">
         <v>3</v>
       </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A71" s="4">
+      <c r="E70" s="5"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="18"/>
+    </row>
+    <row r="71" spans="1:7" ht="19" customHeight="1">
+      <c r="A71" s="8">
         <v>1167082591</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="7">
+      <c r="C71" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3">
         <v>3</v>
       </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
-    </row>
-    <row r="72" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A72" s="4">
+      <c r="E71" s="5"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="18"/>
+    </row>
+    <row r="72" spans="1:7" ht="19" customHeight="1">
+      <c r="A72" s="8">
         <v>1153479645</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" s="7">
+      <c r="C72" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3">
         <v>3</v>
       </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
-    </row>
-    <row r="73" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A73" s="4">
+      <c r="E72" s="5"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="18"/>
+    </row>
+    <row r="73" spans="1:7" ht="19" customHeight="1">
+      <c r="A73" s="8">
         <v>1155524893</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" s="7">
+      <c r="C73" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3">
         <v>3</v>
       </c>
-      <c r="E73" s="11"/>
-      <c r="F73" s="12"/>
-    </row>
-    <row r="74" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A74" s="4">
+      <c r="E73" s="5"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="18"/>
+    </row>
+    <row r="74" spans="1:7" ht="19" customHeight="1">
+      <c r="A74" s="8">
         <v>1150599171</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D74" s="7">
+      <c r="C74" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3">
         <v>3</v>
       </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="12"/>
-    </row>
-    <row r="75" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A75" s="4">
+      <c r="E74" s="5"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="18"/>
+    </row>
+    <row r="75" spans="1:7" ht="19" customHeight="1">
+      <c r="A75" s="8">
         <v>1154873481</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D75" s="7">
+      <c r="C75" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3">
         <v>3</v>
       </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="12"/>
-    </row>
-    <row r="76" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A76" s="4">
+      <c r="E75" s="5"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="18"/>
+    </row>
+    <row r="76" spans="1:7" ht="19" customHeight="1">
+      <c r="A76" s="8">
         <v>1152884167</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76" s="7">
+      <c r="C76" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3">
         <v>3</v>
       </c>
-      <c r="E76" s="11"/>
-      <c r="F76" s="12"/>
-    </row>
-    <row r="77" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A77" s="4">
+      <c r="E76" s="5"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="18"/>
+    </row>
+    <row r="77" spans="1:7" ht="19" customHeight="1">
+      <c r="A77" s="8">
         <v>1152128029</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77" s="7">
+      <c r="C77" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3">
         <v>3</v>
       </c>
-      <c r="E77" s="11"/>
-      <c r="F77" s="12"/>
-    </row>
-    <row r="78" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A78" s="4">
+      <c r="E77" s="5"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="18"/>
+    </row>
+    <row r="78" spans="1:7" ht="19" customHeight="1">
+      <c r="A78" s="8">
         <v>1151910013</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D78" s="7">
+      <c r="C78" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3">
         <v>3</v>
       </c>
-      <c r="E78" s="11"/>
-      <c r="F78" s="12"/>
-    </row>
-    <row r="79" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A79" s="4">
+      <c r="E78" s="5"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="18"/>
+    </row>
+    <row r="79" spans="1:7" ht="19" customHeight="1">
+      <c r="A79" s="8">
         <v>1154287575</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79" s="7">
+      <c r="C79" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3">
         <v>3</v>
       </c>
-      <c r="E79" s="11"/>
-      <c r="F79" s="12"/>
-    </row>
-    <row r="80" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A80" s="4">
+      <c r="E79" s="5"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="18"/>
+    </row>
+    <row r="80" spans="1:7" ht="19" customHeight="1">
+      <c r="A80" s="8">
         <v>1152571822</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="7">
+      <c r="C80" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3">
         <v>3</v>
       </c>
-      <c r="E80" s="11"/>
-      <c r="F80" s="12"/>
-    </row>
-    <row r="81" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A81" s="4">
+      <c r="E80" s="5"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="18"/>
+    </row>
+    <row r="81" spans="1:7" ht="19" customHeight="1">
+      <c r="A81" s="8">
         <v>1150680112</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C81" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3">
         <v>3</v>
       </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="12"/>
-    </row>
-    <row r="82" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A82" s="4">
+      <c r="E81" s="5"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="18"/>
+    </row>
+    <row r="82" spans="1:7" ht="19" customHeight="1">
+      <c r="A82" s="8">
         <v>1150690798</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D82" s="7">
+      <c r="C82" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3">
         <v>3</v>
       </c>
-      <c r="E82" s="11"/>
-      <c r="F82" s="12"/>
-    </row>
-    <row r="83" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A83" s="4">
+      <c r="E82" s="5"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="18"/>
+    </row>
+    <row r="83" spans="1:7" ht="19" customHeight="1">
+      <c r="A83" s="8">
         <v>1151961511</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="C83" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3">
         <v>3</v>
       </c>
-      <c r="E83" s="11"/>
-      <c r="F83" s="12"/>
-    </row>
-    <row r="84" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A84" s="4">
+      <c r="E83" s="5"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="18"/>
+    </row>
+    <row r="84" spans="1:7" ht="19" customHeight="1">
+      <c r="A84" s="8">
         <v>1149761460</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="7">
+      <c r="C84" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3">
         <v>3</v>
       </c>
-      <c r="E84" s="11"/>
-      <c r="F84" s="12"/>
-    </row>
-    <row r="85" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A85" s="4">
+      <c r="E84" s="5"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="18"/>
+    </row>
+    <row r="85" spans="1:7" ht="19" customHeight="1">
+      <c r="A85" s="8">
         <v>2297211076</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="7">
+      <c r="C85" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3">
         <v>4</v>
       </c>
-      <c r="E85" s="11"/>
-      <c r="F85" s="12"/>
-    </row>
-    <row r="86" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A86" s="4">
+      <c r="E85" s="5"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="18"/>
+    </row>
+    <row r="86" spans="1:7" ht="19" customHeight="1">
+      <c r="A86" s="8">
         <v>1153216211</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D86" s="7">
+      <c r="C86" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3">
         <v>4</v>
       </c>
-      <c r="E86" s="11"/>
-      <c r="F86" s="12"/>
-    </row>
-    <row r="87" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A87" s="4">
+      <c r="E86" s="5"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="18"/>
+    </row>
+    <row r="87" spans="1:7" ht="19" customHeight="1">
+      <c r="A87" s="8">
         <v>1152536460</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D87" s="7">
+      <c r="C87" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3">
         <v>4</v>
       </c>
-      <c r="E87" s="11"/>
-      <c r="F87" s="12"/>
-    </row>
-    <row r="88" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A88" s="4">
+      <c r="E87" s="5"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="18"/>
+    </row>
+    <row r="88" spans="1:7" ht="19" customHeight="1">
+      <c r="A88" s="8">
         <v>1152152763</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D88" s="7">
+      <c r="C88" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3">
         <v>4</v>
       </c>
-      <c r="E88" s="11"/>
-      <c r="F88" s="12"/>
-    </row>
-    <row r="89" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A89" s="4">
+      <c r="E88" s="5"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="18"/>
+    </row>
+    <row r="89" spans="1:7" ht="19" customHeight="1">
+      <c r="A89" s="8">
         <v>1156092080</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D89" s="7">
+      <c r="C89" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3">
         <v>4</v>
       </c>
-      <c r="E89" s="11"/>
-      <c r="F89" s="12"/>
-    </row>
-    <row r="90" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A90" s="4">
+      <c r="E89" s="5"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="18"/>
+    </row>
+    <row r="90" spans="1:7" ht="19" customHeight="1">
+      <c r="A90" s="8">
         <v>2510170026</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90" s="7">
+      <c r="C90" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3">
         <v>4</v>
       </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="12"/>
-    </row>
-    <row r="91" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A91" s="4">
+      <c r="E90" s="5"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="18"/>
+    </row>
+    <row r="91" spans="1:7" ht="19" customHeight="1">
+      <c r="A91" s="8">
         <v>1151404256</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D91" s="7">
+      <c r="C91" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3">
         <v>4</v>
       </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="12"/>
-    </row>
-    <row r="92" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A92" s="4">
+      <c r="E91" s="5"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="18"/>
+    </row>
+    <row r="92" spans="1:7" ht="19" customHeight="1">
+      <c r="A92" s="8">
         <v>1152224984</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D92" s="7">
+      <c r="C92" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3">
         <v>4</v>
       </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="12"/>
-    </row>
-    <row r="93" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A93" s="4">
+      <c r="E92" s="5"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="18"/>
+    </row>
+    <row r="93" spans="1:7" ht="19" customHeight="1">
+      <c r="A93" s="8">
         <v>1150781068</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93" s="7">
+      <c r="C93" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3">
         <v>4</v>
       </c>
-      <c r="E93" s="11"/>
-      <c r="F93" s="12"/>
-    </row>
-    <row r="94" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A94" s="4">
+      <c r="E93" s="5"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="18"/>
+    </row>
+    <row r="94" spans="1:7" ht="19" customHeight="1">
+      <c r="A94" s="8">
         <v>1150218970</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D94" s="7">
+      <c r="C94" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3">
         <v>4</v>
       </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="12"/>
-    </row>
-    <row r="95" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A95" s="4">
+      <c r="E94" s="5"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="18"/>
+    </row>
+    <row r="95" spans="1:7" ht="19" customHeight="1">
+      <c r="A95" s="8">
         <v>1153072044</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="7">
+      <c r="C95" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3">
         <v>4</v>
       </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="12"/>
-    </row>
-    <row r="96" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A96" s="4">
+      <c r="E95" s="5"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="18"/>
+    </row>
+    <row r="96" spans="1:7" ht="19" customHeight="1">
+      <c r="A96" s="8">
         <v>1153072069</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D96" s="7">
+      <c r="C96" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3">
         <v>4</v>
       </c>
-      <c r="E96" s="11"/>
-      <c r="F96" s="12"/>
-    </row>
-    <row r="97" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A97" s="4">
+      <c r="E96" s="5"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="18"/>
+    </row>
+    <row r="97" spans="1:7" ht="19" customHeight="1">
+      <c r="A97" s="8">
         <v>1149401059</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D97" s="7">
+      <c r="C97" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3">
         <v>4</v>
       </c>
-      <c r="E97" s="11"/>
-      <c r="F97" s="12"/>
-    </row>
-    <row r="98" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A98" s="4">
+      <c r="E97" s="5"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="18"/>
+    </row>
+    <row r="98" spans="1:7" ht="19" customHeight="1">
+      <c r="A98" s="8">
         <v>1153495591</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98" s="7">
+      <c r="C98" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3">
         <v>4</v>
       </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A99" s="4">
+      <c r="E98" s="5"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="18"/>
+    </row>
+    <row r="99" spans="1:7" ht="19" customHeight="1">
+      <c r="A99" s="8">
         <v>1150973210</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D99" s="7">
+      <c r="C99" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="12"/>
-    </row>
-    <row r="100" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A100" s="4">
+      <c r="E99" s="5"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="18"/>
+    </row>
+    <row r="100" spans="1:7" ht="19" customHeight="1">
+      <c r="A100" s="8">
         <v>1151704598</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="7">
+      <c r="C100" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3">
         <v>4</v>
       </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="12"/>
-    </row>
-    <row r="101" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A101" s="4">
+      <c r="E100" s="5"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="18"/>
+    </row>
+    <row r="101" spans="1:7" ht="19" customHeight="1">
+      <c r="A101" s="8">
         <v>1151845870</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D101" s="7">
+      <c r="C101" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3">
         <v>4</v>
       </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="12"/>
-    </row>
-    <row r="102" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A102" s="4">
+      <c r="E101" s="5"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="18"/>
+    </row>
+    <row r="102" spans="1:7" ht="19" customHeight="1">
+      <c r="A102" s="8">
         <v>1149888925</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D102" s="7">
+      <c r="C102" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3">
         <v>4</v>
       </c>
-      <c r="E102" s="11"/>
-      <c r="F102" s="12"/>
-    </row>
-    <row r="103" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A103" s="4">
+      <c r="E102" s="5"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="18"/>
+    </row>
+    <row r="103" spans="1:7" ht="19" customHeight="1">
+      <c r="A103" s="8">
         <v>1153380116</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D103" s="7">
+      <c r="C103" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3">
         <v>4</v>
       </c>
-      <c r="E103" s="11"/>
-      <c r="F103" s="12"/>
-    </row>
-    <row r="104" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A104" s="4">
+      <c r="E103" s="5"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="18"/>
+    </row>
+    <row r="104" spans="1:7" ht="19" customHeight="1">
+      <c r="A104" s="8">
         <v>1152305007</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D104" s="7">
+      <c r="C104" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3">
         <v>4</v>
       </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="12"/>
-    </row>
-    <row r="105" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A105" s="4">
+      <c r="E104" s="5"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="18"/>
+    </row>
+    <row r="105" spans="1:7" ht="19" customHeight="1">
+      <c r="A105" s="8">
         <v>1153607922</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D105" s="7">
+      <c r="C105" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3">
         <v>4</v>
       </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="12"/>
-    </row>
-    <row r="106" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A106" s="4">
+      <c r="E105" s="5"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="18"/>
+    </row>
+    <row r="106" spans="1:7" ht="19" customHeight="1">
+      <c r="A106" s="8">
         <v>1152853493</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D106" s="7">
+      <c r="C106" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3">
         <v>4</v>
       </c>
-      <c r="E106" s="11"/>
-      <c r="F106" s="12"/>
-    </row>
-    <row r="107" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A107" s="4">
+      <c r="E106" s="5"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="18"/>
+    </row>
+    <row r="107" spans="1:7" ht="19" customHeight="1">
+      <c r="A107" s="8">
         <v>1153534167</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D107" s="7">
+      <c r="C107" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3">
         <v>4</v>
       </c>
-      <c r="E107" s="11"/>
-      <c r="F107" s="12"/>
-    </row>
-    <row r="108" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A108" s="4">
+      <c r="E107" s="5"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="18"/>
+    </row>
+    <row r="108" spans="1:7" ht="19" customHeight="1">
+      <c r="A108" s="8">
         <v>1149855445</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D108" s="7">
+      <c r="C108" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3">
         <v>4</v>
       </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="12"/>
-    </row>
-    <row r="109" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A109" s="4">
+      <c r="E108" s="5"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="18"/>
+    </row>
+    <row r="109" spans="1:7" ht="19" customHeight="1">
+      <c r="A109" s="8">
         <v>1153291388</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D109" s="7">
+      <c r="C109" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3">
         <v>4</v>
       </c>
-      <c r="E109" s="11"/>
-      <c r="F109" s="12"/>
-    </row>
-    <row r="110" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A110" s="4">
+      <c r="E109" s="5"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="18"/>
+    </row>
+    <row r="110" spans="1:7" ht="19" customHeight="1">
+      <c r="A110" s="8">
         <v>1151814371</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110" s="7">
+      <c r="C110" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3">
         <v>4</v>
       </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="12"/>
-    </row>
-    <row r="111" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A111" s="4">
+      <c r="E110" s="5"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="18"/>
+    </row>
+    <row r="111" spans="1:7" ht="19" customHeight="1">
+      <c r="A111" s="8">
         <v>1158612646</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D111" s="7">
+      <c r="C111" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3">
         <v>4</v>
       </c>
-      <c r="E111" s="11"/>
-      <c r="F111" s="12"/>
-    </row>
-    <row r="112" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A112" s="4">
+      <c r="E111" s="5"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="18"/>
+    </row>
+    <row r="112" spans="1:7" ht="19" customHeight="1">
+      <c r="A112" s="8">
         <v>1151003728</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C112" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D112" s="7">
+      <c r="C112" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3">
         <v>5</v>
       </c>
-      <c r="E112" s="11"/>
-      <c r="F112" s="12"/>
-    </row>
-    <row r="113" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A113" s="4">
+      <c r="E112" s="5"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="18"/>
+    </row>
+    <row r="113" spans="1:7" ht="19" customHeight="1">
+      <c r="A113" s="8">
         <v>1174052116</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D113" s="7">
+      <c r="C113" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3">
         <v>5</v>
       </c>
-      <c r="E113" s="11"/>
-      <c r="F113" s="12"/>
-    </row>
-    <row r="114" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A114" s="4">
+      <c r="E113" s="5"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="18"/>
+    </row>
+    <row r="114" spans="1:7" ht="19" customHeight="1">
+      <c r="A114" s="8">
         <v>1153013931</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D114" s="7">
+      <c r="C114" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3">
         <v>5</v>
       </c>
-      <c r="E114" s="11"/>
-      <c r="F114" s="12"/>
-    </row>
-    <row r="115" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A115" s="4">
+      <c r="E114" s="5"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="18"/>
+    </row>
+    <row r="115" spans="1:7" ht="19" customHeight="1">
+      <c r="A115" s="8">
         <v>1150396081</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="7">
+      <c r="C115" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3">
         <v>5</v>
       </c>
-      <c r="E115" s="11"/>
-      <c r="F115" s="12"/>
-    </row>
-    <row r="116" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A116" s="4">
+      <c r="E115" s="5"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="18"/>
+    </row>
+    <row r="116" spans="1:7" ht="19" customHeight="1">
+      <c r="A116" s="8">
         <v>1150690699</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D116" s="7">
+      <c r="C116" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3">
         <v>5</v>
       </c>
-      <c r="E116" s="11"/>
-      <c r="F116" s="12"/>
-    </row>
-    <row r="117" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A117" s="4">
+      <c r="E116" s="5"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="18"/>
+    </row>
+    <row r="117" spans="1:7" ht="19" customHeight="1">
+      <c r="A117" s="8">
         <v>1152698252</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D117" s="7">
+      <c r="C117" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3">
         <v>5</v>
       </c>
-      <c r="E117" s="11"/>
-      <c r="F117" s="12"/>
-    </row>
-    <row r="118" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A118" s="4">
+      <c r="E117" s="5"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="18"/>
+    </row>
+    <row r="118" spans="1:7" ht="19" customHeight="1">
+      <c r="A118" s="8">
         <v>1153384795</v>
       </c>
-      <c r="B118" s="13" t="s">
+      <c r="B118" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D118" s="7">
+      <c r="C118" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3">
         <v>5</v>
       </c>
-      <c r="E118" s="11"/>
-      <c r="F118" s="12"/>
-    </row>
-    <row r="119" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A119" s="4">
+      <c r="E118" s="5"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="18"/>
+    </row>
+    <row r="119" spans="1:7" ht="19" customHeight="1">
+      <c r="A119" s="8">
         <v>1150304325</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D119" s="7">
+      <c r="C119" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3">
         <v>5</v>
       </c>
-      <c r="E119" s="11"/>
-      <c r="F119" s="12"/>
-    </row>
-    <row r="120" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A120" s="4">
+      <c r="E119" s="5"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="18"/>
+    </row>
+    <row r="120" spans="1:7" ht="19" customHeight="1">
+      <c r="A120" s="8">
         <v>1152915870</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="7">
+      <c r="C120" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3">
         <v>5</v>
       </c>
-      <c r="E120" s="11"/>
-      <c r="F120" s="12"/>
-    </row>
-    <row r="121" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A121" s="4">
+      <c r="E120" s="5"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="18"/>
+    </row>
+    <row r="121" spans="1:7" ht="19" customHeight="1">
+      <c r="A121" s="8">
         <v>1152367700</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D121" s="7">
+      <c r="C121" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3">
         <v>5</v>
       </c>
-      <c r="E121" s="11"/>
-      <c r="F121" s="12"/>
-    </row>
-    <row r="122" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A122" s="4">
+      <c r="E121" s="5"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="18"/>
+    </row>
+    <row r="122" spans="1:7" ht="19" customHeight="1">
+      <c r="A122" s="8">
         <v>1152775639</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D122" s="7">
+      <c r="C122" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3">
         <v>5</v>
       </c>
-      <c r="E122" s="11"/>
-      <c r="F122" s="12"/>
-    </row>
-    <row r="123" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A123" s="4">
+      <c r="E122" s="5"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="18"/>
+    </row>
+    <row r="123" spans="1:7" ht="19" customHeight="1">
+      <c r="A123" s="8">
         <v>1149182303</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D123" s="7">
+      <c r="C123" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3">
         <v>5</v>
       </c>
-      <c r="E123" s="11"/>
-      <c r="F123" s="12"/>
-    </row>
-    <row r="124" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A124" s="4">
+      <c r="E123" s="5"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="18"/>
+    </row>
+    <row r="124" spans="1:7" ht="19" customHeight="1">
+      <c r="A124" s="8">
         <v>1149628024</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D124" s="7">
+      <c r="C124" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3">
         <v>5</v>
       </c>
-      <c r="E124" s="11"/>
-      <c r="F124" s="12"/>
-    </row>
-    <row r="125" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A125" s="4">
+      <c r="E124" s="5"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="18"/>
+    </row>
+    <row r="125" spans="1:7" ht="19" customHeight="1">
+      <c r="A125" s="8">
         <v>1152522833</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125" s="7">
+      <c r="C125" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3">
         <v>5</v>
       </c>
-      <c r="E125" s="11"/>
-      <c r="F125" s="12"/>
-    </row>
-    <row r="126" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A126" s="4">
+      <c r="E125" s="5"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="18"/>
+    </row>
+    <row r="126" spans="1:7" ht="19" customHeight="1">
+      <c r="A126" s="8">
         <v>2382166136</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D126" s="7">
+      <c r="C126" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3">
         <v>5</v>
       </c>
-      <c r="E126" s="11"/>
-      <c r="F126" s="12"/>
-    </row>
-    <row r="127" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A127" s="4">
+      <c r="E126" s="5"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="18"/>
+    </row>
+    <row r="127" spans="1:7" ht="19" customHeight="1">
+      <c r="A127" s="8">
         <v>1151669510</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D127" s="7">
+      <c r="C127" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3">
         <v>5</v>
       </c>
-      <c r="E127" s="11"/>
-      <c r="F127" s="12"/>
-    </row>
-    <row r="128" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A128" s="4">
+      <c r="E127" s="5"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="18"/>
+    </row>
+    <row r="128" spans="1:7" ht="19" customHeight="1">
+      <c r="A128" s="8">
         <v>1155012543</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D128" s="7">
+      <c r="C128" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3">
         <v>5</v>
       </c>
-      <c r="E128" s="11"/>
-      <c r="F128" s="12"/>
-    </row>
-    <row r="129" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A129" s="4">
+      <c r="E128" s="5"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="18"/>
+    </row>
+    <row r="129" spans="1:7" ht="19" customHeight="1">
+      <c r="A129" s="8">
         <v>1150763322</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D129" s="7">
+      <c r="C129" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3">
         <v>5</v>
       </c>
-      <c r="E129" s="11"/>
-      <c r="F129" s="12"/>
-    </row>
-    <row r="130" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A130" s="4">
+      <c r="E129" s="5"/>
+      <c r="F129" s="14"/>
+      <c r="G129" s="18"/>
+    </row>
+    <row r="130" spans="1:7" ht="19" customHeight="1">
+      <c r="A130" s="8">
         <v>1150527107</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B130" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130" s="7">
+      <c r="C130" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3">
         <v>5</v>
       </c>
-      <c r="E130" s="11"/>
-      <c r="F130" s="12"/>
-    </row>
-    <row r="131" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A131" s="4">
+      <c r="E130" s="5"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="18"/>
+    </row>
+    <row r="131" spans="1:7" ht="19" customHeight="1">
+      <c r="A131" s="8">
         <v>1171859398</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D131" s="7">
+      <c r="C131" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3">
         <v>5</v>
       </c>
-      <c r="E131" s="11"/>
-      <c r="F131" s="12"/>
-    </row>
-    <row r="132" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A132" s="4">
+      <c r="E131" s="5"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="18"/>
+    </row>
+    <row r="132" spans="1:7" ht="19" customHeight="1">
+      <c r="A132" s="8">
         <v>1151485529</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D132" s="7">
+      <c r="C132" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3">
         <v>5</v>
       </c>
-      <c r="E132" s="11"/>
-      <c r="F132" s="12"/>
-    </row>
-    <row r="133" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A133" s="4">
+      <c r="E132" s="5"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="18"/>
+    </row>
+    <row r="133" spans="1:7" ht="19" customHeight="1">
+      <c r="A133" s="8">
         <v>1153562317</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D133" s="7">
+      <c r="C133" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D133" s="3">
         <v>5</v>
       </c>
-      <c r="E133" s="11"/>
-      <c r="F133" s="12"/>
-    </row>
-    <row r="134" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A134" s="4">
+      <c r="E133" s="5"/>
+      <c r="F133" s="14"/>
+      <c r="G133" s="18"/>
+    </row>
+    <row r="134" spans="1:7" ht="19" customHeight="1">
+      <c r="A134" s="8">
         <v>1153018385</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D134" s="7">
+      <c r="C134" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3">
         <v>5</v>
       </c>
-      <c r="E134" s="11"/>
-      <c r="F134" s="12"/>
-    </row>
-    <row r="135" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A135" s="4">
+      <c r="E134" s="5"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="18"/>
+    </row>
+    <row r="135" spans="1:7" ht="19" customHeight="1">
+      <c r="A135" s="8">
         <v>2288260736</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135" s="7">
+      <c r="C135" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3">
         <v>5</v>
       </c>
-      <c r="E135" s="11"/>
-      <c r="F135" s="12"/>
-    </row>
-    <row r="136" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A136" s="4">
+      <c r="E135" s="5"/>
+      <c r="F135" s="14"/>
+      <c r="G135" s="18"/>
+    </row>
+    <row r="136" spans="1:7" ht="19" customHeight="1">
+      <c r="A136" s="8">
         <v>1152156905</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D136" s="7">
+      <c r="C136" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D136" s="3">
         <v>5</v>
       </c>
-      <c r="E136" s="11"/>
-      <c r="F136" s="12"/>
-    </row>
-    <row r="137" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A137" s="4">
+      <c r="E136" s="5"/>
+      <c r="F136" s="14"/>
+      <c r="G136" s="18"/>
+    </row>
+    <row r="137" spans="1:7" ht="19" customHeight="1">
+      <c r="A137" s="8">
         <v>1152746895</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D137" s="7">
+      <c r="C137" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D137" s="3">
         <v>5</v>
       </c>
-      <c r="E137" s="11"/>
-      <c r="F137" s="12"/>
-    </row>
-    <row r="138" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A138" s="4">
+      <c r="E137" s="5"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="18"/>
+    </row>
+    <row r="138" spans="1:7" ht="19" customHeight="1">
+      <c r="A138" s="8">
         <v>1153259260</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D138" s="7">
+      <c r="C138" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3">
         <v>5</v>
       </c>
-      <c r="E138" s="11"/>
-      <c r="F138" s="12"/>
-    </row>
-    <row r="139" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A139" s="4">
+      <c r="E138" s="5"/>
+      <c r="F138" s="14"/>
+      <c r="G138" s="18"/>
+    </row>
+    <row r="139" spans="1:7" ht="19" customHeight="1">
+      <c r="A139" s="8">
         <v>1153491590</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139" s="7">
+      <c r="C139" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3">
         <v>5</v>
       </c>
-      <c r="E139" s="11"/>
-      <c r="F139" s="12"/>
-    </row>
-    <row r="140" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A140" s="4">
+      <c r="E139" s="5"/>
+      <c r="F139" s="14"/>
+      <c r="G139" s="18"/>
+    </row>
+    <row r="140" spans="1:7" ht="19" customHeight="1">
+      <c r="A140" s="8">
         <v>1148755273</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D140" s="7">
+      <c r="C140" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D140" s="3">
         <v>1</v>
       </c>
-      <c r="E140" s="11"/>
-      <c r="F140" s="12"/>
-    </row>
-    <row r="141" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A141" s="4">
+      <c r="E140" s="5"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="18"/>
+    </row>
+    <row r="141" spans="1:7" ht="19" customHeight="1">
+      <c r="A141" s="8">
         <v>1146774821</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D141" s="7">
+      <c r="C141" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="3">
         <v>1</v>
       </c>
-      <c r="E141" s="11"/>
-      <c r="F141" s="12"/>
-    </row>
-    <row r="142" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A142" s="4">
+      <c r="E141" s="5"/>
+      <c r="F141" s="14"/>
+      <c r="G141" s="18"/>
+    </row>
+    <row r="142" spans="1:7" ht="19" customHeight="1">
+      <c r="A142" s="8">
         <v>1146165780</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D142" s="7">
+      <c r="C142" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="3">
         <v>1</v>
       </c>
-      <c r="E142" s="11"/>
-      <c r="F142" s="12"/>
-    </row>
-    <row r="143" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A143" s="4">
+      <c r="E142" s="5"/>
+      <c r="F142" s="14"/>
+      <c r="G142" s="18"/>
+    </row>
+    <row r="143" spans="1:7" ht="19" customHeight="1">
+      <c r="A143" s="8">
         <v>1147913071</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D143" s="7">
+      <c r="C143" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="3">
         <v>1</v>
       </c>
-      <c r="E143" s="11"/>
-      <c r="F143" s="12"/>
-    </row>
-    <row r="144" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A144" s="4">
+      <c r="E143" s="5"/>
+      <c r="F143" s="14"/>
+      <c r="G143" s="18"/>
+    </row>
+    <row r="144" spans="1:7" ht="19" customHeight="1">
+      <c r="A144" s="8">
         <v>1149665844</v>
       </c>
-      <c r="B144" s="13" t="s">
+      <c r="B144" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D144" s="7">
+      <c r="C144" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="3">
         <v>1</v>
       </c>
-      <c r="E144" s="11"/>
-      <c r="F144" s="12"/>
-    </row>
-    <row r="145" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A145" s="4">
+      <c r="E144" s="5"/>
+      <c r="F144" s="14"/>
+      <c r="G144" s="18"/>
+    </row>
+    <row r="145" spans="1:7" ht="19" customHeight="1">
+      <c r="A145" s="8">
         <v>2282375720</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D145" s="7">
+      <c r="C145" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="3">
         <v>1</v>
       </c>
-      <c r="E145" s="11"/>
-      <c r="F145" s="12"/>
-    </row>
-    <row r="146" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A146" s="4">
+      <c r="E145" s="5"/>
+      <c r="F145" s="14"/>
+      <c r="G145" s="18"/>
+    </row>
+    <row r="146" spans="1:7" ht="19" customHeight="1">
+      <c r="A146" s="8">
         <v>2415139746</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D146" s="7">
+      <c r="C146" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="3">
         <v>1</v>
       </c>
-      <c r="E146" s="11"/>
-      <c r="F146" s="12"/>
-    </row>
-    <row r="147" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A147" s="4">
+      <c r="E146" s="5"/>
+      <c r="F146" s="14"/>
+      <c r="G146" s="18"/>
+    </row>
+    <row r="147" spans="1:7" ht="19" customHeight="1">
+      <c r="A147" s="8">
         <v>1146628035</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D147" s="7">
+      <c r="C147" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="3">
         <v>1</v>
       </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="12"/>
-    </row>
-    <row r="148" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A148" s="4">
+      <c r="E147" s="5"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="18"/>
+    </row>
+    <row r="148" spans="1:7" ht="19" customHeight="1">
+      <c r="A148" s="8">
         <v>1148873159</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D148" s="7">
+      <c r="C148" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="3">
         <v>1</v>
       </c>
-      <c r="E148" s="11"/>
-      <c r="F148" s="12"/>
-    </row>
-    <row r="149" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A149" s="4">
+      <c r="E148" s="5"/>
+      <c r="F148" s="14"/>
+      <c r="G148" s="18"/>
+    </row>
+    <row r="149" spans="1:7" ht="19" customHeight="1">
+      <c r="A149" s="8">
         <v>2275349674</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D149" s="7">
+      <c r="C149" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="3">
         <v>1</v>
       </c>
-      <c r="E149" s="11"/>
-      <c r="F149" s="12"/>
-    </row>
-    <row r="150" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A150" s="4">
+      <c r="E149" s="5"/>
+      <c r="F149" s="14"/>
+      <c r="G149" s="18"/>
+    </row>
+    <row r="150" spans="1:7" ht="19" customHeight="1">
+      <c r="A150" s="8">
         <v>1145487730</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D150" s="7">
+      <c r="C150" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="3">
         <v>1</v>
       </c>
-      <c r="E150" s="11"/>
-      <c r="F150" s="12"/>
-    </row>
-    <row r="151" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A151" s="4">
+      <c r="E150" s="5"/>
+      <c r="F150" s="14"/>
+      <c r="G150" s="18"/>
+    </row>
+    <row r="151" spans="1:7" ht="19" customHeight="1">
+      <c r="A151" s="8">
         <v>1146809536</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D151" s="7">
+      <c r="C151" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="3">
         <v>1</v>
       </c>
-      <c r="E151" s="11"/>
-      <c r="F151" s="12"/>
-    </row>
-    <row r="152" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A152" s="4">
+      <c r="E151" s="5"/>
+      <c r="F151" s="14"/>
+      <c r="G151" s="18"/>
+    </row>
+    <row r="152" spans="1:7" ht="19" customHeight="1">
+      <c r="A152" s="8">
         <v>1164976993</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D152" s="7">
+      <c r="C152" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D152" s="3">
         <v>1</v>
       </c>
-      <c r="E152" s="11"/>
-      <c r="F152" s="12"/>
-    </row>
-    <row r="153" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A153" s="4">
+      <c r="E152" s="5"/>
+      <c r="F152" s="14"/>
+      <c r="G152" s="18"/>
+    </row>
+    <row r="153" spans="1:7" ht="19" customHeight="1">
+      <c r="A153" s="8">
         <v>1146821820</v>
       </c>
-      <c r="B153" s="13" t="s">
+      <c r="B153" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D153" s="7">
+      <c r="C153" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D153" s="3">
         <v>1</v>
       </c>
-      <c r="E153" s="11"/>
-      <c r="F153" s="12"/>
-    </row>
-    <row r="154" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A154" s="4">
+      <c r="E153" s="5"/>
+      <c r="F153" s="14"/>
+      <c r="G153" s="18"/>
+    </row>
+    <row r="154" spans="1:7" ht="19" customHeight="1">
+      <c r="A154" s="8">
         <v>1146526668</v>
       </c>
-      <c r="B154" s="13" t="s">
+      <c r="B154" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D154" s="7">
+      <c r="C154" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" s="3">
         <v>1</v>
       </c>
-      <c r="E154" s="11"/>
-      <c r="F154" s="12"/>
-    </row>
-    <row r="155" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A155" s="4">
+      <c r="E154" s="5"/>
+      <c r="F154" s="14"/>
+      <c r="G154" s="18"/>
+    </row>
+    <row r="155" spans="1:7" ht="19" customHeight="1">
+      <c r="A155" s="8">
         <v>1149762419</v>
       </c>
-      <c r="B155" s="13" t="s">
+      <c r="B155" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D155" s="7">
+      <c r="C155" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D155" s="3">
         <v>1</v>
       </c>
-      <c r="E155" s="11"/>
-      <c r="F155" s="12"/>
-    </row>
-    <row r="156" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A156" s="4">
+      <c r="E155" s="5"/>
+      <c r="F155" s="14"/>
+      <c r="G155" s="18"/>
+    </row>
+    <row r="156" spans="1:7" ht="19" customHeight="1">
+      <c r="A156" s="8">
         <v>1146972862</v>
       </c>
-      <c r="B156" s="13" t="s">
+      <c r="B156" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D156" s="7">
+      <c r="C156" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D156" s="3">
         <v>1</v>
       </c>
-      <c r="E156" s="11"/>
-      <c r="F156" s="12"/>
-    </row>
-    <row r="157" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A157" s="4">
+      <c r="E156" s="5"/>
+      <c r="F156" s="14"/>
+      <c r="G156" s="18"/>
+    </row>
+    <row r="157" spans="1:7" ht="19" customHeight="1">
+      <c r="A157" s="8">
         <v>1148273418</v>
       </c>
-      <c r="B157" s="13" t="s">
+      <c r="B157" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D157" s="7">
+      <c r="C157" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D157" s="3">
         <v>1</v>
       </c>
-      <c r="E157" s="11"/>
-      <c r="F157" s="12"/>
-    </row>
-    <row r="158" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A158" s="4">
+      <c r="E157" s="5"/>
+      <c r="F157" s="14"/>
+      <c r="G157" s="18"/>
+    </row>
+    <row r="158" spans="1:7" ht="19" customHeight="1">
+      <c r="A158" s="8">
         <v>1148688326</v>
       </c>
-      <c r="B158" s="13" t="s">
+      <c r="B158" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D158" s="7">
+      <c r="C158" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D158" s="3">
         <v>1</v>
       </c>
-      <c r="E158" s="11"/>
-      <c r="F158" s="12"/>
-    </row>
-    <row r="159" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A159" s="4">
+      <c r="E158" s="5"/>
+      <c r="F158" s="14"/>
+      <c r="G158" s="18"/>
+    </row>
+    <row r="159" spans="1:7" ht="19" customHeight="1">
+      <c r="A159" s="8">
         <v>1146775844</v>
       </c>
-      <c r="B159" s="13" t="s">
+      <c r="B159" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D159" s="7">
+      <c r="C159" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D159" s="3">
         <v>1</v>
       </c>
-      <c r="E159" s="11"/>
-      <c r="F159" s="12"/>
-    </row>
-    <row r="160" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A160" s="4">
+      <c r="E159" s="5"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="18"/>
+    </row>
+    <row r="160" spans="1:7" ht="19" customHeight="1">
+      <c r="A160" s="8">
         <v>2344822255</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D160" s="7">
+      <c r="C160" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="3">
         <v>1</v>
       </c>
-      <c r="E160" s="11"/>
-      <c r="F160" s="12"/>
-    </row>
-    <row r="161" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A161" s="4">
+      <c r="E160" s="5"/>
+      <c r="F160" s="14"/>
+      <c r="G160" s="18"/>
+    </row>
+    <row r="161" spans="1:7" ht="19" customHeight="1">
+      <c r="A161" s="8">
         <v>1150838223</v>
       </c>
-      <c r="B161" s="13" t="s">
+      <c r="B161" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D161" s="7">
+      <c r="C161" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D161" s="3">
         <v>1</v>
       </c>
-      <c r="E161" s="11"/>
-      <c r="F161" s="12"/>
-    </row>
-    <row r="162" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A162" s="4">
+      <c r="E161" s="5"/>
+      <c r="F161" s="14"/>
+      <c r="G161" s="18"/>
+    </row>
+    <row r="162" spans="1:7" ht="19" customHeight="1">
+      <c r="A162" s="8">
         <v>1146376064</v>
       </c>
-      <c r="B162" s="13" t="s">
+      <c r="B162" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D162" s="7">
+      <c r="C162" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D162" s="3">
         <v>1</v>
       </c>
-      <c r="E162" s="11"/>
-      <c r="F162" s="12"/>
-    </row>
-    <row r="163" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A163" s="4">
+      <c r="E162" s="5"/>
+      <c r="F162" s="14"/>
+      <c r="G162" s="18"/>
+    </row>
+    <row r="163" spans="1:7" ht="19" customHeight="1">
+      <c r="A163" s="8">
         <v>1144789813</v>
       </c>
-      <c r="B163" s="13" t="s">
+      <c r="B163" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D163" s="7">
+      <c r="C163" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D163" s="3">
         <v>1</v>
       </c>
-      <c r="E163" s="11"/>
-      <c r="F163" s="12"/>
-    </row>
-    <row r="164" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A164" s="4">
+      <c r="E163" s="5"/>
+      <c r="F163" s="14"/>
+      <c r="G163" s="18"/>
+    </row>
+    <row r="164" spans="1:7" ht="19" customHeight="1">
+      <c r="A164" s="8">
         <v>1146471519</v>
       </c>
-      <c r="B164" s="13" t="s">
+      <c r="B164" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D164" s="7">
+      <c r="C164" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D164" s="3">
         <v>1</v>
       </c>
-      <c r="E164" s="11"/>
-      <c r="F164" s="12"/>
-    </row>
-    <row r="165" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A165" s="4">
+      <c r="E164" s="5"/>
+      <c r="F164" s="14"/>
+      <c r="G164" s="18"/>
+    </row>
+    <row r="165" spans="1:7" ht="19" customHeight="1">
+      <c r="A165" s="8">
         <v>1145431654</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D165" s="7">
+      <c r="C165" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D165" s="3">
         <v>1</v>
       </c>
-      <c r="E165" s="11"/>
-      <c r="F165" s="12"/>
-    </row>
-    <row r="166" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A166" s="4">
+      <c r="E165" s="5"/>
+      <c r="F165" s="14"/>
+      <c r="G165" s="18"/>
+    </row>
+    <row r="166" spans="1:7" ht="19" customHeight="1">
+      <c r="A166" s="8">
         <v>1148252990</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D166" s="7">
+      <c r="C166" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D166" s="3">
         <v>2</v>
       </c>
-      <c r="E166" s="11"/>
-      <c r="F166" s="12"/>
-    </row>
-    <row r="167" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A167" s="4">
+      <c r="E166" s="5"/>
+      <c r="F166" s="14"/>
+      <c r="G166" s="18"/>
+    </row>
+    <row r="167" spans="1:7" ht="19" customHeight="1">
+      <c r="A167" s="8">
         <v>1149306225</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D167" s="7">
+      <c r="C167" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D167" s="3">
         <v>2</v>
       </c>
-      <c r="E167" s="11"/>
-      <c r="F167" s="12"/>
-    </row>
-    <row r="168" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A168" s="4">
+      <c r="E167" s="5"/>
+      <c r="F167" s="14"/>
+      <c r="G167" s="18"/>
+    </row>
+    <row r="168" spans="1:7" ht="19" customHeight="1">
+      <c r="A168" s="8">
         <v>1151264437</v>
       </c>
-      <c r="B168" s="13" t="s">
+      <c r="B168" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D168" s="7">
+      <c r="C168" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D168" s="3">
         <v>2</v>
       </c>
-      <c r="E168" s="11"/>
-      <c r="F168" s="12"/>
-    </row>
-    <row r="169" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A169" s="4">
+      <c r="E168" s="5"/>
+      <c r="F168" s="14"/>
+      <c r="G168" s="18"/>
+    </row>
+    <row r="169" spans="1:7" ht="19" customHeight="1">
+      <c r="A169" s="8">
         <v>1150158754</v>
       </c>
-      <c r="B169" s="13" t="s">
+      <c r="B169" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C169" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D169" s="7">
+      <c r="C169" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D169" s="3">
         <v>2</v>
       </c>
-      <c r="E169" s="11"/>
-      <c r="F169" s="12"/>
-    </row>
-    <row r="170" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A170" s="4">
+      <c r="E169" s="5"/>
+      <c r="F169" s="14"/>
+      <c r="G169" s="18"/>
+    </row>
+    <row r="170" spans="1:7" ht="19" customHeight="1">
+      <c r="A170" s="8">
         <v>1148596271</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C170" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D170" s="7">
+      <c r="C170" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D170" s="3">
         <v>2</v>
       </c>
-      <c r="E170" s="11"/>
-      <c r="F170" s="12"/>
-    </row>
-    <row r="171" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A171" s="4">
+      <c r="E170" s="5"/>
+      <c r="F170" s="14"/>
+      <c r="G170" s="18"/>
+    </row>
+    <row r="171" spans="1:7" ht="19" customHeight="1">
+      <c r="A171" s="8">
         <v>1147407355</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C171" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D171" s="7">
+      <c r="C171" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D171" s="3">
         <v>2</v>
       </c>
-      <c r="E171" s="11"/>
-      <c r="F171" s="12"/>
-    </row>
-    <row r="172" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A172" s="4">
+      <c r="E171" s="5"/>
+      <c r="F171" s="14"/>
+      <c r="G171" s="18"/>
+    </row>
+    <row r="172" spans="1:7" ht="19" customHeight="1">
+      <c r="A172" s="8">
         <v>1146987373</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D172" s="7">
+      <c r="C172" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D172" s="3">
         <v>2</v>
       </c>
-      <c r="E172" s="11"/>
-      <c r="F172" s="12"/>
-    </row>
-    <row r="173" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A173" s="4">
+      <c r="E172" s="5"/>
+      <c r="F172" s="14"/>
+      <c r="G172" s="18"/>
+    </row>
+    <row r="173" spans="1:7" ht="19" customHeight="1">
+      <c r="A173" s="8">
         <v>1142858388</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C173" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D173" s="7">
+      <c r="C173" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D173" s="3">
         <v>2</v>
       </c>
-      <c r="E173" s="11"/>
-      <c r="F173" s="12"/>
-    </row>
-    <row r="174" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A174" s="4">
+      <c r="E173" s="5"/>
+      <c r="F173" s="14"/>
+      <c r="G173" s="18"/>
+    </row>
+    <row r="174" spans="1:7" ht="19" customHeight="1">
+      <c r="A174" s="8">
         <v>1148535568</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D174" s="7">
+      <c r="C174" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D174" s="3">
         <v>2</v>
       </c>
-      <c r="E174" s="11"/>
-      <c r="F174" s="12"/>
-    </row>
-    <row r="175" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A175" s="4">
+      <c r="E174" s="5"/>
+      <c r="F174" s="14"/>
+      <c r="G174" s="18"/>
+    </row>
+    <row r="175" spans="1:7" ht="19" customHeight="1">
+      <c r="A175" s="8">
         <v>1147255028</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D175" s="7">
+      <c r="C175" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D175" s="3">
         <v>2</v>
       </c>
-      <c r="E175" s="11"/>
-      <c r="F175" s="12"/>
-    </row>
-    <row r="176" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A176" s="4">
+      <c r="E175" s="5"/>
+      <c r="F175" s="14"/>
+      <c r="G175" s="18"/>
+    </row>
+    <row r="176" spans="1:7" ht="19" customHeight="1">
+      <c r="A176" s="8">
         <v>1147682353</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D176" s="7">
+      <c r="C176" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D176" s="3">
         <v>2</v>
       </c>
-      <c r="E176" s="11"/>
-      <c r="F176" s="12"/>
-    </row>
-    <row r="177" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A177" s="4">
+      <c r="E176" s="5"/>
+      <c r="F176" s="14"/>
+      <c r="G176" s="18"/>
+    </row>
+    <row r="177" spans="1:7" ht="19" customHeight="1">
+      <c r="A177" s="8">
         <v>1146380868</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C177" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D177" s="7">
+      <c r="C177" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D177" s="3">
         <v>2</v>
       </c>
-      <c r="E177" s="11"/>
-      <c r="F177" s="12"/>
-    </row>
-    <row r="178" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A178" s="4">
+      <c r="E177" s="5"/>
+      <c r="F177" s="14"/>
+      <c r="G177" s="18"/>
+    </row>
+    <row r="178" spans="1:7" ht="19" customHeight="1">
+      <c r="A178" s="8">
         <v>1149234906</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D178" s="7">
+      <c r="C178" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D178" s="3">
         <v>2</v>
       </c>
-      <c r="E178" s="11"/>
-      <c r="F178" s="12"/>
-    </row>
-    <row r="179" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A179" s="4">
+      <c r="E178" s="5"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="18"/>
+    </row>
+    <row r="179" spans="1:7" ht="19" customHeight="1">
+      <c r="A179" s="8">
         <v>1145460539</v>
       </c>
       <c r="B179" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D179" s="7">
+      <c r="C179" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D179" s="3">
         <v>2</v>
       </c>
-      <c r="E179" s="11"/>
-      <c r="F179" s="12"/>
-    </row>
-    <row r="180" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A180" s="4">
+      <c r="E179" s="5"/>
+      <c r="F179" s="14"/>
+      <c r="G179" s="18"/>
+    </row>
+    <row r="180" spans="1:7" ht="19" customHeight="1">
+      <c r="A180" s="8">
         <v>1146879539</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C180" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D180" s="7">
+      <c r="C180" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D180" s="3">
         <v>2</v>
       </c>
-      <c r="E180" s="11"/>
-      <c r="F180" s="12"/>
-    </row>
-    <row r="181" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A181" s="4">
+      <c r="E180" s="5"/>
+      <c r="F180" s="14"/>
+      <c r="G180" s="18"/>
+    </row>
+    <row r="181" spans="1:7" ht="19" customHeight="1">
+      <c r="A181" s="8">
         <v>1146061013</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C181" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D181" s="7">
+      <c r="C181" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D181" s="3">
         <v>2</v>
       </c>
-      <c r="E181" s="11"/>
-      <c r="F181" s="12"/>
-    </row>
-    <row r="182" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A182" s="4">
+      <c r="E181" s="5"/>
+      <c r="F181" s="14"/>
+      <c r="G181" s="18"/>
+    </row>
+    <row r="182" spans="1:7" ht="19" customHeight="1">
+      <c r="A182" s="8">
         <v>1161327497</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B182" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C182" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D182" s="7">
+      <c r="C182" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D182" s="3">
         <v>2</v>
       </c>
-      <c r="E182" s="11"/>
-      <c r="F182" s="12"/>
-    </row>
-    <row r="183" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A183" s="4">
+      <c r="E182" s="5"/>
+      <c r="F182" s="14"/>
+      <c r="G182" s="18"/>
+    </row>
+    <row r="183" spans="1:7" ht="19" customHeight="1">
+      <c r="A183" s="8">
         <v>1146546294</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C183" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D183" s="7">
+      <c r="C183" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D183" s="3">
         <v>2</v>
       </c>
-      <c r="E183" s="11"/>
-      <c r="F183" s="12"/>
-    </row>
-    <row r="184" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A184" s="4">
+      <c r="E183" s="5"/>
+      <c r="F183" s="14"/>
+      <c r="G183" s="18"/>
+    </row>
+    <row r="184" spans="1:7" ht="19" customHeight="1">
+      <c r="A184" s="8">
         <v>1147314809</v>
       </c>
-      <c r="B184" s="13" t="s">
+      <c r="B184" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C184" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D184" s="7">
+      <c r="C184" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D184" s="3">
         <v>2</v>
       </c>
-      <c r="E184" s="11"/>
-      <c r="F184" s="12"/>
-    </row>
-    <row r="185" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A185" s="4">
+      <c r="E184" s="5"/>
+      <c r="F184" s="14"/>
+      <c r="G184" s="18"/>
+    </row>
+    <row r="185" spans="1:7" ht="19" customHeight="1">
+      <c r="A185" s="8">
         <v>1148907890</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C185" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D185" s="7">
+      <c r="C185" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D185" s="3">
         <v>2</v>
       </c>
-      <c r="E185" s="11"/>
-      <c r="F185" s="12"/>
-    </row>
-    <row r="186" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A186" s="4">
+      <c r="E185" s="5"/>
+      <c r="F185" s="14"/>
+      <c r="G185" s="18"/>
+    </row>
+    <row r="186" spans="1:7" ht="19" customHeight="1">
+      <c r="A186" s="8">
         <v>1148220138</v>
       </c>
-      <c r="B186" s="13" t="s">
+      <c r="B186" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C186" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D186" s="7">
+      <c r="C186" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D186" s="3">
         <v>2</v>
       </c>
-      <c r="E186" s="11"/>
-      <c r="F186" s="12"/>
-    </row>
-    <row r="187" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A187" s="4">
+      <c r="E186" s="5"/>
+      <c r="F186" s="14"/>
+      <c r="G186" s="18"/>
+    </row>
+    <row r="187" spans="1:7" ht="19" customHeight="1">
+      <c r="A187" s="8">
         <v>1149587360</v>
       </c>
-      <c r="B187" s="13" t="s">
+      <c r="B187" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D187" s="7">
+      <c r="C187" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D187" s="3">
         <v>2</v>
       </c>
-      <c r="E187" s="11"/>
-      <c r="F187" s="12"/>
-    </row>
-    <row r="188" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A188" s="4">
+      <c r="E187" s="5"/>
+      <c r="F187" s="14"/>
+      <c r="G187" s="18"/>
+    </row>
+    <row r="188" spans="1:7" ht="19" customHeight="1">
+      <c r="A188" s="8">
         <v>1149826164</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="B188" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D188" s="7">
+      <c r="C188" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D188" s="3">
         <v>2</v>
       </c>
-      <c r="E188" s="11"/>
-      <c r="F188" s="12"/>
-    </row>
-    <row r="189" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A189" s="4">
+      <c r="E188" s="5"/>
+      <c r="F188" s="14"/>
+      <c r="G188" s="18"/>
+    </row>
+    <row r="189" spans="1:7" ht="19" customHeight="1">
+      <c r="A189" s="8">
         <v>2337878892</v>
       </c>
-      <c r="B189" s="13" t="s">
+      <c r="B189" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D189" s="7">
+      <c r="C189" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D189" s="3">
         <v>2</v>
       </c>
-      <c r="E189" s="11"/>
-      <c r="F189" s="12"/>
-    </row>
-    <row r="190" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A190" s="4">
+      <c r="E189" s="5"/>
+      <c r="F189" s="14"/>
+      <c r="G189" s="18"/>
+    </row>
+    <row r="190" spans="1:7" ht="19" customHeight="1">
+      <c r="A190" s="8">
         <v>1149812065</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C190" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D190" s="7">
+      <c r="C190" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D190" s="3">
         <v>3</v>
       </c>
-      <c r="E190" s="11"/>
-      <c r="F190" s="12"/>
-    </row>
-    <row r="191" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A191" s="4">
+      <c r="E190" s="5"/>
+      <c r="F190" s="14"/>
+      <c r="G190" s="18"/>
+    </row>
+    <row r="191" spans="1:7" ht="19" customHeight="1">
+      <c r="A191" s="8">
         <v>1147392706</v>
       </c>
-      <c r="B191" s="13" t="s">
+      <c r="B191" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D191" s="7">
+      <c r="C191" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D191" s="3">
         <v>3</v>
       </c>
-      <c r="E191" s="11"/>
-      <c r="F191" s="12"/>
-    </row>
-    <row r="192" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A192" s="4">
+      <c r="E191" s="5"/>
+      <c r="F191" s="14"/>
+      <c r="G191" s="18"/>
+    </row>
+    <row r="192" spans="1:7" ht="19" customHeight="1">
+      <c r="A192" s="8">
         <v>1145344212</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="B192" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C192" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D192" s="7">
+      <c r="C192" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D192" s="3">
         <v>3</v>
       </c>
-      <c r="E192" s="11"/>
-      <c r="F192" s="12"/>
-    </row>
-    <row r="193" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A193" s="4">
+      <c r="E192" s="5"/>
+      <c r="F192" s="14"/>
+      <c r="G192" s="18"/>
+    </row>
+    <row r="193" spans="1:7" ht="19" customHeight="1">
+      <c r="A193" s="8">
         <v>1151073234</v>
       </c>
-      <c r="B193" s="13" t="s">
+      <c r="B193" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C193" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D193" s="7">
+      <c r="C193" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D193" s="3">
         <v>3</v>
       </c>
-      <c r="E193" s="11"/>
-      <c r="F193" s="12"/>
-    </row>
-    <row r="194" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A194" s="4">
+      <c r="E193" s="5"/>
+      <c r="F193" s="14"/>
+      <c r="G193" s="18"/>
+    </row>
+    <row r="194" spans="1:7" ht="19" customHeight="1">
+      <c r="A194" s="8">
         <v>1149661421</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B194" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="C194" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D194" s="7">
+      <c r="C194" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D194" s="3">
         <v>3</v>
       </c>
-      <c r="E194" s="11"/>
-      <c r="F194" s="12"/>
-    </row>
-    <row r="195" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A195" s="4">
+      <c r="E194" s="5"/>
+      <c r="F194" s="14"/>
+      <c r="G194" s="18"/>
+    </row>
+    <row r="195" spans="1:7" ht="19" customHeight="1">
+      <c r="A195" s="8">
         <v>1147116089</v>
       </c>
-      <c r="B195" s="13" t="s">
+      <c r="B195" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C195" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D195" s="7">
+      <c r="C195" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D195" s="3">
         <v>3</v>
       </c>
-      <c r="E195" s="11"/>
-      <c r="F195" s="12"/>
-    </row>
-    <row r="196" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A196" s="4">
+      <c r="E195" s="5"/>
+      <c r="F195" s="14"/>
+      <c r="G195" s="18"/>
+    </row>
+    <row r="196" spans="1:7" ht="19" customHeight="1">
+      <c r="A196" s="8">
         <v>1147116014</v>
       </c>
-      <c r="B196" s="13" t="s">
+      <c r="B196" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C196" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D196" s="7">
+      <c r="C196" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D196" s="3">
         <v>3</v>
       </c>
-      <c r="E196" s="11"/>
-      <c r="F196" s="12"/>
-    </row>
-    <row r="197" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A197" s="4">
+      <c r="E196" s="5"/>
+      <c r="F196" s="14"/>
+      <c r="G196" s="18"/>
+    </row>
+    <row r="197" spans="1:7" ht="19" customHeight="1">
+      <c r="A197" s="8">
         <v>1147138059</v>
       </c>
-      <c r="B197" s="13" t="s">
+      <c r="B197" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C197" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D197" s="7">
+      <c r="C197" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D197" s="3">
         <v>3</v>
       </c>
-      <c r="E197" s="11"/>
-      <c r="F197" s="12"/>
-    </row>
-    <row r="198" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A198" s="4">
+      <c r="E197" s="5"/>
+      <c r="F197" s="14"/>
+      <c r="G197" s="18"/>
+    </row>
+    <row r="198" spans="1:7" ht="19" customHeight="1">
+      <c r="A198" s="8">
         <v>1146518921</v>
       </c>
-      <c r="B198" s="13" t="s">
+      <c r="B198" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C198" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D198" s="7">
+      <c r="C198" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D198" s="3">
         <v>3</v>
       </c>
-      <c r="E198" s="11"/>
-      <c r="F198" s="12"/>
-    </row>
-    <row r="199" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A199" s="4">
+      <c r="E198" s="5"/>
+      <c r="F198" s="14"/>
+      <c r="G198" s="18"/>
+    </row>
+    <row r="199" spans="1:7" ht="19" customHeight="1">
+      <c r="A199" s="8">
         <v>1154144388</v>
       </c>
-      <c r="B199" s="13" t="s">
+      <c r="B199" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D199" s="7">
+      <c r="C199" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D199" s="3">
         <v>3</v>
       </c>
-      <c r="E199" s="11"/>
-      <c r="F199" s="12"/>
-    </row>
-    <row r="200" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A200" s="4">
+      <c r="E199" s="5"/>
+      <c r="F199" s="14"/>
+      <c r="G199" s="18"/>
+    </row>
+    <row r="200" spans="1:7" ht="19" customHeight="1">
+      <c r="A200" s="8">
         <v>1147117111</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B200" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D200" s="7">
+      <c r="C200" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D200" s="3">
         <v>3</v>
       </c>
-      <c r="E200" s="11"/>
-      <c r="F200" s="12"/>
-    </row>
-    <row r="201" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A201" s="4">
+      <c r="E200" s="5"/>
+      <c r="F200" s="14"/>
+      <c r="G200" s="18"/>
+    </row>
+    <row r="201" spans="1:7" ht="19" customHeight="1">
+      <c r="A201" s="8">
         <v>1147073637</v>
       </c>
-      <c r="B201" s="13" t="s">
+      <c r="B201" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C201" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D201" s="7">
+      <c r="C201" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D201" s="3">
         <v>3</v>
       </c>
-      <c r="E201" s="11"/>
-      <c r="F201" s="12"/>
-    </row>
-    <row r="202" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A202" s="4">
+      <c r="E201" s="5"/>
+      <c r="F201" s="14"/>
+      <c r="G201" s="18"/>
+    </row>
+    <row r="202" spans="1:7" ht="19" customHeight="1">
+      <c r="A202" s="8">
         <v>1149366534</v>
       </c>
-      <c r="B202" s="13" t="s">
+      <c r="B202" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C202" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D202" s="7">
+      <c r="C202" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D202" s="3">
         <v>3</v>
       </c>
-      <c r="E202" s="11"/>
-      <c r="F202" s="12"/>
-    </row>
-    <row r="203" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A203" s="4">
+      <c r="E202" s="5"/>
+      <c r="F202" s="14"/>
+      <c r="G202" s="18"/>
+    </row>
+    <row r="203" spans="1:7" ht="19" customHeight="1">
+      <c r="A203" s="8">
         <v>1151122668</v>
       </c>
-      <c r="B203" s="13" t="s">
+      <c r="B203" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C203" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D203" s="7">
+      <c r="C203" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D203" s="3">
         <v>3</v>
       </c>
-      <c r="E203" s="11"/>
-      <c r="F203" s="12"/>
-    </row>
-    <row r="204" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A204" s="4">
+      <c r="E203" s="5"/>
+      <c r="F203" s="14"/>
+      <c r="G203" s="18"/>
+    </row>
+    <row r="204" spans="1:7" ht="19" customHeight="1">
+      <c r="A204" s="8">
         <v>1147318826</v>
       </c>
-      <c r="B204" s="13" t="s">
+      <c r="B204" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C204" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D204" s="7">
+      <c r="C204" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D204" s="3">
         <v>3</v>
       </c>
-      <c r="E204" s="11"/>
-      <c r="F204" s="12"/>
-    </row>
-    <row r="205" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A205" s="4">
+      <c r="E204" s="5"/>
+      <c r="F204" s="14"/>
+      <c r="G204" s="18"/>
+    </row>
+    <row r="205" spans="1:7" ht="19" customHeight="1">
+      <c r="A205" s="8">
         <v>2282275516</v>
       </c>
-      <c r="B205" s="13" t="s">
+      <c r="B205" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C205" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D205" s="7">
+      <c r="C205" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D205" s="3">
         <v>3</v>
       </c>
-      <c r="E205" s="11"/>
-      <c r="F205" s="12"/>
-    </row>
-    <row r="206" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A206" s="4">
+      <c r="E205" s="5"/>
+      <c r="F205" s="14"/>
+      <c r="G205" s="18"/>
+    </row>
+    <row r="206" spans="1:7" ht="19" customHeight="1">
+      <c r="A206" s="8">
         <v>1148331737</v>
       </c>
-      <c r="B206" s="13" t="s">
+      <c r="B206" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C206" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D206" s="7">
+      <c r="C206" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D206" s="3">
         <v>3</v>
       </c>
-      <c r="E206" s="11"/>
-      <c r="F206" s="12"/>
-    </row>
-    <row r="207" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A207" s="4">
+      <c r="E206" s="5"/>
+      <c r="F206" s="14"/>
+      <c r="G206" s="18"/>
+    </row>
+    <row r="207" spans="1:7" ht="19" customHeight="1">
+      <c r="A207" s="8">
         <v>1148003252</v>
       </c>
-      <c r="B207" s="13" t="s">
+      <c r="B207" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C207" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D207" s="7">
+      <c r="C207" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D207" s="3">
         <v>3</v>
       </c>
-      <c r="E207" s="11"/>
-      <c r="F207" s="12"/>
-    </row>
-    <row r="208" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A208" s="4">
+      <c r="E207" s="5"/>
+      <c r="F207" s="14"/>
+      <c r="G207" s="18"/>
+    </row>
+    <row r="208" spans="1:7" ht="19" customHeight="1">
+      <c r="A208" s="8">
         <v>1146792161</v>
       </c>
-      <c r="B208" s="13" t="s">
+      <c r="B208" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C208" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D208" s="7">
+      <c r="C208" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D208" s="3">
         <v>3</v>
       </c>
-      <c r="E208" s="11"/>
-      <c r="F208" s="12"/>
-    </row>
-    <row r="209" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A209" s="4">
+      <c r="E208" s="5"/>
+      <c r="F208" s="14"/>
+      <c r="G208" s="18"/>
+    </row>
+    <row r="209" spans="1:7" ht="19" customHeight="1">
+      <c r="A209" s="8">
         <v>1148196452</v>
       </c>
-      <c r="B209" s="13" t="s">
+      <c r="B209" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C209" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D209" s="7">
+      <c r="C209" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D209" s="3">
         <v>3</v>
       </c>
-      <c r="E209" s="11"/>
-      <c r="F209" s="12"/>
-    </row>
-    <row r="210" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A210" s="4">
+      <c r="E209" s="5"/>
+      <c r="F209" s="14"/>
+      <c r="G209" s="18"/>
+    </row>
+    <row r="210" spans="1:7" ht="19" customHeight="1">
+      <c r="A210" s="8">
         <v>1146902935</v>
       </c>
-      <c r="B210" s="13" t="s">
+      <c r="B210" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C210" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D210" s="7">
+      <c r="C210" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D210" s="3">
         <v>3</v>
       </c>
-      <c r="E210" s="11"/>
-      <c r="F210" s="12"/>
-    </row>
-    <row r="211" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A211" s="4">
+      <c r="E210" s="5"/>
+      <c r="F210" s="14"/>
+      <c r="G210" s="18"/>
+    </row>
+    <row r="211" spans="1:7" ht="19" customHeight="1">
+      <c r="A211" s="8">
         <v>1145718209</v>
       </c>
-      <c r="B211" s="13" t="s">
+      <c r="B211" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C211" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D211" s="7">
+      <c r="C211" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" s="3">
         <v>3</v>
       </c>
-      <c r="E211" s="11"/>
-      <c r="F211" s="12"/>
-    </row>
-    <row r="212" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A212" s="4">
+      <c r="E211" s="5"/>
+      <c r="F211" s="14"/>
+      <c r="G211" s="18"/>
+    </row>
+    <row r="212" spans="1:7" ht="19" customHeight="1">
+      <c r="A212" s="8">
         <v>1148921412</v>
       </c>
-      <c r="B212" s="13" t="s">
+      <c r="B212" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C212" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D212" s="7">
+      <c r="C212" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D212" s="3">
         <v>3</v>
       </c>
-      <c r="E212" s="11"/>
-      <c r="F212" s="12"/>
-    </row>
-    <row r="213" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A213" s="4">
+      <c r="E212" s="5"/>
+      <c r="F212" s="14"/>
+      <c r="G212" s="18"/>
+    </row>
+    <row r="213" spans="1:7" ht="19" customHeight="1">
+      <c r="A213" s="8">
         <v>1150070421</v>
       </c>
-      <c r="B213" s="13" t="s">
+      <c r="B213" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C213" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D213" s="7">
+      <c r="C213" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D213" s="3">
         <v>3</v>
       </c>
-      <c r="E213" s="11"/>
-      <c r="F213" s="12"/>
-    </row>
-    <row r="214" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A214" s="4">
+      <c r="E213" s="5"/>
+      <c r="F213" s="14"/>
+      <c r="G213" s="18"/>
+    </row>
+    <row r="214" spans="1:7" ht="19" customHeight="1">
+      <c r="A214" s="8">
         <v>1169254040</v>
       </c>
-      <c r="B214" s="13" t="s">
+      <c r="B214" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C214" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D214" s="7">
+      <c r="C214" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D214" s="3">
         <v>3</v>
       </c>
-      <c r="E214" s="11"/>
-      <c r="F214" s="12"/>
-    </row>
-    <row r="215" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A215" s="4">
+      <c r="E214" s="5"/>
+      <c r="F214" s="14"/>
+      <c r="G214" s="18"/>
+    </row>
+    <row r="215" spans="1:7" ht="19" customHeight="1">
+      <c r="A215" s="8">
         <v>1145733752</v>
       </c>
-      <c r="B215" s="13" t="s">
+      <c r="B215" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C215" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D215" s="7">
+      <c r="C215" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D215" s="3">
         <v>3</v>
       </c>
-      <c r="E215" s="11"/>
-      <c r="F215" s="12"/>
-    </row>
-    <row r="216" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A216" s="4">
+      <c r="E215" s="5"/>
+      <c r="F215" s="14"/>
+      <c r="G215" s="18"/>
+    </row>
+    <row r="216" spans="1:7" ht="19" customHeight="1">
+      <c r="A216" s="8">
         <v>1146851652</v>
       </c>
-      <c r="B216" s="13" t="s">
+      <c r="B216" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="C216" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D216" s="7">
+      <c r="C216" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D216" s="3">
         <v>3</v>
       </c>
-      <c r="E216" s="11"/>
-      <c r="F216" s="12"/>
-    </row>
-    <row r="217" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A217" s="4">
+      <c r="E216" s="5"/>
+      <c r="F216" s="14"/>
+      <c r="G216" s="18"/>
+    </row>
+    <row r="217" spans="1:7" ht="19" customHeight="1">
+      <c r="A217" s="8">
         <v>1146339948</v>
       </c>
-      <c r="B217" s="13" t="s">
+      <c r="B217" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C217" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D217" s="7">
+      <c r="C217" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D217" s="3">
         <v>4</v>
       </c>
-      <c r="E217" s="11"/>
-      <c r="F217" s="12"/>
-    </row>
-    <row r="218" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A218" s="4">
+      <c r="E217" s="5"/>
+      <c r="F217" s="14"/>
+      <c r="G217" s="18"/>
+    </row>
+    <row r="218" spans="1:7" ht="19" customHeight="1">
+      <c r="A218" s="8">
         <v>1156163931</v>
       </c>
-      <c r="B218" s="13" t="s">
+      <c r="B218" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C218" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D218" s="7">
+      <c r="C218" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D218" s="3">
         <v>4</v>
       </c>
-      <c r="E218" s="11"/>
-      <c r="F218" s="12"/>
-    </row>
-    <row r="219" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A219" s="4">
+      <c r="E218" s="5"/>
+      <c r="F218" s="14"/>
+      <c r="G218" s="18"/>
+    </row>
+    <row r="219" spans="1:7" ht="19" customHeight="1">
+      <c r="A219" s="8">
         <v>1148066275</v>
       </c>
-      <c r="B219" s="13" t="s">
+      <c r="B219" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D219" s="7">
+      <c r="C219" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D219" s="3">
         <v>4</v>
       </c>
-      <c r="E219" s="11"/>
-      <c r="F219" s="12"/>
-    </row>
-    <row r="220" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A220" s="4">
+      <c r="E219" s="5"/>
+      <c r="F219" s="14"/>
+      <c r="G219" s="18"/>
+    </row>
+    <row r="220" spans="1:7" ht="19" customHeight="1">
+      <c r="A220" s="8">
         <v>1148850710</v>
       </c>
-      <c r="B220" s="13" t="s">
+      <c r="B220" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C220" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D220" s="7">
+      <c r="C220" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D220" s="3">
         <v>4</v>
       </c>
-      <c r="E220" s="11"/>
-      <c r="F220" s="12"/>
-    </row>
-    <row r="221" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A221" s="4">
+      <c r="E220" s="5"/>
+      <c r="F220" s="14"/>
+      <c r="G220" s="18"/>
+    </row>
+    <row r="221" spans="1:7" ht="19" customHeight="1">
+      <c r="A221" s="8">
         <v>1146399652</v>
       </c>
-      <c r="B221" s="13" t="s">
+      <c r="B221" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="C221" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D221" s="7">
+      <c r="C221" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D221" s="3">
         <v>4</v>
       </c>
-      <c r="E221" s="11"/>
-      <c r="F221" s="12"/>
-    </row>
-    <row r="222" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A222" s="4">
+      <c r="E221" s="5"/>
+      <c r="F221" s="14"/>
+      <c r="G221" s="18"/>
+    </row>
+    <row r="222" spans="1:7" ht="19" customHeight="1">
+      <c r="A222" s="8">
         <v>1148398181</v>
       </c>
-      <c r="B222" s="13" t="s">
+      <c r="B222" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="C222" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D222" s="7">
+      <c r="C222" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D222" s="3">
         <v>4</v>
       </c>
-      <c r="E222" s="11"/>
-      <c r="F222" s="12"/>
-    </row>
-    <row r="223" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A223" s="4">
+      <c r="E222" s="5"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="18"/>
+    </row>
+    <row r="223" spans="1:7" ht="19" customHeight="1">
+      <c r="A223" s="8">
         <v>1145648166</v>
       </c>
-      <c r="B223" s="13" t="s">
+      <c r="B223" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C223" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D223" s="7">
+      <c r="C223" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D223" s="3">
         <v>4</v>
       </c>
-      <c r="E223" s="11"/>
-      <c r="F223" s="12"/>
-    </row>
-    <row r="224" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A224" s="4">
+      <c r="E223" s="5"/>
+      <c r="F223" s="14"/>
+      <c r="G223" s="18"/>
+    </row>
+    <row r="224" spans="1:7" ht="19" customHeight="1">
+      <c r="A224" s="8">
         <v>1147594236</v>
       </c>
-      <c r="B224" s="13" t="s">
+      <c r="B224" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C224" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D224" s="7">
+      <c r="C224" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D224" s="3">
         <v>4</v>
       </c>
-      <c r="E224" s="11"/>
-      <c r="F224" s="12"/>
-    </row>
-    <row r="225" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A225" s="4">
+      <c r="E224" s="5"/>
+      <c r="F224" s="14"/>
+      <c r="G224" s="18"/>
+    </row>
+    <row r="225" spans="1:7" ht="19" customHeight="1">
+      <c r="A225" s="8">
         <v>1146766389</v>
       </c>
-      <c r="B225" s="13" t="s">
+      <c r="B225" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C225" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D225" s="7">
+      <c r="C225" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D225" s="3">
         <v>4</v>
       </c>
-      <c r="E225" s="11"/>
-      <c r="F225" s="12"/>
-    </row>
-    <row r="226" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A226" s="4">
+      <c r="E225" s="5"/>
+      <c r="F225" s="14"/>
+      <c r="G225" s="18"/>
+    </row>
+    <row r="226" spans="1:7" ht="19" customHeight="1">
+      <c r="A226" s="8">
         <v>1148766015</v>
       </c>
       <c r="B226" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C226" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D226" s="7">
+      <c r="C226" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D226" s="3">
         <v>4</v>
       </c>
-      <c r="E226" s="11"/>
-      <c r="F226" s="12"/>
-    </row>
-    <row r="227" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A227" s="4">
+      <c r="E226" s="5"/>
+      <c r="F226" s="14"/>
+      <c r="G226" s="18"/>
+    </row>
+    <row r="227" spans="1:7" ht="19" customHeight="1">
+      <c r="A227" s="8">
         <v>1161794449</v>
       </c>
-      <c r="B227" s="13" t="s">
+      <c r="B227" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C227" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D227" s="7">
+      <c r="C227" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D227" s="3">
         <v>4</v>
       </c>
-      <c r="E227" s="11"/>
-      <c r="F227" s="12"/>
-    </row>
-    <row r="228" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A228" s="4">
+      <c r="E227" s="5"/>
+      <c r="F227" s="14"/>
+      <c r="G227" s="18"/>
+    </row>
+    <row r="228" spans="1:7" ht="19" customHeight="1">
+      <c r="A228" s="8">
         <v>1149400937</v>
       </c>
-      <c r="B228" s="13" t="s">
+      <c r="B228" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D228" s="7">
+      <c r="C228" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D228" s="3">
         <v>4</v>
       </c>
-      <c r="E228" s="11"/>
-      <c r="F228" s="12"/>
-    </row>
-    <row r="229" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A229" s="4">
+      <c r="E228" s="5"/>
+      <c r="F228" s="14"/>
+      <c r="G228" s="18"/>
+    </row>
+    <row r="229" spans="1:7" ht="19" customHeight="1">
+      <c r="A229" s="8">
         <v>1148097148</v>
       </c>
-      <c r="B229" s="13" t="s">
+      <c r="B229" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C229" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D229" s="7">
+      <c r="C229" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D229" s="3">
         <v>4</v>
       </c>
-      <c r="E229" s="11"/>
-      <c r="F229" s="12"/>
-    </row>
-    <row r="230" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A230" s="4">
+      <c r="E229" s="5"/>
+      <c r="F229" s="14"/>
+      <c r="G229" s="18"/>
+    </row>
+    <row r="230" spans="1:7" ht="19" customHeight="1">
+      <c r="A230" s="8">
         <v>1149512558</v>
       </c>
-      <c r="B230" s="13" t="s">
+      <c r="B230" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="C230" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D230" s="7">
+      <c r="C230" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D230" s="3">
         <v>4</v>
       </c>
-      <c r="E230" s="11"/>
-      <c r="F230" s="12"/>
-    </row>
-    <row r="231" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A231" s="4">
+      <c r="E230" s="5"/>
+      <c r="F230" s="14"/>
+      <c r="G230" s="18"/>
+    </row>
+    <row r="231" spans="1:7" ht="19" customHeight="1">
+      <c r="A231" s="8">
         <v>1148636135</v>
       </c>
-      <c r="B231" s="13" t="s">
+      <c r="B231" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="C231" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D231" s="7">
+      <c r="C231" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D231" s="3">
         <v>4</v>
       </c>
-      <c r="E231" s="11"/>
-      <c r="F231" s="12"/>
-    </row>
-    <row r="232" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A232" s="4">
+      <c r="E231" s="5"/>
+      <c r="F231" s="14"/>
+      <c r="G231" s="18"/>
+    </row>
+    <row r="232" spans="1:7" ht="19" customHeight="1">
+      <c r="A232" s="8">
         <v>1148833708</v>
       </c>
-      <c r="B232" s="13" t="s">
+      <c r="B232" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C232" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D232" s="7">
+      <c r="C232" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" s="3">
         <v>4</v>
       </c>
-      <c r="E232" s="11"/>
-      <c r="F232" s="12"/>
-    </row>
-    <row r="233" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A233" s="4">
+      <c r="E232" s="5"/>
+      <c r="F232" s="14"/>
+      <c r="G232" s="18"/>
+    </row>
+    <row r="233" spans="1:7" ht="19" customHeight="1">
+      <c r="A233" s="8">
         <v>1145244214</v>
       </c>
-      <c r="B233" s="13" t="s">
+      <c r="B233" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C233" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D233" s="7">
+      <c r="C233" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D233" s="3">
         <v>4</v>
       </c>
-      <c r="E233" s="11"/>
-      <c r="F233" s="12"/>
-    </row>
-    <row r="234" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A234" s="4">
+      <c r="E233" s="5"/>
+      <c r="F233" s="14"/>
+      <c r="G233" s="18"/>
+    </row>
+    <row r="234" spans="1:7" ht="19" customHeight="1">
+      <c r="A234" s="8">
         <v>1149415935</v>
       </c>
-      <c r="B234" s="13" t="s">
+      <c r="B234" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="C234" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D234" s="7">
+      <c r="C234" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D234" s="3">
         <v>4</v>
       </c>
-      <c r="E234" s="11"/>
-      <c r="F234" s="12"/>
-    </row>
-    <row r="235" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A235" s="4">
+      <c r="E234" s="5"/>
+      <c r="F234" s="14"/>
+      <c r="G234" s="18"/>
+    </row>
+    <row r="235" spans="1:7" ht="19" customHeight="1">
+      <c r="A235" s="8">
         <v>2282843446</v>
       </c>
-      <c r="B235" s="13" t="s">
+      <c r="B235" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C235" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D235" s="7">
+      <c r="C235" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="3">
         <v>4</v>
       </c>
-      <c r="E235" s="11"/>
-      <c r="F235" s="12"/>
-    </row>
-    <row r="236" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A236" s="4">
+      <c r="E235" s="5"/>
+      <c r="F235" s="14"/>
+      <c r="G235" s="18"/>
+    </row>
+    <row r="236" spans="1:7" ht="19" customHeight="1">
+      <c r="A236" s="8">
         <v>1147952509</v>
       </c>
-      <c r="B236" s="13" t="s">
+      <c r="B236" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="C236" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D236" s="7">
+      <c r="C236" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D236" s="3">
         <v>4</v>
       </c>
-      <c r="E236" s="11"/>
-      <c r="F236" s="12"/>
-    </row>
-    <row r="237" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A237" s="4">
+      <c r="E236" s="5"/>
+      <c r="F236" s="14"/>
+      <c r="G236" s="18"/>
+    </row>
+    <row r="237" spans="1:7" ht="19" customHeight="1">
+      <c r="A237" s="8">
         <v>1149342303</v>
       </c>
-      <c r="B237" s="13" t="s">
+      <c r="B237" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C237" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D237" s="7">
+      <c r="C237" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D237" s="3">
         <v>4</v>
       </c>
-      <c r="E237" s="11"/>
-      <c r="F237" s="12"/>
-    </row>
-    <row r="238" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A238" s="4">
+      <c r="E237" s="5"/>
+      <c r="F237" s="14"/>
+      <c r="G237" s="18"/>
+    </row>
+    <row r="238" spans="1:7" ht="19" customHeight="1">
+      <c r="A238" s="8">
         <v>1147346579</v>
       </c>
-      <c r="B238" s="13" t="s">
+      <c r="B238" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C238" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D238" s="7">
+      <c r="C238" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D238" s="3">
         <v>4</v>
       </c>
-      <c r="E238" s="11"/>
-      <c r="F238" s="12"/>
-    </row>
-    <row r="239" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A239" s="4">
+      <c r="E238" s="5"/>
+      <c r="F238" s="14"/>
+      <c r="G238" s="18"/>
+    </row>
+    <row r="239" spans="1:7" ht="19" customHeight="1">
+      <c r="A239" s="8">
         <v>1146982663</v>
       </c>
-      <c r="B239" s="13" t="s">
+      <c r="B239" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C239" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D239" s="7">
+      <c r="C239" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D239" s="3">
         <v>4</v>
       </c>
-      <c r="E239" s="11"/>
-      <c r="F239" s="12"/>
-    </row>
-    <row r="240" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A240" s="4">
+      <c r="E239" s="5"/>
+      <c r="F239" s="14"/>
+      <c r="G239" s="18"/>
+    </row>
+    <row r="240" spans="1:7" ht="19" customHeight="1">
+      <c r="A240" s="8">
         <v>1148895673</v>
       </c>
-      <c r="B240" s="13" t="s">
+      <c r="B240" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C240" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D240" s="7">
+      <c r="C240" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D240" s="3">
         <v>4</v>
       </c>
-      <c r="E240" s="11"/>
-      <c r="F240" s="12"/>
-    </row>
-    <row r="241" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A241" s="4">
+      <c r="E240" s="5"/>
+      <c r="F240" s="14"/>
+      <c r="G240" s="18"/>
+    </row>
+    <row r="241" spans="1:7" ht="19" customHeight="1">
+      <c r="A241" s="8">
         <v>1147803256</v>
       </c>
-      <c r="B241" s="10" t="s">
+      <c r="B241" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C241" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D241" s="7">
+      <c r="C241" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D241" s="3">
         <v>4</v>
       </c>
-      <c r="E241" s="11"/>
-      <c r="F241" s="12"/>
-    </row>
-    <row r="242" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A242" s="4">
+      <c r="E241" s="5"/>
+      <c r="F241" s="14"/>
+      <c r="G241" s="18"/>
+    </row>
+    <row r="242" spans="1:7" ht="19" customHeight="1">
+      <c r="A242" s="8">
         <v>1147817827</v>
       </c>
-      <c r="B242" s="13" t="s">
+      <c r="B242" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="C242" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D242" s="7">
+      <c r="C242" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D242" s="3">
         <v>4</v>
       </c>
-      <c r="E242" s="11"/>
-      <c r="F242" s="12"/>
-    </row>
-    <row r="243" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A243" s="4">
+      <c r="E242" s="5"/>
+      <c r="F242" s="14"/>
+      <c r="G242" s="18"/>
+    </row>
+    <row r="243" spans="1:7" ht="19" customHeight="1">
+      <c r="A243" s="8">
         <v>2317822274</v>
       </c>
-      <c r="B243" s="13" t="s">
+      <c r="B243" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C243" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D243" s="7">
+      <c r="C243" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D243" s="3">
         <v>5</v>
       </c>
-      <c r="E243" s="11"/>
-      <c r="F243" s="12"/>
-    </row>
-    <row r="244" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A244" s="4">
+      <c r="E243" s="5"/>
+      <c r="F243" s="14"/>
+      <c r="G243" s="18"/>
+    </row>
+    <row r="244" spans="1:7" ht="19" customHeight="1">
+      <c r="A244" s="8">
         <v>2368543738</v>
       </c>
-      <c r="B244" s="13" t="s">
+      <c r="B244" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C244" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D244" s="7">
+      <c r="C244" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D244" s="3">
         <v>5</v>
       </c>
-      <c r="E244" s="11"/>
-      <c r="F244" s="12"/>
-    </row>
-    <row r="245" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A245" s="4">
+      <c r="E244" s="5"/>
+      <c r="F244" s="14"/>
+      <c r="G244" s="18"/>
+    </row>
+    <row r="245" spans="1:7" ht="19" customHeight="1">
+      <c r="A245" s="8">
         <v>1147244998</v>
       </c>
-      <c r="B245" s="13" t="s">
+      <c r="B245" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="C245" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D245" s="7">
+      <c r="C245" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D245" s="3">
         <v>5</v>
       </c>
-      <c r="E245" s="11"/>
-      <c r="F245" s="12"/>
-    </row>
-    <row r="246" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A246" s="4">
+      <c r="E245" s="5"/>
+      <c r="F245" s="14"/>
+      <c r="G245" s="18"/>
+    </row>
+    <row r="246" spans="1:7" ht="19" customHeight="1">
+      <c r="A246" s="8">
         <v>1147138414</v>
       </c>
-      <c r="B246" s="13" t="s">
+      <c r="B246" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C246" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D246" s="7">
+      <c r="C246" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D246" s="3">
         <v>5</v>
       </c>
-      <c r="E246" s="11"/>
-      <c r="F246" s="12"/>
-    </row>
-    <row r="247" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A247" s="4">
+      <c r="E246" s="5"/>
+      <c r="F246" s="14"/>
+      <c r="G246" s="18"/>
+    </row>
+    <row r="247" spans="1:7" ht="19" customHeight="1">
+      <c r="A247" s="8">
         <v>1147800385</v>
       </c>
-      <c r="B247" s="13" t="s">
+      <c r="B247" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C247" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D247" s="7">
+      <c r="C247" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D247" s="3">
         <v>5</v>
       </c>
-      <c r="E247" s="11"/>
-      <c r="F247" s="12"/>
-    </row>
-    <row r="248" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A248" s="4">
+      <c r="E247" s="5"/>
+      <c r="F247" s="14"/>
+      <c r="G247" s="18"/>
+    </row>
+    <row r="248" spans="1:7" ht="19" customHeight="1">
+      <c r="A248" s="8">
         <v>1145124374</v>
       </c>
-      <c r="B248" s="13" t="s">
+      <c r="B248" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="C248" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D248" s="7">
+      <c r="C248" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D248" s="3">
         <v>5</v>
       </c>
-      <c r="E248" s="11"/>
-      <c r="F248" s="12"/>
-    </row>
-    <row r="249" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A249" s="4">
+      <c r="E248" s="5"/>
+      <c r="F248" s="14"/>
+      <c r="G248" s="18"/>
+    </row>
+    <row r="249" spans="1:7" ht="19" customHeight="1">
+      <c r="A249" s="8">
         <v>1146362445</v>
       </c>
-      <c r="B249" s="13" t="s">
+      <c r="B249" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="C249" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D249" s="7">
+      <c r="C249" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D249" s="3">
         <v>5</v>
       </c>
-      <c r="E249" s="11"/>
-      <c r="F249" s="12"/>
-    </row>
-    <row r="250" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A250" s="4">
+      <c r="E249" s="5"/>
+      <c r="F249" s="14"/>
+      <c r="G249" s="18"/>
+    </row>
+    <row r="250" spans="1:7" ht="19" customHeight="1">
+      <c r="A250" s="8">
         <v>1149064972</v>
       </c>
-      <c r="B250" s="13" t="s">
+      <c r="B250" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C250" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D250" s="7">
+      <c r="C250" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D250" s="3">
         <v>5</v>
       </c>
-      <c r="E250" s="11"/>
-      <c r="F250" s="12"/>
-    </row>
-    <row r="251" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A251" s="4">
+      <c r="E250" s="5"/>
+      <c r="F250" s="14"/>
+      <c r="G250" s="18"/>
+    </row>
+    <row r="251" spans="1:7" ht="19" customHeight="1">
+      <c r="A251" s="8">
         <v>1146726300</v>
       </c>
-      <c r="B251" s="13" t="s">
+      <c r="B251" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C251" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D251" s="7">
+      <c r="C251" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D251" s="3">
         <v>5</v>
       </c>
-      <c r="E251" s="11"/>
-      <c r="F251" s="12"/>
-    </row>
-    <row r="252" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A252" s="4">
+      <c r="E251" s="5"/>
+      <c r="F251" s="14"/>
+      <c r="G251" s="18"/>
+    </row>
+    <row r="252" spans="1:7" ht="19" customHeight="1">
+      <c r="A252" s="8">
         <v>1149452821</v>
       </c>
-      <c r="B252" s="13" t="s">
+      <c r="B252" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C252" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D252" s="7">
+      <c r="C252" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D252" s="3">
         <v>5</v>
       </c>
-      <c r="E252" s="11"/>
-      <c r="F252" s="12"/>
-    </row>
-    <row r="253" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A253" s="4">
+      <c r="E252" s="5"/>
+      <c r="F252" s="14"/>
+      <c r="G252" s="18"/>
+    </row>
+    <row r="253" spans="1:7" ht="19" customHeight="1">
+      <c r="A253" s="8">
         <v>1146907470</v>
       </c>
-      <c r="B253" s="13" t="s">
+      <c r="B253" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C253" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D253" s="7">
+      <c r="C253" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D253" s="3">
         <v>5</v>
       </c>
-      <c r="E253" s="11"/>
-      <c r="F253" s="12"/>
-    </row>
-    <row r="254" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A254" s="4">
+      <c r="E253" s="5"/>
+      <c r="F253" s="14"/>
+      <c r="G253" s="18"/>
+    </row>
+    <row r="254" spans="1:7" ht="19" customHeight="1">
+      <c r="A254" s="8">
         <v>1145545081</v>
       </c>
-      <c r="B254" s="13" t="s">
+      <c r="B254" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C254" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D254" s="7">
+      <c r="C254" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D254" s="3">
         <v>5</v>
       </c>
-      <c r="E254" s="11"/>
-      <c r="F254" s="12"/>
-    </row>
-    <row r="255" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A255" s="4">
+      <c r="E254" s="5"/>
+      <c r="F254" s="14"/>
+      <c r="G254" s="18"/>
+    </row>
+    <row r="255" spans="1:7" ht="19" customHeight="1">
+      <c r="A255" s="8">
         <v>1149931006</v>
       </c>
-      <c r="B255" s="13" t="s">
+      <c r="B255" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C255" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D255" s="7">
+      <c r="C255" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D255" s="3">
         <v>5</v>
       </c>
-      <c r="E255" s="11"/>
-      <c r="F255" s="12"/>
-    </row>
-    <row r="256" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A256" s="4">
+      <c r="E255" s="5"/>
+      <c r="F255" s="14"/>
+      <c r="G255" s="18"/>
+    </row>
+    <row r="256" spans="1:7" ht="19" customHeight="1">
+      <c r="A256" s="8">
         <v>2277240962</v>
       </c>
-      <c r="B256" s="13" t="s">
+      <c r="B256" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C256" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D256" s="7">
+      <c r="C256" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D256" s="3">
         <v>5</v>
       </c>
-      <c r="E256" s="11"/>
-      <c r="F256" s="12"/>
-    </row>
-    <row r="257" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A257" s="4">
+      <c r="E256" s="5"/>
+      <c r="F256" s="14"/>
+      <c r="G256" s="18"/>
+    </row>
+    <row r="257" spans="1:7" ht="19" customHeight="1">
+      <c r="A257" s="8">
         <v>1145922330</v>
       </c>
-      <c r="B257" s="13" t="s">
+      <c r="B257" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C257" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D257" s="7">
+      <c r="C257" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D257" s="3">
         <v>5</v>
       </c>
-      <c r="E257" s="11"/>
-      <c r="F257" s="12"/>
-    </row>
-    <row r="258" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A258" s="4">
+      <c r="E257" s="5"/>
+      <c r="F257" s="14"/>
+      <c r="G257" s="18"/>
+    </row>
+    <row r="258" spans="1:7" ht="19" customHeight="1">
+      <c r="A258" s="8">
         <v>1168345146</v>
       </c>
-      <c r="B258" s="13" t="s">
+      <c r="B258" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="C258" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D258" s="7">
+      <c r="C258" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D258" s="3">
         <v>5</v>
       </c>
-      <c r="E258" s="11"/>
-      <c r="F258" s="12"/>
-    </row>
-    <row r="259" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A259" s="4">
+      <c r="E258" s="5"/>
+      <c r="F258" s="14"/>
+      <c r="G258" s="18"/>
+    </row>
+    <row r="259" spans="1:7" ht="19" customHeight="1">
+      <c r="A259" s="8">
         <v>2395502558</v>
       </c>
-      <c r="B259" s="13" t="s">
+      <c r="B259" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C259" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D259" s="7">
+      <c r="C259" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D259" s="3">
         <v>5</v>
       </c>
-      <c r="E259" s="11"/>
-      <c r="F259" s="12"/>
-    </row>
-    <row r="260" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A260" s="4">
+      <c r="E259" s="5"/>
+      <c r="F259" s="14"/>
+      <c r="G259" s="18"/>
+    </row>
+    <row r="260" spans="1:7" ht="19" customHeight="1">
+      <c r="A260" s="8">
         <v>1146162415</v>
       </c>
-      <c r="B260" s="13" t="s">
+      <c r="B260" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="C260" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D260" s="7">
+      <c r="C260" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D260" s="3">
         <v>5</v>
       </c>
-      <c r="E260" s="11"/>
-      <c r="F260" s="12"/>
-    </row>
-    <row r="261" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A261" s="4">
+      <c r="E260" s="5"/>
+      <c r="F260" s="14"/>
+      <c r="G260" s="18"/>
+    </row>
+    <row r="261" spans="1:7" ht="19" customHeight="1">
+      <c r="A261" s="8">
         <v>1152946875</v>
       </c>
-      <c r="B261" s="13" t="s">
+      <c r="B261" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="C261" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D261" s="7">
+      <c r="C261" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D261" s="3">
         <v>5</v>
       </c>
-      <c r="E261" s="11"/>
-      <c r="F261" s="12"/>
-    </row>
-    <row r="262" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A262" s="4">
+      <c r="E261" s="5"/>
+      <c r="F261" s="14"/>
+      <c r="G261" s="18"/>
+    </row>
+    <row r="262" spans="1:7" ht="19" customHeight="1">
+      <c r="A262" s="8">
         <v>1150772208</v>
       </c>
-      <c r="B262" s="13" t="s">
+      <c r="B262" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C262" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D262" s="7">
+      <c r="C262" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D262" s="3">
         <v>5</v>
       </c>
-      <c r="E262" s="11"/>
-      <c r="F262" s="12"/>
-    </row>
-    <row r="263" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A263" s="4">
+      <c r="E262" s="5"/>
+      <c r="F262" s="14"/>
+      <c r="G262" s="18"/>
+    </row>
+    <row r="263" spans="1:7" ht="19" customHeight="1">
+      <c r="A263" s="8">
         <v>1148980897</v>
       </c>
-      <c r="B263" s="13" t="s">
+      <c r="B263" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C263" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D263" s="7">
+      <c r="C263" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D263" s="3">
         <v>5</v>
       </c>
-      <c r="E263" s="11"/>
-      <c r="F263" s="12"/>
-    </row>
-    <row r="264" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A264" s="4">
+      <c r="E263" s="5"/>
+      <c r="F263" s="14"/>
+      <c r="G263" s="18"/>
+    </row>
+    <row r="264" spans="1:7" ht="19" customHeight="1">
+      <c r="A264" s="8">
         <v>1146607773</v>
       </c>
-      <c r="B264" s="13" t="s">
+      <c r="B264" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C264" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D264" s="7">
+      <c r="C264" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D264" s="3">
         <v>5</v>
       </c>
-      <c r="E264" s="11"/>
-      <c r="F264" s="12"/>
-    </row>
-    <row r="265" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A265" s="4">
+      <c r="E264" s="5"/>
+      <c r="F264" s="14"/>
+      <c r="G264" s="18"/>
+    </row>
+    <row r="265" spans="1:7" ht="19" customHeight="1">
+      <c r="A265" s="8">
         <v>1146979255</v>
       </c>
-      <c r="B265" s="13" t="s">
+      <c r="B265" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C265" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D265" s="7">
+      <c r="C265" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D265" s="3">
         <v>5</v>
       </c>
-      <c r="E265" s="11"/>
-      <c r="F265" s="12"/>
-    </row>
-    <row r="266" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A266" s="4">
+      <c r="E265" s="5"/>
+      <c r="F265" s="14"/>
+      <c r="G265" s="18"/>
+    </row>
+    <row r="266" spans="1:7" ht="19" customHeight="1">
+      <c r="A266" s="8">
         <v>1149811893</v>
       </c>
-      <c r="B266" s="13" t="s">
+      <c r="B266" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C266" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D266" s="7">
+      <c r="C266" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D266" s="3">
         <v>5</v>
       </c>
-      <c r="E266" s="11"/>
-      <c r="F266" s="12"/>
-    </row>
-    <row r="267" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A267" s="17">
+      <c r="E266" s="5"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="18"/>
+    </row>
+    <row r="267" spans="1:7" ht="19" customHeight="1">
+      <c r="A267" s="9">
         <v>1149339077</v>
       </c>
-      <c r="B267" s="18" t="s">
+      <c r="B267" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C267" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D267" s="20">
+      <c r="C267" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D267" s="7">
         <v>6</v>
       </c>
-      <c r="E267" s="11"/>
-      <c r="F267" s="12"/>
-    </row>
-    <row r="268" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A268" s="17">
+      <c r="E267" s="5"/>
+      <c r="F267" s="14"/>
+      <c r="G267" s="18"/>
+    </row>
+    <row r="268" spans="1:7" ht="19" customHeight="1">
+      <c r="A268" s="9">
         <v>1149508598</v>
       </c>
-      <c r="B268" s="13" t="s">
+      <c r="B268" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C268" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D268" s="20">
+      <c r="C268" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D268" s="7">
         <v>6</v>
       </c>
-      <c r="E268" s="11"/>
-      <c r="F268" s="12"/>
-    </row>
-    <row r="269" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A269" s="17">
+      <c r="E268" s="5"/>
+      <c r="F268" s="14"/>
+      <c r="G268" s="18"/>
+    </row>
+    <row r="269" spans="1:7" ht="19" customHeight="1">
+      <c r="A269" s="9">
         <v>1147789356</v>
       </c>
-      <c r="B269" s="13" t="s">
+      <c r="B269" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C269" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D269" s="20">
+      <c r="C269" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D269" s="7">
         <v>6</v>
       </c>
-      <c r="E269" s="11"/>
-      <c r="F269" s="12"/>
-    </row>
-    <row r="270" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A270" s="17">
+      <c r="E269" s="5"/>
+      <c r="F269" s="14"/>
+      <c r="G269" s="18"/>
+    </row>
+    <row r="270" spans="1:7" ht="19" customHeight="1">
+      <c r="A270" s="9">
         <v>1146611726</v>
       </c>
-      <c r="B270" s="13" t="s">
+      <c r="B270" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="C270" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D270" s="20">
+      <c r="C270" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D270" s="7">
         <v>6</v>
       </c>
-      <c r="E270" s="11"/>
-      <c r="F270" s="12"/>
-    </row>
-    <row r="271" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A271" s="17">
+      <c r="E270" s="5"/>
+      <c r="F270" s="14"/>
+      <c r="G270" s="18"/>
+    </row>
+    <row r="271" spans="1:7" ht="19" customHeight="1">
+      <c r="A271" s="9">
         <v>1147262016</v>
       </c>
-      <c r="B271" s="13" t="s">
+      <c r="B271" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="C271" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D271" s="20">
+      <c r="C271" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D271" s="7">
         <v>6</v>
       </c>
-      <c r="E271" s="11"/>
-      <c r="F271" s="12"/>
-    </row>
-    <row r="272" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A272" s="17">
+      <c r="E271" s="5"/>
+      <c r="F271" s="14"/>
+      <c r="G271" s="18"/>
+    </row>
+    <row r="272" spans="1:7" ht="19" customHeight="1">
+      <c r="A272" s="9">
         <v>1147494130</v>
       </c>
-      <c r="B272" s="13" t="s">
+      <c r="B272" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="C272" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D272" s="20">
+      <c r="C272" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D272" s="7">
         <v>6</v>
       </c>
-      <c r="E272" s="11"/>
-      <c r="F272" s="12"/>
-    </row>
-    <row r="273" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A273" s="17">
+      <c r="E272" s="5"/>
+      <c r="F272" s="14"/>
+      <c r="G272" s="18"/>
+    </row>
+    <row r="273" spans="1:7" ht="19" customHeight="1">
+      <c r="A273" s="9">
         <v>1148272907</v>
       </c>
-      <c r="B273" s="13" t="s">
+      <c r="B273" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="C273" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D273" s="20">
+      <c r="C273" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D273" s="7">
         <v>6</v>
       </c>
-      <c r="E273" s="11"/>
-      <c r="F273" s="12"/>
-    </row>
-    <row r="274" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A274" s="17">
+      <c r="E273" s="5"/>
+      <c r="F273" s="14"/>
+      <c r="G273" s="18"/>
+    </row>
+    <row r="274" spans="1:7" ht="19" customHeight="1">
+      <c r="A274" s="9">
         <v>1149254607</v>
       </c>
-      <c r="B274" s="13" t="s">
+      <c r="B274" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C274" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D274" s="20">
+      <c r="C274" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D274" s="7">
         <v>6</v>
       </c>
-      <c r="E274" s="11"/>
-      <c r="F274" s="12"/>
-    </row>
-    <row r="275" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A275" s="17">
+      <c r="E274" s="5"/>
+      <c r="F274" s="14"/>
+      <c r="G274" s="18"/>
+    </row>
+    <row r="275" spans="1:7" ht="19" customHeight="1">
+      <c r="A275" s="9">
         <v>1149049734</v>
       </c>
-      <c r="B275" s="13" t="s">
+      <c r="B275" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C275" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D275" s="20">
+      <c r="C275" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D275" s="7">
         <v>6</v>
       </c>
-      <c r="E275" s="11"/>
-      <c r="F275" s="12"/>
-    </row>
-    <row r="276" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A276" s="17">
+      <c r="E275" s="5"/>
+      <c r="F275" s="14"/>
+      <c r="G275" s="18"/>
+    </row>
+    <row r="276" spans="1:7" ht="19" customHeight="1">
+      <c r="A276" s="9">
         <v>1147396244</v>
       </c>
-      <c r="B276" s="13" t="s">
+      <c r="B276" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="C276" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D276" s="20">
+      <c r="C276" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D276" s="7">
         <v>6</v>
       </c>
-      <c r="E276" s="11"/>
-      <c r="F276" s="12"/>
-    </row>
-    <row r="277" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A277" s="17">
+      <c r="E276" s="5"/>
+      <c r="F276" s="14"/>
+      <c r="G276" s="18"/>
+    </row>
+    <row r="277" spans="1:7" ht="19" customHeight="1">
+      <c r="A277" s="9">
         <v>1146310931</v>
       </c>
-      <c r="B277" s="13" t="s">
+      <c r="B277" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="C277" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D277" s="20">
+      <c r="C277" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D277" s="7">
         <v>6</v>
       </c>
-      <c r="E277" s="11"/>
-      <c r="F277" s="12"/>
-    </row>
-    <row r="278" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A278" s="17">
+      <c r="E277" s="5"/>
+      <c r="F277" s="14"/>
+      <c r="G277" s="18"/>
+    </row>
+    <row r="278" spans="1:7" ht="19" customHeight="1">
+      <c r="A278" s="9">
         <v>1145927230</v>
       </c>
-      <c r="B278" s="13" t="s">
+      <c r="B278" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="C278" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D278" s="20">
+      <c r="C278" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D278" s="7">
         <v>6</v>
       </c>
-      <c r="E278" s="11"/>
-      <c r="F278" s="12"/>
-    </row>
-    <row r="279" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A279" s="17">
+      <c r="E278" s="5"/>
+      <c r="F278" s="14"/>
+      <c r="G278" s="18"/>
+    </row>
+    <row r="279" spans="1:7" ht="19" customHeight="1">
+      <c r="A279" s="9">
         <v>1148274754</v>
       </c>
-      <c r="B279" s="13" t="s">
+      <c r="B279" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="C279" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D279" s="20">
+      <c r="C279" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D279" s="7">
         <v>6</v>
       </c>
-      <c r="E279" s="11"/>
-      <c r="F279" s="12"/>
-    </row>
-    <row r="280" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A280" s="17">
+      <c r="E279" s="5"/>
+      <c r="F279" s="14"/>
+      <c r="G279" s="18"/>
+    </row>
+    <row r="280" spans="1:7" ht="19" customHeight="1">
+      <c r="A280" s="9">
         <v>1147544322</v>
       </c>
-      <c r="B280" s="13" t="s">
+      <c r="B280" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C280" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D280" s="20">
+      <c r="C280" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D280" s="7">
         <v>6</v>
       </c>
-      <c r="E280" s="11"/>
-      <c r="F280" s="12"/>
-    </row>
-    <row r="281" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A281" s="17">
+      <c r="E280" s="5"/>
+      <c r="F280" s="14"/>
+      <c r="G280" s="18"/>
+    </row>
+    <row r="281" spans="1:7" ht="19" customHeight="1">
+      <c r="A281" s="9">
         <v>1146374598</v>
       </c>
-      <c r="B281" s="13" t="s">
+      <c r="B281" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C281" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D281" s="20">
+      <c r="C281" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D281" s="7">
         <v>6</v>
       </c>
-      <c r="E281" s="11"/>
-      <c r="F281" s="12"/>
-    </row>
-    <row r="282" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A282" s="17">
+      <c r="E281" s="5"/>
+      <c r="F281" s="14"/>
+      <c r="G281" s="18"/>
+    </row>
+    <row r="282" spans="1:7" ht="19" customHeight="1">
+      <c r="A282" s="9">
         <v>1150177127</v>
       </c>
-      <c r="B282" s="13" t="s">
+      <c r="B282" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="C282" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D282" s="20">
+      <c r="C282" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D282" s="7">
         <v>6</v>
       </c>
-      <c r="E282" s="11"/>
-      <c r="F282" s="12"/>
-    </row>
-    <row r="283" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A283" s="17">
+      <c r="E282" s="5"/>
+      <c r="F282" s="14"/>
+      <c r="G282" s="18"/>
+    </row>
+    <row r="283" spans="1:7" ht="19" customHeight="1">
+      <c r="A283" s="9">
         <v>1147539728</v>
       </c>
-      <c r="B283" s="13" t="s">
+      <c r="B283" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C283" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D283" s="20">
+      <c r="C283" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D283" s="7">
         <v>6</v>
       </c>
-      <c r="E283" s="11"/>
-      <c r="F283" s="12"/>
-    </row>
-    <row r="284" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A284" s="17">
+      <c r="E283" s="5"/>
+      <c r="F283" s="14"/>
+      <c r="G283" s="18"/>
+    </row>
+    <row r="284" spans="1:7" ht="19" customHeight="1">
+      <c r="A284" s="9">
         <v>1147293839</v>
       </c>
-      <c r="B284" s="13" t="s">
+      <c r="B284" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C284" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D284" s="20">
+      <c r="C284" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D284" s="7">
         <v>6</v>
       </c>
-      <c r="E284" s="11"/>
-      <c r="F284" s="12"/>
-    </row>
-    <row r="285" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A285" s="17">
+      <c r="E284" s="5"/>
+      <c r="F284" s="14"/>
+      <c r="G284" s="18"/>
+    </row>
+    <row r="285" spans="1:7" ht="19" customHeight="1">
+      <c r="A285" s="9">
         <v>1148251356</v>
       </c>
-      <c r="B285" s="13" t="s">
+      <c r="B285" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C285" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D285" s="20">
+      <c r="C285" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D285" s="7">
         <v>6</v>
       </c>
-      <c r="E285" s="11"/>
-      <c r="F285" s="12"/>
-    </row>
-    <row r="286" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A286" s="17">
+      <c r="E285" s="5"/>
+      <c r="F285" s="14"/>
+      <c r="G285" s="18"/>
+    </row>
+    <row r="286" spans="1:7" ht="19" customHeight="1">
+      <c r="A286" s="9">
         <v>1147637472</v>
       </c>
-      <c r="B286" s="13" t="s">
+      <c r="B286" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C286" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D286" s="20">
+      <c r="C286" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D286" s="7">
         <v>6</v>
       </c>
-      <c r="E286" s="11"/>
-      <c r="F286" s="12"/>
-    </row>
-    <row r="287" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A287" s="17">
+      <c r="E286" s="5"/>
+      <c r="F286" s="14"/>
+      <c r="G286" s="18"/>
+    </row>
+    <row r="287" spans="1:7" ht="19" customHeight="1">
+      <c r="A287" s="9">
         <v>1149530295</v>
       </c>
-      <c r="B287" s="13" t="s">
+      <c r="B287" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C287" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D287" s="20">
+      <c r="C287" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D287" s="7">
         <v>6</v>
       </c>
-      <c r="E287" s="11"/>
-      <c r="F287" s="12"/>
-    </row>
-    <row r="288" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A288" s="17">
+      <c r="E287" s="5"/>
+      <c r="F287" s="14"/>
+      <c r="G287" s="18"/>
+    </row>
+    <row r="288" spans="1:7" ht="19" customHeight="1">
+      <c r="A288" s="9">
         <v>1148778382</v>
       </c>
-      <c r="B288" s="13" t="s">
+      <c r="B288" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C288" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D288" s="20">
+      <c r="C288" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D288" s="7">
         <v>6</v>
       </c>
-      <c r="E288" s="11"/>
-      <c r="F288" s="12"/>
-    </row>
-    <row r="289" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A289" s="17">
+      <c r="E288" s="5"/>
+      <c r="F288" s="14"/>
+      <c r="G288" s="18"/>
+    </row>
+    <row r="289" spans="1:7" ht="19" customHeight="1">
+      <c r="A289" s="9">
         <v>1147236846</v>
       </c>
-      <c r="B289" s="13" t="s">
+      <c r="B289" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C289" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D289" s="20">
+      <c r="C289" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D289" s="7">
         <v>6</v>
       </c>
-      <c r="E289" s="11"/>
-      <c r="F289" s="12"/>
-    </row>
-    <row r="290" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A290" s="17">
+      <c r="E289" s="5"/>
+      <c r="F289" s="14"/>
+      <c r="G289" s="18"/>
+    </row>
+    <row r="290" spans="1:7" ht="19" customHeight="1">
+      <c r="A290" s="9">
         <v>2389352689</v>
       </c>
-      <c r="B290" s="13" t="s">
+      <c r="B290" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="C290" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D290" s="20">
+      <c r="C290" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D290" s="7">
         <v>6</v>
       </c>
-      <c r="E290" s="11"/>
-      <c r="F290" s="12"/>
-    </row>
-    <row r="291" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A291" s="17">
+      <c r="E290" s="5"/>
+      <c r="F290" s="14"/>
+      <c r="G290" s="18"/>
+    </row>
+    <row r="291" spans="1:7" ht="19" customHeight="1">
+      <c r="A291" s="9">
         <v>2319640955</v>
       </c>
-      <c r="B291" s="13" t="s">
+      <c r="B291" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="C291" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D291" s="20">
+      <c r="C291" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D291" s="7">
         <v>6</v>
       </c>
-      <c r="E291" s="11"/>
-      <c r="F291" s="12"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="14"/>
+      <c r="G291" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
